--- a/src/content/info/案例指标信息.xlsx
+++ b/src/content/info/案例指标信息.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\L\d\03-开合\OpenLink\src\content\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B7677C-F64A-4554-9B94-9049C6E8EC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5452B9B8-E6E8-43CE-BE37-E6268D59F53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="623">
   <si>
     <t>时间（date）</t>
   </si>
@@ -127,1675 +127,1844 @@
     <t>2025-08-14</t>
   </si>
   <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>深圳南园街道立面改造</t>
+  </si>
+  <si>
+    <t>Facade Renovation Project of Nanyuan Subdistrict, Shenzhen</t>
+  </si>
+  <si>
+    <t>城市更新</t>
+  </si>
+  <si>
+    <t>Urban Renewal</t>
+  </si>
+  <si>
+    <t>3500㎡</t>
+  </si>
+  <si>
+    <t>深圳南园路</t>
+  </si>
+  <si>
+    <t>Nanyuan Rd, Shenzhen</t>
+  </si>
+  <si>
+    <t>Real Stone Coating, Exterior Wall Paint, Silicone LED Strip Lights</t>
+  </si>
+  <si>
+    <t>住宅、商业</t>
+  </si>
+  <si>
+    <t>Residential，Commercial</t>
+  </si>
+  <si>
+    <t>深圳市南园街道办</t>
+  </si>
+  <si>
+    <t>Nanyuan Subdistrict Office, Futian District, Shenzhen</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>妈湾3座桥</t>
+  </si>
+  <si>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>新疆轩润晟非物质文化遗产科技艺术产业园</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>谢老师 观音寺项目</t>
+  </si>
+  <si>
+    <t>2024-10-14</t>
+  </si>
+  <si>
+    <t>妈湾城市艺术装置</t>
+  </si>
+  <si>
+    <t>2024-09-06</t>
+  </si>
+  <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
+    <t>后海小学初步设计</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>宁夏国药温泉康养小镇</t>
+  </si>
+  <si>
+    <t>Ningxia Sinopharm Hot Spring Wellness Town</t>
+  </si>
+  <si>
+    <t>酒店</t>
+  </si>
+  <si>
+    <t>Hot Spring Resort Hotel</t>
+  </si>
+  <si>
+    <t>150600㎡</t>
+  </si>
+  <si>
+    <t>宁夏固原市泾源县</t>
+  </si>
+  <si>
+    <t>Jingyuan County, Guyuan City, Ningxia Hui Autonomous Region</t>
+  </si>
+  <si>
+    <t>Honeycomb aluminum panels, solid wood,  glass curtain wall</t>
+  </si>
+  <si>
+    <t>温泉别墅、温泉酒店、高端民宿</t>
+  </si>
+  <si>
+    <t>Hot Spring Villas, Hot Spring Hotel, High-end Homestays</t>
+  </si>
+  <si>
+    <t>中国医药集团有限公司</t>
+  </si>
+  <si>
+    <t>China National Pharmaceutical Group Corporation</t>
+  </si>
+  <si>
+    <t>2024-02-22</t>
+  </si>
+  <si>
+    <t>吕洞山景区游客服务中心设计</t>
+  </si>
+  <si>
+    <t>2024-01-03</t>
+  </si>
+  <si>
+    <t>东莞滨海文化区方案设计国际竞赛</t>
+  </si>
+  <si>
+    <t>2023-12-13</t>
+  </si>
+  <si>
+    <t>武夷山茶庄园项目概念规划</t>
+  </si>
+  <si>
+    <t>2023-11-30</t>
+  </si>
+  <si>
+    <t>珠海市（第四批）历史建筑数字化建档</t>
+  </si>
+  <si>
+    <t>2023-11-06</t>
+  </si>
+  <si>
+    <t>深圳前海哈罗外籍人员子女学校改造</t>
+  </si>
+  <si>
+    <t>2023-11-01</t>
+  </si>
+  <si>
+    <t>呼伦贝尔小酒吧</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>河南信阳车云山茶文化民宿</t>
+  </si>
+  <si>
+    <t>Cheyun Mountain Tea Culture Homestay, Xinyang, Henan Province</t>
+  </si>
+  <si>
+    <t>度假民宿</t>
+  </si>
+  <si>
+    <t>Vacation Homestay</t>
+  </si>
+  <si>
+    <t>3900㎡</t>
+  </si>
+  <si>
+    <t>信阳市董家河车云山</t>
+  </si>
+  <si>
+    <t>Cheyun Mountain, Dongjiahe, Xinyang City, Henan Province</t>
+  </si>
+  <si>
+    <t>原木、铝镁锰屋面板、玻璃幕墙</t>
+  </si>
+  <si>
+    <t>Honeycomb aluminum panels、solid wood、glass curtain wall</t>
+  </si>
+  <si>
+    <t>度假民宿、接待、展厅</t>
+  </si>
+  <si>
+    <t>Vacation Homestay，Reception，Showroom</t>
+  </si>
+  <si>
+    <t>河南省住建厅</t>
+  </si>
+  <si>
+    <t>Department of Housing and Urban-Rural Development of Henan Province</t>
+  </si>
+  <si>
+    <t>五里山房</t>
+  </si>
+  <si>
+    <t>2023-08-29</t>
+  </si>
+  <si>
+    <t>台湾新竹县竹东客家文化大合埕</t>
+  </si>
+  <si>
+    <t>Dahecheng of Hakka Culture, Zhudong, Hsinchu County, Taiwan</t>
+  </si>
+  <si>
+    <t>文化建筑</t>
+  </si>
+  <si>
+    <t>Cultural Building</t>
+  </si>
+  <si>
+    <t>11353.78㎡</t>
+  </si>
+  <si>
+    <t>台湾新竹县</t>
+  </si>
+  <si>
+    <t>Hsinchu County, Taiwan, China</t>
+  </si>
+  <si>
+    <t>Fair-facedConcrete, Weathering Steel，Granite，Chinese Fir，Exposed Aggregate</t>
+  </si>
+  <si>
+    <t>办公、商业、展厅、展演、餐饮</t>
+  </si>
+  <si>
+    <t>Office, Commercial, Showroom, Performance Hall, Catering Area</t>
+  </si>
+  <si>
+    <t>新竹县政府</t>
+  </si>
+  <si>
+    <t>Henan Investment Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2023-07-20</t>
+  </si>
+  <si>
+    <t>鹤湖新居微更新</t>
+  </si>
+  <si>
+    <t>2023-07-09</t>
+  </si>
+  <si>
+    <t>海南环岛公路重点驿站酒店</t>
+  </si>
+  <si>
+    <t>Key Resort Inns of Hainan Coastal Ring Road</t>
+  </si>
+  <si>
+    <t>度假驿站酒店</t>
+  </si>
+  <si>
+    <t>Holiday Resort Inn</t>
+  </si>
+  <si>
+    <t>48700㎡</t>
+  </si>
+  <si>
+    <t>海南省东方市板桥镇</t>
+  </si>
+  <si>
+    <t>Banqiao Town, Dongfang City, Hainan Province</t>
+  </si>
+  <si>
+    <t>Fair-Faced Concrete, Aluminum Honeycomb Panel, Glass</t>
+  </si>
+  <si>
+    <t>艺术酒店、艺术博物馆、游客中心、国际交流中心</t>
+  </si>
+  <si>
+    <t>Art Hotel, Art Museum, Visitor Center 、International Exchange Center</t>
+  </si>
+  <si>
+    <t>海南省自然资源和规划厅</t>
+  </si>
+  <si>
+    <t>Hainan Provincial Department of Natural Resources and Planning</t>
+  </si>
+  <si>
+    <t>2023-07-07</t>
+  </si>
+  <si>
+    <t>南方新住宅竞赛</t>
+  </si>
+  <si>
+    <t>2023-06-16</t>
+  </si>
+  <si>
+    <t>坪山河景观桥概念方案设计</t>
+  </si>
+  <si>
+    <t>2023-05-21</t>
+  </si>
+  <si>
+    <t>中原制药厂</t>
+  </si>
+  <si>
+    <t>Zhongyuan Pharmaceutical Factory</t>
+  </si>
+  <si>
+    <t>产业园</t>
+  </si>
+  <si>
+    <t>Industrial Park</t>
+  </si>
+  <si>
+    <t>430000㎡</t>
+  </si>
+  <si>
+    <t>郑州市高新区</t>
+  </si>
+  <si>
+    <t>Zhengzhou High Tech Zone</t>
+  </si>
+  <si>
+    <t>Fair-faced Concrete, Anodized Aluminum Panel, Glass, Weathering Steel</t>
+  </si>
+  <si>
+    <t>办公、商业、展厅、会议、生产车间</t>
+  </si>
+  <si>
+    <t>Office，Commercial，Exhibition Hall，Conference，Production Workshop</t>
+  </si>
+  <si>
+    <t>河南投资集团</t>
+  </si>
+  <si>
+    <t>2023-05-03</t>
+  </si>
+  <si>
+    <t>百校焕新项目</t>
+  </si>
+  <si>
+    <t>2023-04-03</t>
+  </si>
+  <si>
+    <t>利元亨南通华东</t>
+  </si>
+  <si>
+    <t>2022-12-20</t>
+  </si>
+  <si>
+    <t>广东嘉速物流工改工项目</t>
+  </si>
+  <si>
+    <t>2022-11-10</t>
+  </si>
+  <si>
+    <t>大江东唐焱厂房BIPV</t>
+  </si>
+  <si>
+    <t>BIPV Project of Tangyan Factory Building, Dadongjiang</t>
+  </si>
+  <si>
+    <t>厂房</t>
+  </si>
+  <si>
+    <t>Factory Building</t>
+  </si>
+  <si>
+    <t>139455㎡</t>
+  </si>
+  <si>
+    <t>浙江省杭州市钱塘区</t>
+  </si>
+  <si>
+    <t>Qiantang District, Hangzhou City, Zhejiang Province, China</t>
+  </si>
+  <si>
+    <t>耐候钢、彩釉玻璃、铝板、碲化镉光伏组件</t>
+  </si>
+  <si>
+    <t>Weathering Steel，Color Glazed Glass，Aluminum Panel，CdTe PV Module</t>
+  </si>
+  <si>
+    <t>厂房、立体车库</t>
+  </si>
+  <si>
+    <t>Factory Building，Stereo Parking Garage</t>
+  </si>
+  <si>
+    <t>焱唐能源科技(杭州)有限责任公司</t>
+  </si>
+  <si>
+    <t>Yantang Energy Technology (Hangzhou) Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2022-05-18</t>
+  </si>
+  <si>
+    <t>大疆顺德智能科技园</t>
+  </si>
+  <si>
+    <t>DJI Shunde Intelligent Science &amp; Technology Park</t>
+  </si>
+  <si>
+    <t>175000㎡</t>
+  </si>
+  <si>
+    <t>佛山市顺德区</t>
+  </si>
+  <si>
+    <t>Shunde District, Foshan City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>Glulam，Weathering Steel，Profiled Metal Sheet</t>
+  </si>
+  <si>
+    <t>深圳市大疆创新科技有限公司</t>
+  </si>
+  <si>
+    <t>SZ DJI Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
+    <t>老君山瑞玺叶星河酒店</t>
+  </si>
+  <si>
+    <t>Laojun Mountain Ruixi Yexinghe Hotel</t>
+  </si>
+  <si>
+    <t>度假酒店</t>
+  </si>
+  <si>
+    <t>Resort Hotel</t>
+  </si>
+  <si>
+    <t>2800㎡</t>
+  </si>
+  <si>
+    <t>洛阳市栾川县老君山追梦谷</t>
+  </si>
+  <si>
+    <t>Laojun Mountain Dream Valley, Luanchuan County, Luoyang City</t>
+  </si>
+  <si>
+    <t>Pure White Micro-Cement、Solid Wood、Dark Grey Stone、Glass Curtain Wall</t>
+  </si>
+  <si>
+    <t>别墅观景客房、商务接待、餐饮、艺术长廊</t>
+  </si>
+  <si>
+    <t>Villa Viewing Guest Rooms、Business Reception Area、Catering、Art Corridor</t>
+  </si>
+  <si>
+    <t>洛阳瑞玺叶星河民宿有限公司</t>
+  </si>
+  <si>
+    <t>Luoyang Ruixi Yexinghe Homestay Co., Ltd.</t>
+  </si>
+  <si>
+    <t>嘉荣物流产业园</t>
+  </si>
+  <si>
+    <t>Jiarong Logistics Industrial Park</t>
+  </si>
+  <si>
+    <t>433540㎡</t>
+  </si>
+  <si>
+    <t>东莞市洪梅镇</t>
+  </si>
+  <si>
+    <t>Hongmei Town, Dongguan City</t>
+  </si>
+  <si>
+    <t>Fair-Facedconcrete, Glulam，Anodized Aluminum Panel，Metal Grille，</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、宿舍、商业</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Dormitory，Commercial</t>
+  </si>
+  <si>
+    <t>东莞市嘉耀实业投资有限公司</t>
+  </si>
+  <si>
+    <t>Dongguan Jiayao Industrial Investment Co., Ltd.</t>
+  </si>
+  <si>
+    <t>小天才智能科技中心</t>
+  </si>
+  <si>
+    <t>Imoo Intelligent Technology Center</t>
+  </si>
+  <si>
+    <t>Science and Technology Park</t>
+  </si>
+  <si>
+    <t>195560㎡</t>
+  </si>
+  <si>
+    <t>东莞市滨海湾新区</t>
+  </si>
+  <si>
+    <t>Dongguan Binhaiwan New District</t>
+  </si>
+  <si>
+    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃</t>
+  </si>
+  <si>
+    <t>Glulam，Anodized Aluminum Panel，Metal Grille，Glass</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、公寓</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Apartment</t>
+  </si>
+  <si>
+    <t>广东小天才科技有限公司</t>
+  </si>
+  <si>
+    <t>Guangdong Genius Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>生命之树装置深化设计</t>
+  </si>
+  <si>
+    <t>Detail Design of Tree of Life Installation</t>
+  </si>
+  <si>
+    <t>艺术装置</t>
+  </si>
+  <si>
+    <t>Art Installation</t>
+  </si>
+  <si>
+    <t>300㎡</t>
+  </si>
+  <si>
+    <t>重庆市经开区</t>
+  </si>
+  <si>
+    <t>Chongqing Economic and Technological Development Zone</t>
+  </si>
+  <si>
+    <t>胶合木</t>
+  </si>
+  <si>
+    <t>Glulam</t>
+  </si>
+  <si>
+    <t>广阳湾珊瑚小学</t>
+  </si>
+  <si>
+    <t>Guangyang Bay Coral Primary School</t>
+  </si>
+  <si>
+    <t>2021-12-03</t>
+  </si>
+  <si>
+    <t>庐南学校项目</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>菜鸟物流中心</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>鹏峰</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>小米上海汽车总部</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>城市展厅</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>华为团泊洼地办公项目</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>欢聚集团总部产业园</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>海阳路学校</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>佛山企业家大厦</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>鹏峰奥迪4s店</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>境工作室汇报</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>万兴科技产业研究中心</t>
+  </si>
+  <si>
+    <t>Wondershare Industrial Research Center</t>
+  </si>
+  <si>
+    <t>119344㎡</t>
+  </si>
+  <si>
+    <t>湖南长沙市</t>
+  </si>
+  <si>
+    <t>Changsha City, Hunan Province</t>
+  </si>
+  <si>
+    <t>研发办公、商业、公寓</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Office，Commercial，Apartment</t>
+  </si>
+  <si>
+    <t>万兴科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Wondershare Technology Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2020-09-18</t>
+  </si>
+  <si>
+    <t>李沧项目</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>小天才产业园</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>常州怀德中路项目</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>中联重科智慧产业城</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>佛山绿地彩管大厦</t>
+  </si>
+  <si>
+    <t>Greenland Caiguan Building, Foshan</t>
+  </si>
+  <si>
+    <t>超高层办公楼</t>
+  </si>
+  <si>
+    <t>Super High-rise Office Building</t>
+  </si>
+  <si>
+    <t>261173㎡</t>
+  </si>
+  <si>
+    <t>佛山市禅城区</t>
+  </si>
+  <si>
+    <t>Chancheng District, Foshan</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel，Glass，Perforated Metal Panel</t>
+  </si>
+  <si>
+    <t>办公、酒店、数据中心</t>
+  </si>
+  <si>
+    <t>Office, Hotel，Data Center Complex</t>
+  </si>
+  <si>
+    <t>绿地集团</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
+    <t>广东洲明节能科技有限公司LED生产基地</t>
+  </si>
+  <si>
+    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd. LED Production Base</t>
+  </si>
+  <si>
+    <t>394349㎡</t>
+  </si>
+  <si>
+    <t>惠州市大亚湾区</t>
+  </si>
+  <si>
+    <t>Dayawan District, Huizhou City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、金属格栅、玻璃</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel，Metal Grille，Glass</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、宿舍</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Dormitory</t>
+  </si>
+  <si>
+    <t>广东洲明节能科技有限公司</t>
+  </si>
+  <si>
+    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>PA018276.01中粮祥云•地铁小镇项目商办地块</t>
+  </si>
+  <si>
+    <t>中粮祥云•地铁小镇项目商办地块</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>虹海研发大厦</t>
+  </si>
+  <si>
+    <t>2019-09-29</t>
+  </si>
+  <si>
+    <t>联润大厦项目</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>万达展览馆</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>郑州富士康蔚来云城商业D地块方案</t>
+  </si>
+  <si>
+    <t>2019-02-18</t>
+  </si>
+  <si>
+    <t>许昌信通金融中心项目</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
+    <t>黄山五里山房酒店群</t>
+  </si>
+  <si>
+    <t>Wuli Shanfang Hotel Cluster, Huangshan</t>
+  </si>
+  <si>
+    <t>21500㎡</t>
+  </si>
+  <si>
+    <t>安徽黄山黟县碧阳镇</t>
+  </si>
+  <si>
+    <t>Biyang Town, Yi County, Huangshan City, Anhui Province</t>
+  </si>
+  <si>
+    <t>艺术涂料、金属穿孔铝板、铝镁锰屋面板、青灰瓦</t>
+  </si>
+  <si>
+    <t>Art Coating、Perforated Aluminum Panel、Aluminum-Magnesium-Manganese Roof Panel、Blue-Grey Clay Tile</t>
+  </si>
+  <si>
+    <t>度假别墅客房、商务接待、茶文化展厅、徽文化研学</t>
+  </si>
+  <si>
+    <t>Holiday Villa Guest Rooms, Business Reception Area, Tea Culture Exhibition Hall 、Huizhou Culture Study Base</t>
+  </si>
+  <si>
+    <t>黟县徽黄旅游发展有限公司</t>
+  </si>
+  <si>
+    <t>Yixian Huihuang Tourism Development Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>恒大水世界</t>
+  </si>
+  <si>
+    <t>2018-09-29</t>
+  </si>
+  <si>
+    <t>公司2015-2018作品集</t>
+  </si>
+  <si>
+    <t>2018-09-10</t>
+  </si>
+  <si>
+    <t>崇州7号地块</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>公司装修</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>郑州曲梁863产业园</t>
+  </si>
+  <si>
+    <t>2018-02-11</t>
+  </si>
+  <si>
+    <t>昆仑世纪花园</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>广西巴马酒店综合体项目</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
+    <t>巴马.高端星级酒店综合体</t>
+  </si>
+  <si>
+    <t>Premium Star-rated Hotel Complex in Bama</t>
+  </si>
+  <si>
+    <t>高端度假酒店综合体</t>
+  </si>
+  <si>
+    <t>Premium Holiday Hotel Complex</t>
+  </si>
+  <si>
+    <t>200865㎡</t>
+  </si>
+  <si>
+    <t>巴马瑶族自治县</t>
+  </si>
+  <si>
+    <t>Bama Yao Autonomous County</t>
+  </si>
+  <si>
+    <t>蜂窝铝板、玻璃幕墙、金属格栅</t>
+  </si>
+  <si>
+    <t>Honeycomb Aluminum Panels, Glass Curtain Wall 、 Metal Grilles</t>
+  </si>
+  <si>
+    <t>五星级酒店、高端公寓、瑶族文化体验中心</t>
+  </si>
+  <si>
+    <t>Five-star Hotel, High-end Apartments, Yao Culture Experience Center</t>
+  </si>
+  <si>
+    <t>广西长江天成投资集团</t>
+  </si>
+  <si>
+    <t>Guangxi Yangtze Tessa Investment Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2017-12-05</t>
+  </si>
+  <si>
+    <t>宜宾亿豪酒店</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>甘肃西部中药城</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>福建德化城东中小企业创业园</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>新安区第三工业区康美智慧药房改造项目概念方案</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>康养健康小镇咸宁项目概念性规划设计</t>
+  </si>
+  <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
+    <t>郑州金水</t>
+  </si>
+  <si>
+    <t>2017-05-22</t>
+  </si>
+  <si>
+    <t>广西玉林中药城项目</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>湖南靖州茯苓物流交易中心</t>
+  </si>
+  <si>
+    <t>2017-03-14</t>
+  </si>
+  <si>
+    <t>西宁城西御景华城</t>
+  </si>
+  <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
+    <t>佛山顺德家具厂</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>螺阳镇会所</t>
+  </si>
+  <si>
+    <t>2016-12-19</t>
+  </si>
+  <si>
+    <t>南京K2016-腾旭科技</t>
+  </si>
+  <si>
+    <t>2016-10-26</t>
+  </si>
+  <si>
+    <t>同济工业大厦立面设计</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>广东东明节能科技有限公司LED生产基地项目</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>螺阳镇松星村安置区</t>
+  </si>
+  <si>
+    <t>2016-06-12</t>
+  </si>
+  <si>
+    <t>中国（揭阳）国际珠宝翡翠交易中心项目</t>
+  </si>
+  <si>
+    <t>2016-06-10</t>
+  </si>
+  <si>
+    <t>亲戚房子（谢勇士+高丽+邱四平）</t>
+  </si>
+  <si>
+    <t>2016-05-09</t>
+  </si>
+  <si>
+    <t>中港珠宝旅游商业城</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>富士康企业会所</t>
+  </si>
+  <si>
+    <t>2016-03-30</t>
+  </si>
+  <si>
+    <t>坪山周大生</t>
+  </si>
+  <si>
+    <t>2015-12-21</t>
+  </si>
+  <si>
+    <t>晋江周氏置业项目</t>
+  </si>
+  <si>
+    <t>2015-09-09</t>
+  </si>
+  <si>
+    <t>深圳检验检测认证技术中心建筑设计项目</t>
+  </si>
+  <si>
+    <t>2015-09-01</t>
+  </si>
+  <si>
+    <t>深圳职业技术学院留仙洞校区G栋学生宿舍建设</t>
+  </si>
+  <si>
+    <t>2015-08-13</t>
+  </si>
+  <si>
+    <t>宏发公明售楼处</t>
+  </si>
+  <si>
+    <t>2015-07-14</t>
+  </si>
+  <si>
+    <t>梅林中学扩建学生宿舍楼工程</t>
+  </si>
+  <si>
+    <t>2015-06-01</t>
+  </si>
+  <si>
+    <t>美国云峰商务酒店</t>
+  </si>
+  <si>
+    <t>2015-05-25</t>
+  </si>
+  <si>
+    <t>博林沙井地块项目</t>
+  </si>
+  <si>
+    <t>2015-05-21</t>
+  </si>
+  <si>
+    <t>坪山现代精密办公楼</t>
+  </si>
+  <si>
+    <t>2015-05-08</t>
+  </si>
+  <si>
+    <t>宝投航城工业厂区设计</t>
+  </si>
+  <si>
+    <t>2015-03-12</t>
+  </si>
+  <si>
+    <t>拉斯维加斯雪蛋赌场</t>
+  </si>
+  <si>
+    <t>2015-02-10</t>
+  </si>
+  <si>
+    <t>滇红博物馆</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>深圳大鹏较场尾大旅小舍民宿改造</t>
+  </si>
+  <si>
+    <t>Dalv Xiaoshe Homestay Renovation Project, Jiaochangwei, Dapeng New Area, Shenzhen</t>
+  </si>
+  <si>
+    <t>民宿</t>
+  </si>
+  <si>
+    <t>166485㎡</t>
+  </si>
+  <si>
+    <t>2014-09-17</t>
+  </si>
+  <si>
+    <t>博林天瑞花园立面</t>
+  </si>
+  <si>
+    <t>2014-07-30</t>
+  </si>
+  <si>
+    <t>岑溪汇洋新世界</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>龙华简上村（原2011-04-30—部项目）</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>岑溪市思湖广场</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>河北天户峪旅游度假村项目</t>
+  </si>
+  <si>
+    <t>2014-05-20</t>
+  </si>
+  <si>
+    <t>蛇口工业八路南源工业区更新单元改造项目</t>
+  </si>
+  <si>
+    <t>2014-04-02</t>
+  </si>
+  <si>
+    <t>中泰艺术名庭改造</t>
+  </si>
+  <si>
+    <t>2014-03-26</t>
+  </si>
+  <si>
+    <t>深圳湾“超级城市”国际竞赛</t>
+  </si>
+  <si>
+    <t>2013-12-29</t>
+  </si>
+  <si>
+    <t>博林海德城</t>
+  </si>
+  <si>
+    <t>2013-12-24</t>
+  </si>
+  <si>
+    <t>广东喜之郎集团总部大厦</t>
+  </si>
+  <si>
+    <t>2013-11-25</t>
+  </si>
+  <si>
+    <t>南京明发</t>
+  </si>
+  <si>
+    <t>2013-10-10</t>
+  </si>
+  <si>
+    <t>宝安机场城市更新项目</t>
+  </si>
+  <si>
+    <t>2013-09-18</t>
+  </si>
+  <si>
+    <t>城市复兴</t>
+  </si>
+  <si>
+    <t>2013-09-13</t>
+  </si>
+  <si>
+    <t>宝安机场口岸综合楼项目</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>华润深圳湾综合发展项目北区住宅竞赛</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>老挝茶文化体验中心</t>
+  </si>
+  <si>
+    <t>2013-02-13</t>
+  </si>
+  <si>
+    <t>武汉大学艺术楼</t>
+  </si>
+  <si>
+    <t>Fine Arts Building, Wuhan University</t>
+  </si>
+  <si>
+    <t>文教</t>
+  </si>
+  <si>
+    <t>Culture &amp; Education</t>
+  </si>
+  <si>
+    <t>5371㎡</t>
+  </si>
+  <si>
+    <t>湖北武汉市</t>
+  </si>
+  <si>
+    <t>Wuhan City, Hubei Province</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、玻璃</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel， Glass</t>
+  </si>
+  <si>
+    <t>教室，图书室，音乐厅、会议</t>
+  </si>
+  <si>
+    <t>Classroom, Library, Concert Hall ， Conference Space</t>
+  </si>
+  <si>
+    <t>武汉大学</t>
+  </si>
+  <si>
+    <t>Wuhan University</t>
+  </si>
+  <si>
+    <t>2013-01-01</t>
+  </si>
+  <si>
+    <t>老挝万象茶文化中心</t>
+  </si>
+  <si>
+    <t>Vientiane Tea Culture Center, Laos</t>
+  </si>
+  <si>
+    <t>3200㎡</t>
+  </si>
+  <si>
+    <t>老挝万象市</t>
+  </si>
+  <si>
+    <t>Vientiane Municipality, Laos</t>
+  </si>
+  <si>
+    <t>清水混凝土、胶合木、金属格栅、</t>
+  </si>
+  <si>
+    <t>Fair-Facedconcrete, Glulam， Metal Grille</t>
+  </si>
+  <si>
+    <t>办公、展厅、会所、宿舍</t>
+  </si>
+  <si>
+    <t>Office，Showroom，Club House，Dormitory</t>
+  </si>
+  <si>
+    <t>2012-12-25</t>
+  </si>
+  <si>
+    <t>华润惠州小径湾滨海度假村2期</t>
+  </si>
+  <si>
+    <t>China Resources Park Lane Harbour Coastal Resort Phase 2, Huizhou</t>
+  </si>
+  <si>
+    <t>居住</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>贵阳玉蝶</t>
+  </si>
+  <si>
+    <t>2012-07-14</t>
+  </si>
+  <si>
+    <t>南京文化中心</t>
+  </si>
+  <si>
+    <t>2012-04-10</t>
+  </si>
+  <si>
+    <t>Foshan Entrepreneur Building</t>
+  </si>
+  <si>
+    <t>157553㎡</t>
+  </si>
+  <si>
+    <t>广东佛山市</t>
+  </si>
+  <si>
+    <t>Foshan City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>办公、酒店、会议，商业</t>
+  </si>
+  <si>
+    <t>Office, Hotel, Conference ， Commercial</t>
+  </si>
+  <si>
+    <t>佛山企业家联合体</t>
+  </si>
+  <si>
+    <t>Foshan Entrepreneurs Federation</t>
+  </si>
+  <si>
+    <t>2011-11-06</t>
+  </si>
+  <si>
+    <t>上海杨浦智创天地-w</t>
+  </si>
+  <si>
+    <t>2011-09-05</t>
+  </si>
+  <si>
+    <t>淄博文化中心</t>
+  </si>
+  <si>
+    <t>2011-07-08</t>
+  </si>
+  <si>
+    <t>港珠澳大桥珠海口岸规划国际竞赛</t>
+  </si>
+  <si>
+    <t>International Planning Competition, Zhuhai Port of HZMB</t>
+  </si>
+  <si>
+    <t>交通枢纽</t>
+  </si>
+  <si>
+    <t>Transport Hub（</t>
+  </si>
+  <si>
+    <t>586152m2</t>
+  </si>
+  <si>
+    <t>广东珠海市</t>
+  </si>
+  <si>
+    <t>Zhuhai City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>海关口岸，办公，商业</t>
+  </si>
+  <si>
+    <t>Customs Port, Office ， Commercial Facilities</t>
+  </si>
+  <si>
+    <t>珠海市港珠澳大桥建设协调办公室</t>
+  </si>
+  <si>
+    <t>Zhuhai HZMB Construction Coordination Office</t>
+  </si>
+  <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
+    <t>世界自然基金会汉中游客信息中心</t>
+  </si>
+  <si>
+    <t>WWF Hanzhong Visitor Information Centre</t>
+  </si>
+  <si>
+    <t>Cultural &amp; Tourism</t>
+  </si>
+  <si>
+    <t>332㎡</t>
+  </si>
+  <si>
+    <t>陕西汉中市</t>
+  </si>
+  <si>
+    <t>Hanzhong City, Shaanxi Province</t>
+  </si>
+  <si>
+    <t>胶合木、冷弯薄壁型钢</t>
+  </si>
+  <si>
+    <t>Glulam，Cold-Formed Thin-Wall Steel</t>
+  </si>
+  <si>
+    <t>展厅、接待、办公</t>
+  </si>
+  <si>
+    <t>Showroom, Reception ， Office</t>
+  </si>
+  <si>
+    <t>WWF世界自然基金会</t>
+  </si>
+  <si>
+    <t>WWF – World Wide Fund for Nature</t>
+  </si>
+  <si>
+    <t>2010-12-04</t>
+  </si>
+  <si>
+    <t>淄博大剧院</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
+    <t>四川里坪村小学校</t>
+  </si>
+  <si>
+    <t>Liping Village Primary School, Sichuan</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>201㎡</t>
+  </si>
+  <si>
+    <t>四川青川县</t>
+  </si>
+  <si>
+    <t>Qingchuan, Sichuan</t>
+  </si>
+  <si>
+    <t>生土、原木</t>
+  </si>
+  <si>
+    <t>Raw Earth，Log</t>
+  </si>
+  <si>
+    <t>2022-05-28</t>
+  </si>
+  <si>
+    <t>新丰项目阶段性成果整理</t>
+  </si>
+  <si>
+    <t>2022-01-06</t>
+  </si>
+  <si>
+    <t>新丰美食街</t>
+  </si>
+  <si>
+    <t>新丰菜市场改造</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>规划局环保局办公楼</t>
+  </si>
+  <si>
+    <t>2020-09-06</t>
+  </si>
+  <si>
+    <t>垃圾站+厕所</t>
+  </si>
+  <si>
+    <t>2020-06-27</t>
+  </si>
+  <si>
+    <t>黄局自宅</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>黄寨景观</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>遥田图书馆</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>方志馆档案馆</t>
+  </si>
+  <si>
+    <t>2019-10-12</t>
+  </si>
+  <si>
+    <t>新丰文化中心</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>新丰廉租房项目</t>
+  </si>
+  <si>
+    <t>2019-02-19</t>
+  </si>
+  <si>
+    <t>新丰黄磜镇幸福公社</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>新丰规划局涵洞改造</t>
+  </si>
+  <si>
+    <t>2018-10-10</t>
+  </si>
+  <si>
+    <t>新丰气象站</t>
+  </si>
+  <si>
+    <t>2018-07-31</t>
+  </si>
+  <si>
+    <t>新丰城市厕所项目</t>
+  </si>
+  <si>
+    <t>2018-07-09</t>
+  </si>
+  <si>
+    <t>新丰村委会改造</t>
+  </si>
+  <si>
+    <t>2017-04-17</t>
+  </si>
+  <si>
+    <t>新丰老一中改造</t>
+  </si>
+  <si>
+    <t>外墙漆、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农村自建房别墅景观设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农村自建房别墅设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外墙漆、玻璃、铝板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>376㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱建新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州24时辰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驿站</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、耐候钢、花岗石、杉木、洗石子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐候钢、彩釉玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李松蓢项目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>316574㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高品质生活居住区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、光明区、公明街道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>香槟金铝板、真石漆、莱姆石，玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市公明李松蓢股份合作公司     深圳市特发鸿顺实业有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住、商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100平米</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州市“百千万工程”指挥办</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨海驿站设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装配式居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、耐候钢、压型金属板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>潘先生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教会</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1800㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公楼立面升级改造</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清远市、高新区雄兴工业区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省、陆丰陂洋莲花寨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北省，洪湖市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州市、惠东县、稔平半岛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿孔铝板、铝板、木纹瓷砖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清远市南星化工有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产业园</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非物质文化遗产科技艺术产业园</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30100㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区、乌鲁木齐市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜂窝铝板、原木、玻璃幕墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、蜂窝铝板、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯白微水泥、原木、深灰石材、玻璃幕墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、胶合木、 阳极氧化铝板、金属格栅、</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 阳极氧化铝板、纯白微水泥、木纹瓷砖、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艺术馆、商业、酒店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆轩润景文化传媒有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>城中村住宅外墙立面更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寺院接待、宿舍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寺院活动接待及住宿设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台湾省、台南市、新化区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>学校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>73456㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态的“新公园式学校”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、龙华区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、阳极氧化铝板、玻璃、耐候钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真石漆，外墙漆、硅胶灯带</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、耐候钢、穿孔铝板、外墙漆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙华区工务署</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>观城9年一贯制学校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教学及辅助用房、办公用房、生活用房</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6500㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高端高尔夫练习场设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>西港云壤高尔夫练习场</t>
-  </si>
-  <si>
-    <t>2025-07-23</t>
-  </si>
-  <si>
-    <t>深圳南园街道立面改造</t>
-  </si>
-  <si>
-    <t>Facade Renovation Project of Nanyuan Subdistrict, Shenzhen</t>
-  </si>
-  <si>
-    <t>城市更新</t>
-  </si>
-  <si>
-    <t>Urban Renewal</t>
-  </si>
-  <si>
-    <t>3500㎡</t>
-  </si>
-  <si>
-    <t>深圳南园路</t>
-  </si>
-  <si>
-    <t>Nanyuan Rd, Shenzhen</t>
-  </si>
-  <si>
-    <t>真石漆，外墙漆、硅胶灯带</t>
-  </si>
-  <si>
-    <t>Real Stone Coating, Exterior Wall Paint, Silicone LED Strip Lights</t>
-  </si>
-  <si>
-    <t>住宅、商业</t>
-  </si>
-  <si>
-    <t>Residential，Commercial</t>
-  </si>
-  <si>
-    <t>深圳市南园街道办</t>
-  </si>
-  <si>
-    <t>Nanyuan Subdistrict Office, Futian District, Shenzhen</t>
-  </si>
-  <si>
-    <t>2025-06-22</t>
-  </si>
-  <si>
-    <t>妈湾3座桥</t>
-  </si>
-  <si>
-    <t>2025-02-12</t>
-  </si>
-  <si>
-    <t>新疆轩润晟非物质文化遗产科技艺术产业园</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>谢老师 观音寺项目</t>
-  </si>
-  <si>
-    <t>2024-10-14</t>
-  </si>
-  <si>
-    <t>妈湾城市艺术装置</t>
-  </si>
-  <si>
-    <t>2024-09-06</t>
-  </si>
-  <si>
-    <t>观城9年一贯制学校</t>
-  </si>
-  <si>
-    <t>2024-06-18</t>
-  </si>
-  <si>
-    <t>后海小学初步设计</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>宁夏国药温泉康养小镇</t>
-  </si>
-  <si>
-    <t>Ningxia Sinopharm Hot Spring Wellness Town</t>
-  </si>
-  <si>
-    <t>酒店</t>
-  </si>
-  <si>
-    <t>Hot Spring Resort Hotel</t>
-  </si>
-  <si>
-    <t>150600㎡</t>
-  </si>
-  <si>
-    <t>宁夏固原市泾源县</t>
-  </si>
-  <si>
-    <t>Jingyuan County, Guyuan City, Ningxia Hui Autonomous Region</t>
-  </si>
-  <si>
-    <t>蜂窝铝板、原木、玻璃幕墙</t>
-  </si>
-  <si>
-    <t>Honeycomb aluminum panels, solid wood,  glass curtain wall</t>
-  </si>
-  <si>
-    <t>温泉别墅、温泉酒店、高端民宿</t>
-  </si>
-  <si>
-    <t>Hot Spring Villas, Hot Spring Hotel, High-end Homestays</t>
-  </si>
-  <si>
-    <t>中国医药集团有限公司</t>
-  </si>
-  <si>
-    <t>China National Pharmaceutical Group Corporation</t>
-  </si>
-  <si>
-    <t>2024-02-22</t>
-  </si>
-  <si>
-    <t>吕洞山景区游客服务中心设计</t>
-  </si>
-  <si>
-    <t>2024-01-03</t>
-  </si>
-  <si>
-    <t>东莞滨海文化区方案设计国际竞赛</t>
-  </si>
-  <si>
-    <t>2023-12-13</t>
-  </si>
-  <si>
-    <t>武夷山茶庄园项目概念规划</t>
-  </si>
-  <si>
-    <t>2023-11-30</t>
-  </si>
-  <si>
-    <t>珠海市（第四批）历史建筑数字化建档</t>
-  </si>
-  <si>
-    <t>2023-11-06</t>
-  </si>
-  <si>
-    <t>深圳前海哈罗外籍人员子女学校改造</t>
-  </si>
-  <si>
-    <t>2023-11-01</t>
-  </si>
-  <si>
-    <t>呼伦贝尔小酒吧</t>
-  </si>
-  <si>
-    <t>2023-10-23</t>
-  </si>
-  <si>
-    <t>河南信阳车云山茶文化民宿</t>
-  </si>
-  <si>
-    <t>Cheyun Mountain Tea Culture Homestay, Xinyang, Henan Province</t>
-  </si>
-  <si>
-    <t>度假民宿</t>
-  </si>
-  <si>
-    <t>Vacation Homestay</t>
-  </si>
-  <si>
-    <t>3900㎡</t>
-  </si>
-  <si>
-    <t>信阳市董家河车云山</t>
-  </si>
-  <si>
-    <t>Cheyun Mountain, Dongjiahe, Xinyang City, Henan Province</t>
-  </si>
-  <si>
-    <t>原木、铝镁锰屋面板、玻璃幕墙</t>
-  </si>
-  <si>
-    <t>Honeycomb aluminum panels、solid wood、glass curtain wall</t>
-  </si>
-  <si>
-    <t>度假民宿、接待、展厅</t>
-  </si>
-  <si>
-    <t>Vacation Homestay，Reception，Showroom</t>
-  </si>
-  <si>
-    <t>河南省住建厅</t>
-  </si>
-  <si>
-    <t>Department of Housing and Urban-Rural Development of Henan Province</t>
-  </si>
-  <si>
-    <t>五里山房</t>
-  </si>
-  <si>
-    <t>2023-08-29</t>
-  </si>
-  <si>
-    <t>台湾新竹县竹东客家文化大合埕</t>
-  </si>
-  <si>
-    <t>Dahecheng of Hakka Culture, Zhudong, Hsinchu County, Taiwan</t>
-  </si>
-  <si>
-    <t>文化建筑</t>
-  </si>
-  <si>
-    <t>Cultural Building</t>
-  </si>
-  <si>
-    <t>11353.78㎡</t>
-  </si>
-  <si>
-    <t>台湾新竹县</t>
-  </si>
-  <si>
-    <t>Hsinchu County, Taiwan, China</t>
-  </si>
-  <si>
-    <t>Fair-facedConcrete, Weathering Steel，Granite，Chinese Fir，Exposed Aggregate</t>
-  </si>
-  <si>
-    <t>办公、商业、展厅、展演、餐饮</t>
-  </si>
-  <si>
-    <t>Office, Commercial, Showroom, Performance Hall, Catering Area</t>
-  </si>
-  <si>
-    <t>新竹县政府</t>
-  </si>
-  <si>
-    <t>Henan Investment Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2023-07-20</t>
-  </si>
-  <si>
-    <t>鹤湖新居微更新</t>
-  </si>
-  <si>
-    <t>2023-07-09</t>
-  </si>
-  <si>
-    <t>海南环岛公路重点驿站酒店</t>
-  </si>
-  <si>
-    <t>Key Resort Inns of Hainan Coastal Ring Road</t>
-  </si>
-  <si>
-    <t>度假驿站酒店</t>
-  </si>
-  <si>
-    <t>Holiday Resort Inn</t>
-  </si>
-  <si>
-    <t>48700㎡</t>
-  </si>
-  <si>
-    <t>海南省东方市板桥镇</t>
-  </si>
-  <si>
-    <t>Banqiao Town, Dongfang City, Hainan Province</t>
-  </si>
-  <si>
-    <t>清水混凝土、蜂窝铝板、玻璃</t>
-  </si>
-  <si>
-    <t>Fair-Faced Concrete, Aluminum Honeycomb Panel, Glass</t>
-  </si>
-  <si>
-    <t>艺术酒店、艺术博物馆、游客中心、国际交流中心</t>
-  </si>
-  <si>
-    <t>Art Hotel, Art Museum, Visitor Center 、International Exchange Center</t>
-  </si>
-  <si>
-    <t>海南省自然资源和规划厅</t>
-  </si>
-  <si>
-    <t>Hainan Provincial Department of Natural Resources and Planning</t>
-  </si>
-  <si>
-    <t>2023-07-07</t>
-  </si>
-  <si>
-    <t>南方新住宅竞赛</t>
-  </si>
-  <si>
-    <t>2023-06-16</t>
-  </si>
-  <si>
-    <t>坪山河景观桥概念方案设计</t>
-  </si>
-  <si>
-    <t>2023-05-21</t>
-  </si>
-  <si>
-    <t>中原制药厂</t>
-  </si>
-  <si>
-    <t>Zhongyuan Pharmaceutical Factory</t>
-  </si>
-  <si>
-    <t>产业园</t>
-  </si>
-  <si>
-    <t>Industrial Park</t>
-  </si>
-  <si>
-    <t>430000㎡</t>
-  </si>
-  <si>
-    <t>郑州市高新区</t>
-  </si>
-  <si>
-    <t>Zhengzhou High Tech Zone</t>
-  </si>
-  <si>
-    <t>清水混凝土、阳极氧化铝板、玻璃、耐候钢</t>
-  </si>
-  <si>
-    <t>Fair-faced Concrete, Anodized Aluminum Panel, Glass, Weathering Steel</t>
-  </si>
-  <si>
-    <t>办公、商业、展厅、会议、生产车间</t>
-  </si>
-  <si>
-    <t>Office，Commercial，Exhibition Hall，Conference，Production Workshop</t>
-  </si>
-  <si>
-    <t>河南投资集团</t>
-  </si>
-  <si>
-    <t>2023-05-03</t>
-  </si>
-  <si>
-    <t>百校焕新项目</t>
-  </si>
-  <si>
-    <t>2023-04-03</t>
-  </si>
-  <si>
-    <t>利元亨南通华东</t>
-  </si>
-  <si>
-    <t>2022-12-20</t>
-  </si>
-  <si>
-    <t>广东嘉速物流工改工项目</t>
-  </si>
-  <si>
-    <t>2022-11-10</t>
-  </si>
-  <si>
-    <t>大江东唐焱厂房BIPV</t>
-  </si>
-  <si>
-    <t>BIPV Project of Tangyan Factory Building, Dadongjiang</t>
-  </si>
-  <si>
-    <t>厂房</t>
-  </si>
-  <si>
-    <t>Factory Building</t>
-  </si>
-  <si>
-    <t>139455㎡</t>
-  </si>
-  <si>
-    <t>浙江省杭州市钱塘区</t>
-  </si>
-  <si>
-    <t>Qiantang District, Hangzhou City, Zhejiang Province, China</t>
-  </si>
-  <si>
-    <t>耐候钢、彩釉玻璃、铝板、碲化镉光伏组件</t>
-  </si>
-  <si>
-    <t>Weathering Steel，Color Glazed Glass，Aluminum Panel，CdTe PV Module</t>
-  </si>
-  <si>
-    <t>厂房、立体车库</t>
-  </si>
-  <si>
-    <t>Factory Building，Stereo Parking Garage</t>
-  </si>
-  <si>
-    <t>焱唐能源科技(杭州)有限责任公司</t>
-  </si>
-  <si>
-    <t>Yantang Energy Technology (Hangzhou) Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2022-05-18</t>
-  </si>
-  <si>
-    <t>大疆顺德智能科技园</t>
-  </si>
-  <si>
-    <t>DJI Shunde Intelligent Science &amp; Technology Park</t>
-  </si>
-  <si>
-    <t>175000㎡</t>
-  </si>
-  <si>
-    <t>佛山市顺德区</t>
-  </si>
-  <si>
-    <t>Shunde District, Foshan City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>胶合木、耐候钢、压型金属板</t>
-  </si>
-  <si>
-    <t>Glulam，Weathering Steel，Profiled Metal Sheet</t>
-  </si>
-  <si>
-    <t>深圳市大疆创新科技有限公司</t>
-  </si>
-  <si>
-    <t>SZ DJI Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
-    <t>老君山瑞玺叶星河酒店</t>
-  </si>
-  <si>
-    <t>Laojun Mountain Ruixi Yexinghe Hotel</t>
-  </si>
-  <si>
-    <t>度假酒店</t>
-  </si>
-  <si>
-    <t>Resort Hotel</t>
-  </si>
-  <si>
-    <t>2800㎡</t>
-  </si>
-  <si>
-    <t>洛阳市栾川县老君山追梦谷</t>
-  </si>
-  <si>
-    <t>Laojun Mountain Dream Valley, Luanchuan County, Luoyang City</t>
-  </si>
-  <si>
-    <t>纯白微水泥、原木、深灰石材、玻璃幕墙</t>
-  </si>
-  <si>
-    <t>Pure White Micro-Cement、Solid Wood、Dark Grey Stone、Glass Curtain Wall</t>
-  </si>
-  <si>
-    <t>别墅观景客房、商务接待、餐饮、艺术长廊</t>
-  </si>
-  <si>
-    <t>Villa Viewing Guest Rooms、Business Reception Area、Catering、Art Corridor</t>
-  </si>
-  <si>
-    <t>洛阳瑞玺叶星河民宿有限公司</t>
-  </si>
-  <si>
-    <t>Luoyang Ruixi Yexinghe Homestay Co., Ltd.</t>
-  </si>
-  <si>
-    <t>嘉荣物流产业园</t>
-  </si>
-  <si>
-    <t>Jiarong Logistics Industrial Park</t>
-  </si>
-  <si>
-    <t>433540㎡</t>
-  </si>
-  <si>
-    <t>东莞市洪梅镇</t>
-  </si>
-  <si>
-    <t>Hongmei Town, Dongguan City</t>
-  </si>
-  <si>
-    <t>清水混凝土、胶合木、 阳极氧化铝板、金属格栅、</t>
-  </si>
-  <si>
-    <t>Fair-Facedconcrete, Glulam，Anodized Aluminum Panel，Metal Grille，</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、宿舍、商业</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Dormitory，Commercial</t>
-  </si>
-  <si>
-    <t>东莞市嘉耀实业投资有限公司</t>
-  </si>
-  <si>
-    <t>Dongguan Jiayao Industrial Investment Co., Ltd.</t>
-  </si>
-  <si>
-    <t>小天才智能科技中心</t>
-  </si>
-  <si>
-    <t>Imoo Intelligent Technology Center</t>
-  </si>
-  <si>
-    <t>Science and Technology Park</t>
-  </si>
-  <si>
-    <t>195560㎡</t>
-  </si>
-  <si>
-    <t>东莞市滨海湾新区</t>
-  </si>
-  <si>
-    <t>Dongguan Binhaiwan New District</t>
-  </si>
-  <si>
-    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃</t>
-  </si>
-  <si>
-    <t>Glulam，Anodized Aluminum Panel，Metal Grille，Glass</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、公寓</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Apartment</t>
-  </si>
-  <si>
-    <t>广东小天才科技有限公司</t>
-  </si>
-  <si>
-    <t>Guangdong Genius Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>生命之树装置深化设计</t>
-  </si>
-  <si>
-    <t>Detail Design of Tree of Life Installation</t>
-  </si>
-  <si>
-    <t>艺术装置</t>
-  </si>
-  <si>
-    <t>Art Installation</t>
-  </si>
-  <si>
-    <t>300㎡</t>
-  </si>
-  <si>
-    <t>重庆市经开区</t>
-  </si>
-  <si>
-    <t>Chongqing Economic and Technological Development Zone</t>
-  </si>
-  <si>
-    <t>胶合木</t>
-  </si>
-  <si>
-    <t>Glulam</t>
-  </si>
-  <si>
-    <t>广阳湾珊瑚小学</t>
-  </si>
-  <si>
-    <t>Guangyang Bay Coral Primary School</t>
-  </si>
-  <si>
-    <t>2021-12-03</t>
-  </si>
-  <si>
-    <t>庐南学校项目</t>
-  </si>
-  <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>菜鸟物流中心</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>鹏峰</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>小米上海汽车总部</t>
-  </si>
-  <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
-    <t>城市展厅</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>华为团泊洼地办公项目</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>欢聚集团总部产业园</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>海阳路学校</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>佛山企业家大厦</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>鹏峰奥迪4s店</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>境工作室汇报</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>万兴科技产业研究中心</t>
-  </si>
-  <si>
-    <t>Wondershare Industrial Research Center</t>
-  </si>
-  <si>
-    <t>119344㎡</t>
-  </si>
-  <si>
-    <t>湖南长沙市</t>
-  </si>
-  <si>
-    <t>Changsha City, Hunan Province</t>
-  </si>
-  <si>
-    <t>研发办公、商业、公寓</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Office，Commercial，Apartment</t>
-  </si>
-  <si>
-    <t>万兴科技集团股份有限公司</t>
-  </si>
-  <si>
-    <t>Wondershare Technology Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2020-09-18</t>
-  </si>
-  <si>
-    <t>李沧项目</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>小天才产业园</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>常州怀德中路项目</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>中联重科智慧产业城</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>佛山绿地彩管大厦</t>
-  </si>
-  <si>
-    <t>Greenland Caiguan Building, Foshan</t>
-  </si>
-  <si>
-    <t>超高层办公楼</t>
-  </si>
-  <si>
-    <t>Super High-rise Office Building</t>
-  </si>
-  <si>
-    <t>261173㎡</t>
-  </si>
-  <si>
-    <t>佛山市禅城区</t>
-  </si>
-  <si>
-    <t>Chancheng District, Foshan</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel，Glass，Perforated Metal Panel</t>
-  </si>
-  <si>
-    <t>办公、酒店、数据中心</t>
-  </si>
-  <si>
-    <t>Office, Hotel，Data Center Complex</t>
-  </si>
-  <si>
-    <t>绿地集团</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
-    <t>广东洲明节能科技有限公司LED生产基地</t>
-  </si>
-  <si>
-    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd. LED Production Base</t>
-  </si>
-  <si>
-    <t>394349㎡</t>
-  </si>
-  <si>
-    <t>惠州市大亚湾区</t>
-  </si>
-  <si>
-    <t>Dayawan District, Huizhou City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、金属格栅、玻璃</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel，Metal Grille，Glass</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、宿舍</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Dormitory</t>
-  </si>
-  <si>
-    <t>广东洲明节能科技有限公司</t>
-  </si>
-  <si>
-    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>PA018276.01中粮祥云•地铁小镇项目商办地块</t>
-  </si>
-  <si>
-    <t>中粮祥云•地铁小镇项目商办地块</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>虹海研发大厦</t>
-  </si>
-  <si>
-    <t>2019-09-29</t>
-  </si>
-  <si>
-    <t>联润大厦项目</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>万达展览馆</t>
-  </si>
-  <si>
-    <t>2019-02-28</t>
-  </si>
-  <si>
-    <t>郑州富士康蔚来云城商业D地块方案</t>
-  </si>
-  <si>
-    <t>2019-02-18</t>
-  </si>
-  <si>
-    <t>许昌信通金融中心项目</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
-    <t>黄山五里山房酒店群</t>
-  </si>
-  <si>
-    <t>Wuli Shanfang Hotel Cluster, Huangshan</t>
-  </si>
-  <si>
-    <t>21500㎡</t>
-  </si>
-  <si>
-    <t>安徽黄山黟县碧阳镇</t>
-  </si>
-  <si>
-    <t>Biyang Town, Yi County, Huangshan City, Anhui Province</t>
-  </si>
-  <si>
-    <t>艺术涂料、金属穿孔铝板、铝镁锰屋面板、青灰瓦</t>
-  </si>
-  <si>
-    <t>Art Coating、Perforated Aluminum Panel、Aluminum-Magnesium-Manganese Roof Panel、Blue-Grey Clay Tile</t>
-  </si>
-  <si>
-    <t>度假别墅客房、商务接待、茶文化展厅、徽文化研学</t>
-  </si>
-  <si>
-    <t>Holiday Villa Guest Rooms, Business Reception Area, Tea Culture Exhibition Hall 、Huizhou Culture Study Base</t>
-  </si>
-  <si>
-    <t>黟县徽黄旅游发展有限公司</t>
-  </si>
-  <si>
-    <t>Yixian Huihuang Tourism Development Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>恒大水世界</t>
-  </si>
-  <si>
-    <t>2018-09-29</t>
-  </si>
-  <si>
-    <t>公司2015-2018作品集</t>
-  </si>
-  <si>
-    <t>2018-09-10</t>
-  </si>
-  <si>
-    <t>崇州7号地块</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>公司装修</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>郑州曲梁863产业园</t>
-  </si>
-  <si>
-    <t>2018-02-11</t>
-  </si>
-  <si>
-    <t>昆仑世纪花园</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>广西巴马酒店综合体项目</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
-    <t>巴马.高端星级酒店综合体</t>
-  </si>
-  <si>
-    <t>Premium Star-rated Hotel Complex in Bama</t>
-  </si>
-  <si>
-    <t>高端度假酒店综合体</t>
-  </si>
-  <si>
-    <t>Premium Holiday Hotel Complex</t>
-  </si>
-  <si>
-    <t>200865㎡</t>
-  </si>
-  <si>
-    <t>巴马瑶族自治县</t>
-  </si>
-  <si>
-    <t>Bama Yao Autonomous County</t>
-  </si>
-  <si>
-    <t>蜂窝铝板、玻璃幕墙、金属格栅</t>
-  </si>
-  <si>
-    <t>Honeycomb Aluminum Panels, Glass Curtain Wall 、 Metal Grilles</t>
-  </si>
-  <si>
-    <t>五星级酒店、高端公寓、瑶族文化体验中心</t>
-  </si>
-  <si>
-    <t>Five-star Hotel, High-end Apartments, Yao Culture Experience Center</t>
-  </si>
-  <si>
-    <t>广西长江天成投资集团</t>
-  </si>
-  <si>
-    <t>Guangxi Yangtze Tessa Investment Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2017-12-05</t>
-  </si>
-  <si>
-    <t>宜宾亿豪酒店</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>甘肃西部中药城</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>福建德化城东中小企业创业园</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>新安区第三工业区康美智慧药房改造项目概念方案</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>康养健康小镇咸宁项目概念性规划设计</t>
-  </si>
-  <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
-    <t>郑州金水</t>
-  </si>
-  <si>
-    <t>2017-05-22</t>
-  </si>
-  <si>
-    <t>广西玉林中药城项目</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>湖南靖州茯苓物流交易中心</t>
-  </si>
-  <si>
-    <t>2017-03-14</t>
-  </si>
-  <si>
-    <t>西宁城西御景华城</t>
-  </si>
-  <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
-    <t>佛山顺德家具厂</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>螺阳镇会所</t>
-  </si>
-  <si>
-    <t>2016-12-19</t>
-  </si>
-  <si>
-    <t>南京K2016-腾旭科技</t>
-  </si>
-  <si>
-    <t>2016-10-26</t>
-  </si>
-  <si>
-    <t>同济工业大厦立面设计</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>广东东明节能科技有限公司LED生产基地项目</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>螺阳镇松星村安置区</t>
-  </si>
-  <si>
-    <t>2016-06-12</t>
-  </si>
-  <si>
-    <t>中国（揭阳）国际珠宝翡翠交易中心项目</t>
-  </si>
-  <si>
-    <t>2016-06-10</t>
-  </si>
-  <si>
-    <t>亲戚房子（谢勇士+高丽+邱四平）</t>
-  </si>
-  <si>
-    <t>2016-05-09</t>
-  </si>
-  <si>
-    <t>中港珠宝旅游商业城</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>富士康企业会所</t>
-  </si>
-  <si>
-    <t>2016-03-30</t>
-  </si>
-  <si>
-    <t>坪山周大生</t>
-  </si>
-  <si>
-    <t>2015-12-21</t>
-  </si>
-  <si>
-    <t>晋江周氏置业项目</t>
-  </si>
-  <si>
-    <t>2015-09-09</t>
-  </si>
-  <si>
-    <t>深圳检验检测认证技术中心建筑设计项目</t>
-  </si>
-  <si>
-    <t>2015-09-01</t>
-  </si>
-  <si>
-    <t>深圳职业技术学院留仙洞校区G栋学生宿舍建设</t>
-  </si>
-  <si>
-    <t>2015-08-13</t>
-  </si>
-  <si>
-    <t>宏发公明售楼处</t>
-  </si>
-  <si>
-    <t>2015-07-14</t>
-  </si>
-  <si>
-    <t>梅林中学扩建学生宿舍楼工程</t>
-  </si>
-  <si>
-    <t>2015-06-01</t>
-  </si>
-  <si>
-    <t>美国云峰商务酒店</t>
-  </si>
-  <si>
-    <t>2015-05-25</t>
-  </si>
-  <si>
-    <t>博林沙井地块项目</t>
-  </si>
-  <si>
-    <t>2015-05-21</t>
-  </si>
-  <si>
-    <t>坪山现代精密办公楼</t>
-  </si>
-  <si>
-    <t>2015-05-08</t>
-  </si>
-  <si>
-    <t>宝投航城工业厂区设计</t>
-  </si>
-  <si>
-    <t>2015-03-12</t>
-  </si>
-  <si>
-    <t>拉斯维加斯雪蛋赌场</t>
-  </si>
-  <si>
-    <t>2015-02-10</t>
-  </si>
-  <si>
-    <t>滇红博物馆</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
-    <t>深圳大鹏较场尾大旅小舍民宿改造</t>
-  </si>
-  <si>
-    <t>Dalv Xiaoshe Homestay Renovation Project, Jiaochangwei, Dapeng New Area, Shenzhen</t>
-  </si>
-  <si>
-    <t>民宿</t>
-  </si>
-  <si>
-    <t>166485㎡</t>
-  </si>
-  <si>
-    <t>2014-09-17</t>
-  </si>
-  <si>
-    <t>博林天瑞花园立面</t>
-  </si>
-  <si>
-    <t>2014-07-30</t>
-  </si>
-  <si>
-    <t>岑溪汇洋新世界</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>龙华简上村（原2011-04-30—部项目）</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>岑溪市思湖广场</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>河北天户峪旅游度假村项目</t>
-  </si>
-  <si>
-    <t>2014-05-20</t>
-  </si>
-  <si>
-    <t>蛇口工业八路南源工业区更新单元改造项目</t>
-  </si>
-  <si>
-    <t>2014-04-02</t>
-  </si>
-  <si>
-    <t>中泰艺术名庭改造</t>
-  </si>
-  <si>
-    <t>2014-03-26</t>
-  </si>
-  <si>
-    <t>深圳湾“超级城市”国际竞赛</t>
-  </si>
-  <si>
-    <t>2013-12-29</t>
-  </si>
-  <si>
-    <t>博林海德城</t>
-  </si>
-  <si>
-    <t>2013-12-24</t>
-  </si>
-  <si>
-    <t>广东喜之郎集团总部大厦</t>
-  </si>
-  <si>
-    <t>2013-11-25</t>
-  </si>
-  <si>
-    <t>南京明发</t>
-  </si>
-  <si>
-    <t>2013-10-10</t>
-  </si>
-  <si>
-    <t>宝安机场城市更新项目</t>
-  </si>
-  <si>
-    <t>2013-09-18</t>
-  </si>
-  <si>
-    <t>城市复兴</t>
-  </si>
-  <si>
-    <t>2013-09-13</t>
-  </si>
-  <si>
-    <t>宝安机场口岸综合楼项目</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>华润深圳湾综合发展项目北区住宅竞赛</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>老挝茶文化体验中心</t>
-  </si>
-  <si>
-    <t>2013-02-13</t>
-  </si>
-  <si>
-    <t>武汉大学艺术楼</t>
-  </si>
-  <si>
-    <t>Fine Arts Building, Wuhan University</t>
-  </si>
-  <si>
-    <t>文教</t>
-  </si>
-  <si>
-    <t>Culture &amp; Education</t>
-  </si>
-  <si>
-    <t>5371㎡</t>
-  </si>
-  <si>
-    <t>湖北武汉市</t>
-  </si>
-  <si>
-    <t>Wuhan City, Hubei Province</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、玻璃</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel， Glass</t>
-  </si>
-  <si>
-    <t>教室，图书室，音乐厅、会议</t>
-  </si>
-  <si>
-    <t>Classroom, Library, Concert Hall ， Conference Space</t>
-  </si>
-  <si>
-    <t>武汉大学</t>
-  </si>
-  <si>
-    <t>Wuhan University</t>
-  </si>
-  <si>
-    <t>2013-01-01</t>
-  </si>
-  <si>
-    <t>老挝万象茶文化中心</t>
-  </si>
-  <si>
-    <t>Vientiane Tea Culture Center, Laos</t>
-  </si>
-  <si>
-    <t>3200㎡</t>
-  </si>
-  <si>
-    <t>老挝万象市</t>
-  </si>
-  <si>
-    <t>Vientiane Municipality, Laos</t>
-  </si>
-  <si>
-    <t>清水混凝土、胶合木、金属格栅、</t>
-  </si>
-  <si>
-    <t>Fair-Facedconcrete, Glulam， Metal Grille</t>
-  </si>
-  <si>
-    <t>办公、展厅、会所、宿舍</t>
-  </si>
-  <si>
-    <t>Office，Showroom，Club House，Dormitory</t>
-  </si>
-  <si>
-    <t>2012-12-25</t>
-  </si>
-  <si>
-    <t>华润惠州小径湾滨海度假村2期</t>
-  </si>
-  <si>
-    <t>China Resources Park Lane Harbour Coastal Resort Phase 2, Huizhou</t>
-  </si>
-  <si>
-    <t>居住</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>贵阳玉蝶</t>
-  </si>
-  <si>
-    <t>2012-07-14</t>
-  </si>
-  <si>
-    <t>南京文化中心</t>
-  </si>
-  <si>
-    <t>2012-04-10</t>
-  </si>
-  <si>
-    <t>Foshan Entrepreneur Building</t>
-  </si>
-  <si>
-    <t>157553㎡</t>
-  </si>
-  <si>
-    <t>广东佛山市</t>
-  </si>
-  <si>
-    <t>Foshan City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>办公、酒店、会议，商业</t>
-  </si>
-  <si>
-    <t>Office, Hotel, Conference ， Commercial</t>
-  </si>
-  <si>
-    <t>佛山企业家联合体</t>
-  </si>
-  <si>
-    <t>Foshan Entrepreneurs Federation</t>
-  </si>
-  <si>
-    <t>2011-11-06</t>
-  </si>
-  <si>
-    <t>上海杨浦智创天地-w</t>
-  </si>
-  <si>
-    <t>2011-09-05</t>
-  </si>
-  <si>
-    <t>淄博文化中心</t>
-  </si>
-  <si>
-    <t>2011-07-08</t>
-  </si>
-  <si>
-    <t>港珠澳大桥珠海口岸规划国际竞赛</t>
-  </si>
-  <si>
-    <t>International Planning Competition, Zhuhai Port of HZMB</t>
-  </si>
-  <si>
-    <t>交通枢纽</t>
-  </si>
-  <si>
-    <t>Transport Hub（</t>
-  </si>
-  <si>
-    <t>586152m2</t>
-  </si>
-  <si>
-    <t>广东珠海市</t>
-  </si>
-  <si>
-    <t>Zhuhai City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>海关口岸，办公，商业</t>
-  </si>
-  <si>
-    <t>Customs Port, Office ， Commercial Facilities</t>
-  </si>
-  <si>
-    <t>珠海市港珠澳大桥建设协调办公室</t>
-  </si>
-  <si>
-    <t>Zhuhai HZMB Construction Coordination Office</t>
-  </si>
-  <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
-    <t>世界自然基金会汉中游客信息中心</t>
-  </si>
-  <si>
-    <t>WWF Hanzhong Visitor Information Centre</t>
-  </si>
-  <si>
-    <t>Cultural &amp; Tourism</t>
-  </si>
-  <si>
-    <t>332㎡</t>
-  </si>
-  <si>
-    <t>陕西汉中市</t>
-  </si>
-  <si>
-    <t>Hanzhong City, Shaanxi Province</t>
-  </si>
-  <si>
-    <t>胶合木、冷弯薄壁型钢</t>
-  </si>
-  <si>
-    <t>Glulam，Cold-Formed Thin-Wall Steel</t>
-  </si>
-  <si>
-    <t>展厅、接待、办公</t>
-  </si>
-  <si>
-    <t>Showroom, Reception ， Office</t>
-  </si>
-  <si>
-    <t>WWF世界自然基金会</t>
-  </si>
-  <si>
-    <t>WWF – World Wide Fund for Nature</t>
-  </si>
-  <si>
-    <t>2010-12-04</t>
-  </si>
-  <si>
-    <t>淄博大剧院</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
-    <t>四川里坪村小学校</t>
-  </si>
-  <si>
-    <t>Liping Village Primary School, Sichuan</t>
-  </si>
-  <si>
-    <t>学校</t>
-  </si>
-  <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>201㎡</t>
-  </si>
-  <si>
-    <t>四川青川县</t>
-  </si>
-  <si>
-    <t>Qingchuan, Sichuan</t>
-  </si>
-  <si>
-    <t>生土、原木</t>
-  </si>
-  <si>
-    <t>Raw Earth，Log</t>
-  </si>
-  <si>
-    <t>2022-05-28</t>
-  </si>
-  <si>
-    <t>新丰项目阶段性成果整理</t>
-  </si>
-  <si>
-    <t>2022-01-06</t>
-  </si>
-  <si>
-    <t>新丰美食街</t>
-  </si>
-  <si>
-    <t>新丰菜市场改造</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>规划局环保局办公楼</t>
-  </si>
-  <si>
-    <t>2020-09-06</t>
-  </si>
-  <si>
-    <t>垃圾站+厕所</t>
-  </si>
-  <si>
-    <t>2020-06-27</t>
-  </si>
-  <si>
-    <t>黄局自宅</t>
-  </si>
-  <si>
-    <t>2020-06-09</t>
-  </si>
-  <si>
-    <t>黄寨景观</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>遥田图书馆</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>方志馆档案馆</t>
-  </si>
-  <si>
-    <t>2019-10-12</t>
-  </si>
-  <si>
-    <t>新丰文化中心</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>新丰廉租房项目</t>
-  </si>
-  <si>
-    <t>2019-02-19</t>
-  </si>
-  <si>
-    <t>新丰黄磜镇幸福公社</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>新丰规划局涵洞改造</t>
-  </si>
-  <si>
-    <t>2018-10-10</t>
-  </si>
-  <si>
-    <t>新丰气象站</t>
-  </si>
-  <si>
-    <t>2018-07-31</t>
-  </si>
-  <si>
-    <t>新丰城市厕所项目</t>
-  </si>
-  <si>
-    <t>2018-07-09</t>
-  </si>
-  <si>
-    <t>新丰村委会改造</t>
-  </si>
-  <si>
-    <t>2017-04-17</t>
-  </si>
-  <si>
-    <t>新丰老一中改造</t>
-  </si>
-  <si>
-    <t>外墙漆、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>农村自建房别墅景观设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>农村自建房别墅设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东、陆丰陂洋莲花寨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>湖北，洪湖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>外墙漆、玻璃、铝板</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>居住</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>376㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱建新</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>惠州24时辰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4200㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>驿站</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>惠州、惠东县、稔平半岛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、耐候钢、花岗石、杉木、洗石子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐候钢、彩釉玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李松蓢项目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>316574㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>驿站设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高品质生活居住区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳市、光明区、公明街道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>香槟金铝板、真石漆、莱姆石，玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳市公明李松蓢股份合作公司     深圳市特发鸿顺实业有限公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>居住、商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柬埔寨、西港云壤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、耐候钢、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>打位区、售楼处、办公</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1840,7 +2009,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1855,6 +2024,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1915,7 +2090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1949,6 +2124,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2277,13 +2458,13 @@
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="12" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.9140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="30" style="2" customWidth="1"/>
     <col min="11" max="11" width="36" style="2" customWidth="1"/>
-    <col min="12" max="12" width="34" style="2" customWidth="1"/>
+    <col min="12" max="12" width="37.83203125" style="2" customWidth="1"/>
     <col min="13" max="13" width="40" style="2" customWidth="1"/>
-    <col min="14" max="14" width="26" style="2" customWidth="1"/>
+    <col min="14" max="14" width="31.83203125" style="2" customWidth="1"/>
     <col min="15" max="15" width="32" style="2" customWidth="1"/>
     <col min="16" max="16" width="30" style="2" customWidth="1"/>
     <col min="17" max="17" width="34" style="2" customWidth="1"/>
@@ -2343,43 +2524,43 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="34" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="9">
+      <c r="E2" s="12"/>
+      <c r="F2" s="13">
         <v>46370</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
+      <c r="G2" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:17" ht="34" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -2390,7 +2571,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="9">
@@ -2400,23 +2581,23 @@
         <v>517.96</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="Q3" s="3"/>
     </row>
@@ -2425,7 +2606,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
@@ -2436,25 +2617,27 @@
         <v>46152</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="O4" s="5"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="11" t="s">
+        <v>572</v>
+      </c>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17" ht="34" customHeight="1">
@@ -2462,37 +2645,37 @@
         <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
         <v>2026</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="11" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="Q5" s="3"/>
     </row>
@@ -2504,19 +2687,33 @@
         <v>28</v>
       </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>570</v>
+      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="10">
+        <v>46252</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>574</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>575</v>
+      </c>
       <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+      <c r="N6" s="5" t="s">
+        <v>576</v>
+      </c>
       <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="P6" s="5" t="s">
+        <v>577</v>
+      </c>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" ht="34" customHeight="1">
@@ -2527,17 +2724,25 @@
         <v>30</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>578</v>
+      </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="9">
+        <v>46009</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3" t="s">
+        <v>579</v>
+      </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="N7" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -2550,19 +2755,35 @@
         <v>32</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>581</v>
+      </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="F8" s="10">
+        <v>46090</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>583</v>
+      </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>584</v>
+      </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>588</v>
+      </c>
       <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="N8" s="5" t="s">
+        <v>581</v>
+      </c>
       <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="5" t="s">
+        <v>589</v>
+      </c>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" ht="34" customHeight="1">
@@ -2570,79 +2791,95 @@
         <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>619</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>618</v>
+      </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="F9" s="9">
+        <v>45889</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>617</v>
+      </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>620</v>
+      </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3" t="s">
+        <v>621</v>
+      </c>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="N9" s="3" t="s">
+        <v>622</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:17" ht="34" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="10">
+        <v>46147</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="5">
-        <v>2025</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>601</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="34" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -2662,58 +2899,88 @@
     </row>
     <row r="12" spans="1:17" ht="34" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="D12" s="5" t="s">
+        <v>590</v>
+      </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="F12" s="5">
+        <v>2026</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>591</v>
+      </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>593</v>
+      </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="5" t="s">
+        <v>598</v>
+      </c>
       <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
+      <c r="N12" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="P12" s="5" t="s">
+        <v>600</v>
+      </c>
       <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17" ht="34" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>578</v>
+      </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="F13" s="3">
+        <v>2026</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>575</v>
+      </c>
       <c r="M13" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="N13" s="3"/>
+        <v>569</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>603</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
     <row r="14" spans="1:17" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -2733,33 +3000,49 @@
     </row>
     <row r="15" spans="1:17" ht="34" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>614</v>
       </c>
       <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="F15" s="10">
+        <v>45559</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>608</v>
+      </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="5" t="s">
+        <v>612</v>
+      </c>
       <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>615</v>
+      </c>
       <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="P15" s="5" t="s">
+        <v>613</v>
+      </c>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -2779,59 +3062,59 @@
     </row>
     <row r="17" spans="1:17" ht="34" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="F17" s="5">
         <v>2024</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="O17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="P17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -2851,10 +3134,10 @@
     </row>
     <row r="19" spans="1:17" ht="34" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -2874,10 +3157,10 @@
     </row>
     <row r="20" spans="1:17" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2897,10 +3180,10 @@
     </row>
     <row r="21" spans="1:17" ht="34" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2920,10 +3203,10 @@
     </row>
     <row r="22" spans="1:17" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -2943,10 +3226,10 @@
     </row>
     <row r="23" spans="1:17" ht="34" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -2966,59 +3249,59 @@
     </row>
     <row r="24" spans="1:17" ht="34" customHeight="1">
       <c r="A24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="F24" s="5">
         <v>2024</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="O24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="P24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="Q24" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="34" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -3038,59 +3321,59 @@
     </row>
     <row r="26" spans="1:17" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="F26" s="3">
         <v>2025</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="P26" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="M26" s="3" t="s">
+      <c r="Q26" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="34" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3110,59 +3393,59 @@
     </row>
     <row r="28" spans="1:17" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="F28" s="3">
         <v>2023</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="34" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3182,10 +3465,10 @@
     </row>
     <row r="30" spans="1:17" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -3205,59 +3488,59 @@
     </row>
     <row r="31" spans="1:17" ht="34" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F31" s="5">
         <v>2023</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P31" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="Q31" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -3277,10 +3560,10 @@
     </row>
     <row r="33" spans="1:17" ht="34" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3300,10 +3583,10 @@
     </row>
     <row r="34" spans="1:17" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -3323,304 +3606,304 @@
     </row>
     <row r="35" spans="1:17" ht="34" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F35" s="5">
         <v>2025</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="P35" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="Q35" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F36" s="3">
         <v>2022</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>174</v>
+        <v>575</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="34" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F37" s="3">
         <v>2022</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>186</v>
+        <v>596</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="34" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F38" s="5">
         <v>2022</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>197</v>
+        <v>597</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="34" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F39" s="3">
         <v>2022</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="34" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F40" s="5">
         <v>2022</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="34" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3640,10 +3923,10 @@
     </row>
     <row r="42" spans="1:17" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -3663,10 +3946,10 @@
     </row>
     <row r="43" spans="1:17" ht="34" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -3686,10 +3969,10 @@
     </row>
     <row r="44" spans="1:17" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -3709,10 +3992,10 @@
     </row>
     <row r="45" spans="1:17" ht="34" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -3732,10 +4015,10 @@
     </row>
     <row r="46" spans="1:17" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -3755,10 +4038,10 @@
     </row>
     <row r="47" spans="1:17" ht="34" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -3778,10 +4061,10 @@
     </row>
     <row r="48" spans="1:17" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -3801,10 +4084,10 @@
     </row>
     <row r="49" spans="1:17" ht="34" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -3824,10 +4107,10 @@
     </row>
     <row r="50" spans="1:17" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -3847,10 +4130,10 @@
     </row>
     <row r="51" spans="1:17" ht="34" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -3870,59 +4153,59 @@
     </row>
     <row r="52" spans="1:17" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F52" s="3">
         <v>2021</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="34" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -3942,10 +4225,10 @@
     </row>
     <row r="54" spans="1:17" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -3965,10 +4248,10 @@
     </row>
     <row r="55" spans="1:17" ht="34" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -3988,10 +4271,10 @@
     </row>
     <row r="56" spans="1:17" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -4011,108 +4294,108 @@
     </row>
     <row r="57" spans="1:17" ht="34" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F57" s="5">
         <v>2022</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L57" s="5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="N57" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="P57" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="Q57" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F58" s="3">
         <v>2020</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="34" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -4132,10 +4415,10 @@
     </row>
     <row r="60" spans="1:17" ht="34" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -4155,10 +4438,10 @@
     </row>
     <row r="61" spans="1:17" ht="34" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -4178,10 +4461,10 @@
     </row>
     <row r="62" spans="1:17" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -4201,10 +4484,10 @@
     </row>
     <row r="63" spans="1:17" ht="34" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -4224,10 +4507,10 @@
     </row>
     <row r="64" spans="1:17" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -4247,10 +4530,10 @@
     </row>
     <row r="65" spans="1:17" ht="34" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -4270,59 +4553,59 @@
     </row>
     <row r="66" spans="1:17" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F66" s="3">
         <v>2019</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="34" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -4342,10 +4625,10 @@
     </row>
     <row r="68" spans="1:17" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -4365,10 +4648,10 @@
     </row>
     <row r="69" spans="1:17" ht="34" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -4388,10 +4671,10 @@
     </row>
     <row r="70" spans="1:17" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -4411,10 +4694,10 @@
     </row>
     <row r="71" spans="1:17" ht="34" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -4434,10 +4717,10 @@
     </row>
     <row r="72" spans="1:17" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -4457,10 +4740,10 @@
     </row>
     <row r="73" spans="1:17" ht="34" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -4480,59 +4763,59 @@
     </row>
     <row r="74" spans="1:17" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F74" s="3">
         <v>2018</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="34" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -4552,10 +4835,10 @@
     </row>
     <row r="76" spans="1:17" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -4575,10 +4858,10 @@
     </row>
     <row r="77" spans="1:17" ht="34" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -4598,10 +4881,10 @@
     </row>
     <row r="78" spans="1:17" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
@@ -4621,10 +4904,10 @@
     </row>
     <row r="79" spans="1:17" ht="34" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -4644,10 +4927,10 @@
     </row>
     <row r="80" spans="1:17" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -4667,10 +4950,10 @@
     </row>
     <row r="81" spans="1:17" ht="34" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -4690,10 +4973,10 @@
     </row>
     <row r="82" spans="1:17" ht="34" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -4713,10 +4996,10 @@
     </row>
     <row r="83" spans="1:17" ht="34" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -4736,10 +5019,10 @@
     </row>
     <row r="84" spans="1:17" ht="34" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -4759,10 +5042,10 @@
     </row>
     <row r="85" spans="1:17" ht="34" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -4782,10 +5065,10 @@
     </row>
     <row r="86" spans="1:17" ht="34" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -4805,10 +5088,10 @@
     </row>
     <row r="87" spans="1:17" ht="34" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -4828,10 +5111,10 @@
     </row>
     <row r="88" spans="1:17" ht="34" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -4851,10 +5134,10 @@
     </row>
     <row r="89" spans="1:17" ht="34" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -4874,10 +5157,10 @@
     </row>
     <row r="90" spans="1:17" ht="34" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -4897,10 +5180,10 @@
     </row>
     <row r="91" spans="1:17" ht="34" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -4920,10 +5203,10 @@
     </row>
     <row r="92" spans="1:17" ht="34" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -4943,10 +5226,10 @@
     </row>
     <row r="93" spans="1:17" ht="34" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -4966,10 +5249,10 @@
     </row>
     <row r="94" spans="1:17" ht="34" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
@@ -4989,10 +5272,10 @@
     </row>
     <row r="95" spans="1:17" ht="34" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -5012,10 +5295,10 @@
     </row>
     <row r="96" spans="1:17" ht="34" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
@@ -5035,10 +5318,10 @@
     </row>
     <row r="97" spans="1:17" ht="34" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -5058,10 +5341,10 @@
     </row>
     <row r="98" spans="1:17" ht="34" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -5081,10 +5364,10 @@
     </row>
     <row r="99" spans="1:17" ht="34" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -5104,10 +5387,10 @@
     </row>
     <row r="100" spans="1:17" ht="34" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -5127,10 +5410,10 @@
     </row>
     <row r="101" spans="1:17" ht="34" customHeight="1">
       <c r="A101" s="5" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -5150,10 +5433,10 @@
     </row>
     <row r="102" spans="1:17" ht="34" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -5173,10 +5456,10 @@
     </row>
     <row r="103" spans="1:17" ht="34" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -5196,10 +5479,10 @@
     </row>
     <row r="104" spans="1:17" ht="34" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -5219,10 +5502,10 @@
     </row>
     <row r="105" spans="1:17" ht="34" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -5242,59 +5525,59 @@
     </row>
     <row r="106" spans="1:17" ht="34" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F106" s="3">
         <v>2015</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="P106" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="34" customHeight="1">
       <c r="A107" s="5" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
@@ -5314,10 +5597,10 @@
     </row>
     <row r="108" spans="1:17" ht="34" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -5337,10 +5620,10 @@
     </row>
     <row r="109" spans="1:17" ht="34" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -5360,10 +5643,10 @@
     </row>
     <row r="110" spans="1:17" ht="34" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -5383,10 +5666,10 @@
     </row>
     <row r="111" spans="1:17" ht="34" customHeight="1">
       <c r="A111" s="5" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -5406,10 +5689,10 @@
     </row>
     <row r="112" spans="1:17" ht="34" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -5429,10 +5712,10 @@
     </row>
     <row r="113" spans="1:17" ht="34" customHeight="1">
       <c r="A113" s="5" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -5452,10 +5735,10 @@
     </row>
     <row r="114" spans="1:17" ht="34" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
@@ -5475,10 +5758,10 @@
     </row>
     <row r="115" spans="1:17" ht="34" customHeight="1">
       <c r="A115" s="5" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -5498,10 +5781,10 @@
     </row>
     <row r="116" spans="1:17" ht="34" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -5521,10 +5804,10 @@
     </row>
     <row r="117" spans="1:17" ht="34" customHeight="1">
       <c r="A117" s="5" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -5544,10 +5827,10 @@
     </row>
     <row r="118" spans="1:17" ht="34" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -5567,10 +5850,10 @@
     </row>
     <row r="119" spans="1:17" ht="34" customHeight="1">
       <c r="A119" s="5" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
@@ -5590,10 +5873,10 @@
     </row>
     <row r="120" spans="1:17" ht="34" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -5613,10 +5896,10 @@
     </row>
     <row r="121" spans="1:17" ht="34" customHeight="1">
       <c r="A121" s="5" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
@@ -5636,10 +5919,10 @@
     </row>
     <row r="122" spans="1:17" ht="34" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
@@ -5659,153 +5942,153 @@
     </row>
     <row r="123" spans="1:17" ht="34" customHeight="1">
       <c r="A123" s="5" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="F123" s="6">
         <v>2013</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="L123" s="5" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="N123" s="5" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="O123" s="5" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="P123" s="5" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="Q123" s="5" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="34" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F124" s="4">
         <v>2013</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
     </row>
     <row r="125" spans="1:17" ht="34" customHeight="1">
       <c r="A125" s="5" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F125" s="6">
         <v>2012</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="L125" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N125" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O125" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="P125" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="Q125" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="34" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
@@ -5825,10 +6108,10 @@
     </row>
     <row r="127" spans="1:17" ht="34" customHeight="1">
       <c r="A127" s="5" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
@@ -5848,59 +6131,59 @@
     </row>
     <row r="128" spans="1:17" ht="34" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F128" s="4">
         <v>2013</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="34" customHeight="1">
       <c r="A129" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
@@ -5920,10 +6203,10 @@
     </row>
     <row r="130" spans="1:17" ht="34" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
@@ -5943,108 +6226,108 @@
     </row>
     <row r="131" spans="1:17" ht="34" customHeight="1">
       <c r="A131" s="5" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="F131" s="6">
         <v>2011</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="K131" s="5" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="L131" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N131" s="5" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="P131" s="5" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="Q131" s="5" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="34" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F132" s="4">
         <v>2011</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="P132" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="Q132" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="34" customHeight="1">
       <c r="A133" s="5" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
@@ -6064,55 +6347,55 @@
     </row>
     <row r="134" spans="1:17" ht="34" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="F134" s="4">
         <v>2009</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="P134" s="3"/>
       <c r="Q134" s="3"/>
     </row>
     <row r="135" spans="1:17" ht="34" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -6132,10 +6415,10 @@
     </row>
     <row r="136" spans="1:17" ht="34" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
@@ -6155,10 +6438,10 @@
     </row>
     <row r="137" spans="1:17" ht="34" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -6178,10 +6461,10 @@
     </row>
     <row r="138" spans="1:17" ht="34" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
@@ -6201,10 +6484,10 @@
     </row>
     <row r="139" spans="1:17" ht="34" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -6224,10 +6507,10 @@
     </row>
     <row r="140" spans="1:17" ht="34" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
@@ -6247,10 +6530,10 @@
     </row>
     <row r="141" spans="1:17" ht="34" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -6270,10 +6553,10 @@
     </row>
     <row r="142" spans="1:17" ht="34" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
@@ -6293,10 +6576,10 @@
     </row>
     <row r="143" spans="1:17" ht="34" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -6316,10 +6599,10 @@
     </row>
     <row r="144" spans="1:17" ht="34" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
@@ -6339,10 +6622,10 @@
     </row>
     <row r="145" spans="1:17" ht="34" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -6362,10 +6645,10 @@
     </row>
     <row r="146" spans="1:17" ht="34" customHeight="1">
       <c r="A146" s="8" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
@@ -6385,10 +6668,10 @@
     </row>
     <row r="147" spans="1:17" ht="34" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -6408,10 +6691,10 @@
     </row>
     <row r="148" spans="1:17" ht="34" customHeight="1">
       <c r="A148" s="8" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
@@ -6431,10 +6714,10 @@
     </row>
     <row r="149" spans="1:17" ht="34" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -6454,10 +6737,10 @@
     </row>
     <row r="150" spans="1:17" ht="34" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
@@ -6477,10 +6760,10 @@
     </row>
     <row r="151" spans="1:17" ht="34" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>

--- a/src/content/info/案例指标信息.xlsx
+++ b/src/content/info/案例指标信息.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\L\d\03-开合\OpenLink\src\content\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5452B9B8-E6E8-43CE-BE37-E6268D59F53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D005BE71-B4F2-4B39-99A4-509988444DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="683">
   <si>
     <t>时间（date）</t>
   </si>
@@ -85,1886 +85,2130 @@
     <t>住宅</t>
   </si>
   <si>
+    <t>袁小海</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>邱宅</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>文旅</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>装配式居住单元</t>
+  </si>
+  <si>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>台湾教堂</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>南星厂房</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>深圳南园街道立面改造</t>
+  </si>
+  <si>
+    <t>Facade Renovation Project of Nanyuan Subdistrict, Shenzhen</t>
+  </si>
+  <si>
+    <t>城市更新</t>
+  </si>
+  <si>
+    <t>Urban Renewal</t>
+  </si>
+  <si>
+    <t>3500㎡</t>
+  </si>
+  <si>
+    <t>深圳南园路</t>
+  </si>
+  <si>
+    <t>Nanyuan Rd, Shenzhen</t>
+  </si>
+  <si>
+    <t>Real Stone Coating, Exterior Wall Paint, Silicone LED Strip Lights</t>
+  </si>
+  <si>
+    <t>住宅、商业</t>
+  </si>
+  <si>
+    <t>Residential，Commercial</t>
+  </si>
+  <si>
+    <t>深圳市南园街道办</t>
+  </si>
+  <si>
+    <t>Nanyuan Subdistrict Office, Futian District, Shenzhen</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>妈湾3座桥</t>
+  </si>
+  <si>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>新疆轩润晟非物质文化遗产科技艺术产业园</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>谢老师 观音寺项目</t>
+  </si>
+  <si>
+    <t>2024-10-14</t>
+  </si>
+  <si>
+    <t>妈湾城市艺术装置</t>
+  </si>
+  <si>
+    <t>2024-09-06</t>
+  </si>
+  <si>
+    <t>2024-06-18</t>
+  </si>
+  <si>
+    <t>后海小学初步设计</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>宁夏国药温泉康养小镇</t>
+  </si>
+  <si>
+    <t>Ningxia Sinopharm Hot Spring Wellness Town</t>
+  </si>
+  <si>
+    <t>酒店</t>
+  </si>
+  <si>
+    <t>Hot Spring Resort Hotel</t>
+  </si>
+  <si>
+    <t>150600㎡</t>
+  </si>
+  <si>
+    <t>宁夏固原市泾源县</t>
+  </si>
+  <si>
+    <t>Jingyuan County, Guyuan City, Ningxia Hui Autonomous Region</t>
+  </si>
+  <si>
+    <t>Honeycomb aluminum panels, solid wood,  glass curtain wall</t>
+  </si>
+  <si>
+    <t>温泉别墅、温泉酒店、高端民宿</t>
+  </si>
+  <si>
+    <t>Hot Spring Villas, Hot Spring Hotel, High-end Homestays</t>
+  </si>
+  <si>
+    <t>中国医药集团有限公司</t>
+  </si>
+  <si>
+    <t>China National Pharmaceutical Group Corporation</t>
+  </si>
+  <si>
+    <t>2024-02-22</t>
+  </si>
+  <si>
+    <t>吕洞山景区游客服务中心设计</t>
+  </si>
+  <si>
+    <t>2024-01-03</t>
+  </si>
+  <si>
+    <t>东莞滨海文化区方案设计国际竞赛</t>
+  </si>
+  <si>
+    <t>2023-12-13</t>
+  </si>
+  <si>
+    <t>武夷山茶庄园项目概念规划</t>
+  </si>
+  <si>
+    <t>2023-11-30</t>
+  </si>
+  <si>
+    <t>珠海市（第四批）历史建筑数字化建档</t>
+  </si>
+  <si>
+    <t>2023-11-06</t>
+  </si>
+  <si>
+    <t>2023-11-01</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>河南信阳车云山茶文化民宿</t>
+  </si>
+  <si>
+    <t>Cheyun Mountain Tea Culture Homestay, Xinyang, Henan Province</t>
+  </si>
+  <si>
+    <t>度假民宿</t>
+  </si>
+  <si>
+    <t>Vacation Homestay</t>
+  </si>
+  <si>
+    <t>3900㎡</t>
+  </si>
+  <si>
+    <t>信阳市董家河车云山</t>
+  </si>
+  <si>
+    <t>Cheyun Mountain, Dongjiahe, Xinyang City, Henan Province</t>
+  </si>
+  <si>
+    <t>原木、铝镁锰屋面板、玻璃幕墙</t>
+  </si>
+  <si>
+    <t>Honeycomb aluminum panels、solid wood、glass curtain wall</t>
+  </si>
+  <si>
+    <t>度假民宿、接待、展厅</t>
+  </si>
+  <si>
+    <t>Vacation Homestay，Reception，Showroom</t>
+  </si>
+  <si>
+    <t>河南省住建厅</t>
+  </si>
+  <si>
+    <t>Department of Housing and Urban-Rural Development of Henan Province</t>
+  </si>
+  <si>
+    <t>五里山房</t>
+  </si>
+  <si>
+    <t>2023-08-29</t>
+  </si>
+  <si>
+    <t>台湾新竹县竹东客家文化大合埕</t>
+  </si>
+  <si>
+    <t>Dahecheng of Hakka Culture, Zhudong, Hsinchu County, Taiwan</t>
+  </si>
+  <si>
+    <t>文化建筑</t>
+  </si>
+  <si>
+    <t>Cultural Building</t>
+  </si>
+  <si>
+    <t>11353.78㎡</t>
+  </si>
+  <si>
+    <t>台湾新竹县</t>
+  </si>
+  <si>
+    <t>Hsinchu County, Taiwan, China</t>
+  </si>
+  <si>
+    <t>Fair-facedConcrete, Weathering Steel，Granite，Chinese Fir，Exposed Aggregate</t>
+  </si>
+  <si>
+    <t>办公、商业、展厅、展演、餐饮</t>
+  </si>
+  <si>
+    <t>Office, Commercial, Showroom, Performance Hall, Catering Area</t>
+  </si>
+  <si>
+    <t>新竹县政府</t>
+  </si>
+  <si>
+    <t>Henan Investment Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2023-07-20</t>
+  </si>
+  <si>
+    <t>鹤湖新居微更新</t>
+  </si>
+  <si>
+    <t>2023-07-09</t>
+  </si>
+  <si>
+    <t>海南环岛公路重点驿站酒店</t>
+  </si>
+  <si>
+    <t>Key Resort Inns of Hainan Coastal Ring Road</t>
+  </si>
+  <si>
+    <t>度假驿站酒店</t>
+  </si>
+  <si>
+    <t>Holiday Resort Inn</t>
+  </si>
+  <si>
+    <t>48700㎡</t>
+  </si>
+  <si>
+    <t>海南省东方市板桥镇</t>
+  </si>
+  <si>
+    <t>Banqiao Town, Dongfang City, Hainan Province</t>
+  </si>
+  <si>
+    <t>Fair-Faced Concrete, Aluminum Honeycomb Panel, Glass</t>
+  </si>
+  <si>
+    <t>艺术酒店、艺术博物馆、游客中心、国际交流中心</t>
+  </si>
+  <si>
+    <t>Art Hotel, Art Museum, Visitor Center 、International Exchange Center</t>
+  </si>
+  <si>
+    <t>海南省自然资源和规划厅</t>
+  </si>
+  <si>
+    <t>Hainan Provincial Department of Natural Resources and Planning</t>
+  </si>
+  <si>
+    <t>2023-07-07</t>
+  </si>
+  <si>
+    <t>南方新住宅竞赛</t>
+  </si>
+  <si>
+    <t>2023-06-16</t>
+  </si>
+  <si>
+    <t>坪山河景观桥概念方案设计</t>
+  </si>
+  <si>
+    <t>2023-05-21</t>
+  </si>
+  <si>
+    <t>中原制药厂</t>
+  </si>
+  <si>
+    <t>Zhongyuan Pharmaceutical Factory</t>
+  </si>
+  <si>
+    <t>产业园</t>
+  </si>
+  <si>
+    <t>Industrial Park</t>
+  </si>
+  <si>
+    <t>430000㎡</t>
+  </si>
+  <si>
+    <t>郑州市高新区</t>
+  </si>
+  <si>
+    <t>Zhengzhou High Tech Zone</t>
+  </si>
+  <si>
+    <t>Fair-faced Concrete, Anodized Aluminum Panel, Glass, Weathering Steel</t>
+  </si>
+  <si>
+    <t>办公、商业、展厅、会议、生产车间</t>
+  </si>
+  <si>
+    <t>Office，Commercial，Exhibition Hall，Conference，Production Workshop</t>
+  </si>
+  <si>
+    <t>河南投资集团</t>
+  </si>
+  <si>
+    <t>2023-05-03</t>
+  </si>
+  <si>
+    <t>百校焕新项目</t>
+  </si>
+  <si>
+    <t>2023-04-03</t>
+  </si>
+  <si>
+    <t>利元亨南通华东</t>
+  </si>
+  <si>
+    <t>2022-12-20</t>
+  </si>
+  <si>
+    <t>广东嘉速物流工改工项目</t>
+  </si>
+  <si>
+    <t>2022-11-10</t>
+  </si>
+  <si>
+    <t>大江东唐焱厂房BIPV</t>
+  </si>
+  <si>
+    <t>BIPV Project of Tangyan Factory Building, Dadongjiang</t>
+  </si>
+  <si>
+    <t>厂房</t>
+  </si>
+  <si>
+    <t>Factory Building</t>
+  </si>
+  <si>
+    <t>139455㎡</t>
+  </si>
+  <si>
+    <t>浙江省杭州市钱塘区</t>
+  </si>
+  <si>
+    <t>Qiantang District, Hangzhou City, Zhejiang Province, China</t>
+  </si>
+  <si>
+    <t>耐候钢、彩釉玻璃、铝板、碲化镉光伏组件</t>
+  </si>
+  <si>
+    <t>Weathering Steel，Color Glazed Glass，Aluminum Panel，CdTe PV Module</t>
+  </si>
+  <si>
+    <t>厂房、立体车库</t>
+  </si>
+  <si>
+    <t>Factory Building，Stereo Parking Garage</t>
+  </si>
+  <si>
+    <t>焱唐能源科技(杭州)有限责任公司</t>
+  </si>
+  <si>
+    <t>Yantang Energy Technology (Hangzhou) Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2022-05-18</t>
+  </si>
+  <si>
+    <t>大疆顺德智能科技园</t>
+  </si>
+  <si>
+    <t>DJI Shunde Intelligent Science &amp; Technology Park</t>
+  </si>
+  <si>
+    <t>175000㎡</t>
+  </si>
+  <si>
+    <t>佛山市顺德区</t>
+  </si>
+  <si>
+    <t>Shunde District, Foshan City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>Glulam，Weathering Steel，Profiled Metal Sheet</t>
+  </si>
+  <si>
+    <t>深圳市大疆创新科技有限公司</t>
+  </si>
+  <si>
+    <t>SZ DJI Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
+    <t>老君山瑞玺叶星河酒店</t>
+  </si>
+  <si>
+    <t>Laojun Mountain Ruixi Yexinghe Hotel</t>
+  </si>
+  <si>
+    <t>度假酒店</t>
+  </si>
+  <si>
+    <t>Resort Hotel</t>
+  </si>
+  <si>
+    <t>2800㎡</t>
+  </si>
+  <si>
+    <t>洛阳市栾川县老君山追梦谷</t>
+  </si>
+  <si>
+    <t>Laojun Mountain Dream Valley, Luanchuan County, Luoyang City</t>
+  </si>
+  <si>
+    <t>Pure White Micro-Cement、Solid Wood、Dark Grey Stone、Glass Curtain Wall</t>
+  </si>
+  <si>
+    <t>别墅观景客房、商务接待、餐饮、艺术长廊</t>
+  </si>
+  <si>
+    <t>Villa Viewing Guest Rooms、Business Reception Area、Catering、Art Corridor</t>
+  </si>
+  <si>
+    <t>洛阳瑞玺叶星河民宿有限公司</t>
+  </si>
+  <si>
+    <t>Luoyang Ruixi Yexinghe Homestay Co., Ltd.</t>
+  </si>
+  <si>
+    <t>嘉荣物流产业园</t>
+  </si>
+  <si>
+    <t>Jiarong Logistics Industrial Park</t>
+  </si>
+  <si>
+    <t>433540㎡</t>
+  </si>
+  <si>
+    <t>东莞市洪梅镇</t>
+  </si>
+  <si>
+    <t>Hongmei Town, Dongguan City</t>
+  </si>
+  <si>
+    <t>Fair-Facedconcrete, Glulam，Anodized Aluminum Panel，Metal Grille，</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、宿舍、商业</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Dormitory，Commercial</t>
+  </si>
+  <si>
+    <t>东莞市嘉耀实业投资有限公司</t>
+  </si>
+  <si>
+    <t>Dongguan Jiayao Industrial Investment Co., Ltd.</t>
+  </si>
+  <si>
+    <t>小天才智能科技中心</t>
+  </si>
+  <si>
+    <t>Imoo Intelligent Technology Center</t>
+  </si>
+  <si>
+    <t>Science and Technology Park</t>
+  </si>
+  <si>
+    <t>195560㎡</t>
+  </si>
+  <si>
+    <t>东莞市滨海湾新区</t>
+  </si>
+  <si>
+    <t>Dongguan Binhaiwan New District</t>
+  </si>
+  <si>
+    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃</t>
+  </si>
+  <si>
+    <t>Glulam，Anodized Aluminum Panel，Metal Grille，Glass</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、公寓</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Apartment</t>
+  </si>
+  <si>
+    <t>广东小天才科技有限公司</t>
+  </si>
+  <si>
+    <t>Guangdong Genius Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>生命之树装置深化设计</t>
+  </si>
+  <si>
+    <t>Detail Design of Tree of Life Installation</t>
+  </si>
+  <si>
+    <t>艺术装置</t>
+  </si>
+  <si>
+    <t>Art Installation</t>
+  </si>
+  <si>
+    <t>300㎡</t>
+  </si>
+  <si>
+    <t>重庆市经开区</t>
+  </si>
+  <si>
+    <t>Chongqing Economic and Technological Development Zone</t>
+  </si>
+  <si>
+    <t>胶合木</t>
+  </si>
+  <si>
+    <t>Glulam</t>
+  </si>
+  <si>
+    <t>广阳湾珊瑚小学</t>
+  </si>
+  <si>
+    <t>Guangyang Bay Coral Primary School</t>
+  </si>
+  <si>
+    <t>2021-12-03</t>
+  </si>
+  <si>
+    <t>庐南学校项目</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>菜鸟物流中心</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>鹏峰</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>小米上海汽车总部</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>城市展厅</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>华为团泊洼地办公项目</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>欢聚集团总部产业园</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>海阳路学校</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>佛山企业家大厦</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>鹏峰奥迪4s店</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>境工作室汇报</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>万兴科技产业研究中心</t>
+  </si>
+  <si>
+    <t>Wondershare Industrial Research Center</t>
+  </si>
+  <si>
+    <t>119344㎡</t>
+  </si>
+  <si>
+    <t>湖南长沙市</t>
+  </si>
+  <si>
+    <t>Changsha City, Hunan Province</t>
+  </si>
+  <si>
+    <t>研发办公、商业、公寓</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; Office，Commercial，Apartment</t>
+  </si>
+  <si>
+    <t>万兴科技集团股份有限公司</t>
+  </si>
+  <si>
+    <t>Wondershare Technology Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2020-09-18</t>
+  </si>
+  <si>
+    <t>李沧项目</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>小天才产业园</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>常州怀德中路项目</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>中联重科智慧产业城</t>
+  </si>
+  <si>
+    <t>2020-04-08</t>
+  </si>
+  <si>
+    <t>佛山绿地彩管大厦</t>
+  </si>
+  <si>
+    <t>Greenland Caiguan Building, Foshan</t>
+  </si>
+  <si>
+    <t>超高层办公楼</t>
+  </si>
+  <si>
+    <t>Super High-rise Office Building</t>
+  </si>
+  <si>
+    <t>261173㎡</t>
+  </si>
+  <si>
+    <t>佛山市禅城区</t>
+  </si>
+  <si>
+    <t>Chancheng District, Foshan</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel，Glass，Perforated Metal Panel</t>
+  </si>
+  <si>
+    <t>办公、酒店、数据中心</t>
+  </si>
+  <si>
+    <t>Office, Hotel，Data Center Complex</t>
+  </si>
+  <si>
+    <t>绿地集团</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
+    <t>广东洲明节能科技有限公司LED生产基地</t>
+  </si>
+  <si>
+    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd. LED Production Base</t>
+  </si>
+  <si>
+    <t>394349㎡</t>
+  </si>
+  <si>
+    <t>惠州市大亚湾区</t>
+  </si>
+  <si>
+    <t>Dayawan District, Huizhou City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、金属格栅、玻璃</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel，Metal Grille，Glass</t>
+  </si>
+  <si>
+    <t>厂房、研发办公、宿舍</t>
+  </si>
+  <si>
+    <t>Factory Building，R&amp;D &amp; Office，Dormitory</t>
+  </si>
+  <si>
+    <t>广东洲明节能科技有限公司</t>
+  </si>
+  <si>
+    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>PA018276.01中粮祥云•地铁小镇项目商办地块</t>
+  </si>
+  <si>
+    <t>中粮祥云•地铁小镇项目商办地块</t>
+  </si>
+  <si>
+    <t>2019-11-11</t>
+  </si>
+  <si>
+    <t>虹海研发大厦</t>
+  </si>
+  <si>
+    <t>2019-09-29</t>
+  </si>
+  <si>
+    <t>联润大厦项目</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>万达展览馆</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>郑州富士康蔚来云城商业D地块方案</t>
+  </si>
+  <si>
+    <t>2019-02-18</t>
+  </si>
+  <si>
+    <t>许昌信通金融中心项目</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
+    <t>黄山五里山房酒店群</t>
+  </si>
+  <si>
+    <t>Wuli Shanfang Hotel Cluster, Huangshan</t>
+  </si>
+  <si>
+    <t>21500㎡</t>
+  </si>
+  <si>
+    <t>安徽黄山黟县碧阳镇</t>
+  </si>
+  <si>
+    <t>Biyang Town, Yi County, Huangshan City, Anhui Province</t>
+  </si>
+  <si>
+    <t>艺术涂料、金属穿孔铝板、铝镁锰屋面板、青灰瓦</t>
+  </si>
+  <si>
+    <t>Art Coating、Perforated Aluminum Panel、Aluminum-Magnesium-Manganese Roof Panel、Blue-Grey Clay Tile</t>
+  </si>
+  <si>
+    <t>度假别墅客房、商务接待、茶文化展厅、徽文化研学</t>
+  </si>
+  <si>
+    <t>Holiday Villa Guest Rooms, Business Reception Area, Tea Culture Exhibition Hall 、Huizhou Culture Study Base</t>
+  </si>
+  <si>
+    <t>黟县徽黄旅游发展有限公司</t>
+  </si>
+  <si>
+    <t>Yixian Huihuang Tourism Development Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>恒大水世界</t>
+  </si>
+  <si>
+    <t>2018-09-29</t>
+  </si>
+  <si>
+    <t>公司2015-2018作品集</t>
+  </si>
+  <si>
+    <t>2018-09-10</t>
+  </si>
+  <si>
+    <t>崇州7号地块</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>公司装修</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>郑州曲梁863产业园</t>
+  </si>
+  <si>
+    <t>2018-02-11</t>
+  </si>
+  <si>
+    <t>昆仑世纪花园</t>
+  </si>
+  <si>
+    <t>2018-01-12</t>
+  </si>
+  <si>
+    <t>广西巴马酒店综合体项目</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
+    <t>巴马.高端星级酒店综合体</t>
+  </si>
+  <si>
+    <t>Premium Star-rated Hotel Complex in Bama</t>
+  </si>
+  <si>
+    <t>高端度假酒店综合体</t>
+  </si>
+  <si>
+    <t>Premium Holiday Hotel Complex</t>
+  </si>
+  <si>
+    <t>200865㎡</t>
+  </si>
+  <si>
+    <t>巴马瑶族自治县</t>
+  </si>
+  <si>
+    <t>Bama Yao Autonomous County</t>
+  </si>
+  <si>
+    <t>蜂窝铝板、玻璃幕墙、金属格栅</t>
+  </si>
+  <si>
+    <t>Honeycomb Aluminum Panels, Glass Curtain Wall 、 Metal Grilles</t>
+  </si>
+  <si>
+    <t>五星级酒店、高端公寓、瑶族文化体验中心</t>
+  </si>
+  <si>
+    <t>Five-star Hotel, High-end Apartments, Yao Culture Experience Center</t>
+  </si>
+  <si>
+    <t>广西长江天成投资集团</t>
+  </si>
+  <si>
+    <t>Guangxi Yangtze Tessa Investment Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>2017-12-05</t>
+  </si>
+  <si>
+    <t>宜宾亿豪酒店</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>甘肃西部中药城</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>福建德化城东中小企业创业园</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>新安区第三工业区康美智慧药房改造项目概念方案</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>康养健康小镇咸宁项目概念性规划设计</t>
+  </si>
+  <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
+    <t>郑州金水</t>
+  </si>
+  <si>
+    <t>2017-05-22</t>
+  </si>
+  <si>
+    <t>广西玉林中药城项目</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>湖南靖州茯苓物流交易中心</t>
+  </si>
+  <si>
+    <t>2017-03-14</t>
+  </si>
+  <si>
+    <t>西宁城西御景华城</t>
+  </si>
+  <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
+    <t>佛山顺德家具厂</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>螺阳镇会所</t>
+  </si>
+  <si>
+    <t>2016-12-19</t>
+  </si>
+  <si>
+    <t>南京K2016-腾旭科技</t>
+  </si>
+  <si>
+    <t>2016-10-26</t>
+  </si>
+  <si>
+    <t>同济工业大厦立面设计</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>广东东明节能科技有限公司LED生产基地项目</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>螺阳镇松星村安置区</t>
+  </si>
+  <si>
+    <t>2016-06-12</t>
+  </si>
+  <si>
+    <t>中国（揭阳）国际珠宝翡翠交易中心项目</t>
+  </si>
+  <si>
+    <t>2016-06-10</t>
+  </si>
+  <si>
+    <t>亲戚房子（谢勇士+高丽+邱四平）</t>
+  </si>
+  <si>
+    <t>2016-05-09</t>
+  </si>
+  <si>
+    <t>中港珠宝旅游商业城</t>
+  </si>
+  <si>
+    <t>2016-05-03</t>
+  </si>
+  <si>
+    <t>富士康企业会所</t>
+  </si>
+  <si>
+    <t>2016-03-30</t>
+  </si>
+  <si>
+    <t>坪山周大生</t>
+  </si>
+  <si>
+    <t>2015-12-21</t>
+  </si>
+  <si>
+    <t>晋江周氏置业项目</t>
+  </si>
+  <si>
+    <t>2015-09-09</t>
+  </si>
+  <si>
+    <t>深圳检验检测认证技术中心建筑设计项目</t>
+  </si>
+  <si>
+    <t>2015-09-01</t>
+  </si>
+  <si>
+    <t>深圳职业技术学院留仙洞校区G栋学生宿舍建设</t>
+  </si>
+  <si>
+    <t>2015-08-13</t>
+  </si>
+  <si>
+    <t>宏发公明售楼处</t>
+  </si>
+  <si>
+    <t>2015-07-14</t>
+  </si>
+  <si>
+    <t>梅林中学扩建学生宿舍楼工程</t>
+  </si>
+  <si>
+    <t>2015-06-01</t>
+  </si>
+  <si>
+    <t>美国云峰商务酒店</t>
+  </si>
+  <si>
+    <t>2015-05-25</t>
+  </si>
+  <si>
+    <t>博林沙井地块项目</t>
+  </si>
+  <si>
+    <t>2015-05-21</t>
+  </si>
+  <si>
+    <t>坪山现代精密办公楼</t>
+  </si>
+  <si>
+    <t>2015-05-08</t>
+  </si>
+  <si>
+    <t>宝投航城工业厂区设计</t>
+  </si>
+  <si>
+    <t>2015-03-12</t>
+  </si>
+  <si>
+    <t>拉斯维加斯雪蛋赌场</t>
+  </si>
+  <si>
+    <t>2015-02-10</t>
+  </si>
+  <si>
+    <t>滇红博物馆</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>深圳大鹏较场尾大旅小舍民宿改造</t>
+  </si>
+  <si>
+    <t>Dalv Xiaoshe Homestay Renovation Project, Jiaochangwei, Dapeng New Area, Shenzhen</t>
+  </si>
+  <si>
+    <t>民宿</t>
+  </si>
+  <si>
+    <t>166485㎡</t>
+  </si>
+  <si>
+    <t>2014-09-17</t>
+  </si>
+  <si>
+    <t>博林天瑞花园立面</t>
+  </si>
+  <si>
+    <t>2014-07-30</t>
+  </si>
+  <si>
+    <t>岑溪汇洋新世界</t>
+  </si>
+  <si>
+    <t>2014-07-18</t>
+  </si>
+  <si>
+    <t>龙华简上村（原2011-04-30—部项目）</t>
+  </si>
+  <si>
+    <t>2014-07-16</t>
+  </si>
+  <si>
+    <t>岑溪市思湖广场</t>
+  </si>
+  <si>
+    <t>2014-07-08</t>
+  </si>
+  <si>
+    <t>河北天户峪旅游度假村项目</t>
+  </si>
+  <si>
+    <t>2014-05-20</t>
+  </si>
+  <si>
+    <t>蛇口工业八路南源工业区更新单元改造项目</t>
+  </si>
+  <si>
+    <t>2014-04-02</t>
+  </si>
+  <si>
+    <t>中泰艺术名庭改造</t>
+  </si>
+  <si>
+    <t>2014-03-26</t>
+  </si>
+  <si>
+    <t>深圳湾“超级城市”国际竞赛</t>
+  </si>
+  <si>
+    <t>2013-12-29</t>
+  </si>
+  <si>
+    <t>博林海德城</t>
+  </si>
+  <si>
+    <t>2013-12-24</t>
+  </si>
+  <si>
+    <t>广东喜之郎集团总部大厦</t>
+  </si>
+  <si>
+    <t>2013-11-25</t>
+  </si>
+  <si>
+    <t>南京明发</t>
+  </si>
+  <si>
+    <t>2013-10-10</t>
+  </si>
+  <si>
+    <t>宝安机场城市更新项目</t>
+  </si>
+  <si>
+    <t>2013-09-18</t>
+  </si>
+  <si>
+    <t>城市复兴</t>
+  </si>
+  <si>
+    <t>2013-09-13</t>
+  </si>
+  <si>
+    <t>宝安机场口岸综合楼项目</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>华润深圳湾综合发展项目北区住宅竞赛</t>
+  </si>
+  <si>
+    <t>2013-06-28</t>
+  </si>
+  <si>
+    <t>老挝茶文化体验中心</t>
+  </si>
+  <si>
+    <t>2013-02-13</t>
+  </si>
+  <si>
+    <t>武汉大学艺术楼</t>
+  </si>
+  <si>
+    <t>Fine Arts Building, Wuhan University</t>
+  </si>
+  <si>
+    <t>文教</t>
+  </si>
+  <si>
+    <t>Culture &amp; Education</t>
+  </si>
+  <si>
+    <t>5371㎡</t>
+  </si>
+  <si>
+    <t>湖北武汉市</t>
+  </si>
+  <si>
+    <t>Wuhan City, Hubei Province</t>
+  </si>
+  <si>
+    <t>阳极氧化铝板、玻璃</t>
+  </si>
+  <si>
+    <t>Anodized Aluminum Panel， Glass</t>
+  </si>
+  <si>
+    <t>教室，图书室，音乐厅、会议</t>
+  </si>
+  <si>
+    <t>Classroom, Library, Concert Hall ， Conference Space</t>
+  </si>
+  <si>
+    <t>武汉大学</t>
+  </si>
+  <si>
+    <t>Wuhan University</t>
+  </si>
+  <si>
+    <t>2013-01-01</t>
+  </si>
+  <si>
+    <t>老挝万象茶文化中心</t>
+  </si>
+  <si>
+    <t>Vientiane Tea Culture Center, Laos</t>
+  </si>
+  <si>
+    <t>3200㎡</t>
+  </si>
+  <si>
+    <t>老挝万象市</t>
+  </si>
+  <si>
+    <t>Vientiane Municipality, Laos</t>
+  </si>
+  <si>
+    <t>清水混凝土、胶合木、金属格栅、</t>
+  </si>
+  <si>
+    <t>Fair-Facedconcrete, Glulam， Metal Grille</t>
+  </si>
+  <si>
+    <t>办公、展厅、会所、宿舍</t>
+  </si>
+  <si>
+    <t>Office，Showroom，Club House，Dormitory</t>
+  </si>
+  <si>
+    <t>2012-12-25</t>
+  </si>
+  <si>
+    <t>华润惠州小径湾滨海度假村2期</t>
+  </si>
+  <si>
+    <t>China Resources Park Lane Harbour Coastal Resort Phase 2, Huizhou</t>
+  </si>
+  <si>
+    <t>居住</t>
+  </si>
+  <si>
+    <t>2012-10-18</t>
+  </si>
+  <si>
+    <t>贵阳玉蝶</t>
+  </si>
+  <si>
+    <t>2012-07-14</t>
+  </si>
+  <si>
+    <t>南京文化中心</t>
+  </si>
+  <si>
+    <t>2012-04-10</t>
+  </si>
+  <si>
+    <t>Foshan Entrepreneur Building</t>
+  </si>
+  <si>
+    <t>157553㎡</t>
+  </si>
+  <si>
+    <t>广东佛山市</t>
+  </si>
+  <si>
+    <t>Foshan City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>办公、酒店、会议，商业</t>
+  </si>
+  <si>
+    <t>Office, Hotel, Conference ， Commercial</t>
+  </si>
+  <si>
+    <t>佛山企业家联合体</t>
+  </si>
+  <si>
+    <t>Foshan Entrepreneurs Federation</t>
+  </si>
+  <si>
+    <t>2011-11-06</t>
+  </si>
+  <si>
+    <t>上海杨浦智创天地-w</t>
+  </si>
+  <si>
+    <t>2011-09-05</t>
+  </si>
+  <si>
+    <t>淄博文化中心</t>
+  </si>
+  <si>
+    <t>2011-07-08</t>
+  </si>
+  <si>
+    <t>港珠澳大桥珠海口岸规划国际竞赛</t>
+  </si>
+  <si>
+    <t>International Planning Competition, Zhuhai Port of HZMB</t>
+  </si>
+  <si>
+    <t>交通枢纽</t>
+  </si>
+  <si>
+    <t>Transport Hub（</t>
+  </si>
+  <si>
+    <t>586152m2</t>
+  </si>
+  <si>
+    <t>广东珠海市</t>
+  </si>
+  <si>
+    <t>Zhuhai City, Guangdong Province</t>
+  </si>
+  <si>
+    <t>海关口岸，办公，商业</t>
+  </si>
+  <si>
+    <t>Customs Port, Office ， Commercial Facilities</t>
+  </si>
+  <si>
+    <t>珠海市港珠澳大桥建设协调办公室</t>
+  </si>
+  <si>
+    <t>Zhuhai HZMB Construction Coordination Office</t>
+  </si>
+  <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
+    <t>世界自然基金会汉中游客信息中心</t>
+  </si>
+  <si>
+    <t>WWF Hanzhong Visitor Information Centre</t>
+  </si>
+  <si>
+    <t>Cultural &amp; Tourism</t>
+  </si>
+  <si>
+    <t>332㎡</t>
+  </si>
+  <si>
+    <t>陕西汉中市</t>
+  </si>
+  <si>
+    <t>Hanzhong City, Shaanxi Province</t>
+  </si>
+  <si>
+    <t>胶合木、冷弯薄壁型钢</t>
+  </si>
+  <si>
+    <t>Glulam，Cold-Formed Thin-Wall Steel</t>
+  </si>
+  <si>
+    <t>展厅、接待、办公</t>
+  </si>
+  <si>
+    <t>Showroom, Reception ， Office</t>
+  </si>
+  <si>
+    <t>WWF世界自然基金会</t>
+  </si>
+  <si>
+    <t>WWF – World Wide Fund for Nature</t>
+  </si>
+  <si>
+    <t>2010-12-04</t>
+  </si>
+  <si>
+    <t>淄博大剧院</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
+    <t>四川里坪村小学校</t>
+  </si>
+  <si>
+    <t>Liping Village Primary School, Sichuan</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>201㎡</t>
+  </si>
+  <si>
+    <t>四川青川县</t>
+  </si>
+  <si>
+    <t>Qingchuan, Sichuan</t>
+  </si>
+  <si>
+    <t>生土、原木</t>
+  </si>
+  <si>
+    <t>Raw Earth，Log</t>
+  </si>
+  <si>
+    <t>2022-05-28</t>
+  </si>
+  <si>
+    <t>新丰项目阶段性成果整理</t>
+  </si>
+  <si>
+    <t>2022-01-06</t>
+  </si>
+  <si>
+    <t>新丰美食街</t>
+  </si>
+  <si>
+    <t>新丰菜市场改造</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>规划局环保局办公楼</t>
+  </si>
+  <si>
+    <t>2020-09-06</t>
+  </si>
+  <si>
+    <t>垃圾站+厕所</t>
+  </si>
+  <si>
+    <t>2020-06-27</t>
+  </si>
+  <si>
+    <t>黄局自宅</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>黄寨景观</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>遥田图书馆</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>方志馆档案馆</t>
+  </si>
+  <si>
+    <t>2019-10-12</t>
+  </si>
+  <si>
+    <t>新丰文化中心</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>新丰廉租房项目</t>
+  </si>
+  <si>
+    <t>2019-02-19</t>
+  </si>
+  <si>
+    <t>新丰黄磜镇幸福公社</t>
+  </si>
+  <si>
+    <t>2018-11-16</t>
+  </si>
+  <si>
+    <t>新丰规划局涵洞改造</t>
+  </si>
+  <si>
+    <t>2018-10-10</t>
+  </si>
+  <si>
+    <t>新丰气象站</t>
+  </si>
+  <si>
+    <t>2018-07-31</t>
+  </si>
+  <si>
+    <t>新丰城市厕所项目</t>
+  </si>
+  <si>
+    <t>2018-07-09</t>
+  </si>
+  <si>
+    <t>新丰村委会改造</t>
+  </si>
+  <si>
+    <t>2017-04-17</t>
+  </si>
+  <si>
+    <t>新丰老一中改造</t>
+  </si>
+  <si>
+    <t>外墙漆、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农村自建房别墅景观设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农村自建房别墅设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外墙漆、玻璃、铝板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>376㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱建新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州24时辰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驿站</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、耐候钢、花岗石、杉木、洗石子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐候钢、彩釉玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李松蓢项目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>316574㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高品质生活居住区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、光明区、公明街道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>香槟金铝板、真石漆、莱姆石，玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市公明李松蓢股份合作公司     深圳市特发鸿顺实业有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住、商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州市“百千万工程”指挥办</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨海驿站设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装配式居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、耐候钢、压型金属板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>潘先生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文旅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教会</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1800㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公楼立面升级改造</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清远市、高新区雄兴工业区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>广东省、陆丰陂洋莲花寨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖北省，洪湖市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠州市、惠东县、稔平半岛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿孔铝板、铝板、木纹瓷砖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清远市南星化工有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产业园</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非物质文化遗产科技艺术产业园</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30100㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区、乌鲁木齐市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜂窝铝板、原木、玻璃幕墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、蜂窝铝板、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯白微水泥、原木、深灰石材、玻璃幕墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、胶合木、 阳极氧化铝板、金属格栅、</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 阳极氧化铝板、纯白微水泥、木纹瓷砖、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艺术馆、商业、酒店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆轩润景文化传媒有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>城中村住宅外墙立面更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寺院接待、宿舍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寺院活动接待及住宿设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台湾省、台南市、新化区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>学校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>73456㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态的“新公园式学校”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、龙华区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、阳极氧化铝板、玻璃、耐候钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真石漆，外墙漆、硅胶灯带</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、耐候钢、穿孔铝板、外墙漆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙华区工务署</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>观城9年一贯制学校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教学及辅助用房、办公用房、生活用房</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6500㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高端高尔夫练习场设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>西港云壤高尔夫练习场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柬埔寨、西港云壤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、耐候钢、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>打位区、售楼处、办公</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、南山区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、南山区前海自贸区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、耐候钢、铝板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人行天桥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">深圳市前海管理局 
+香港立法会            </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人行立交桥设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30249㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>后海小学改扩建</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木饰面铝板、无机涂料，穿孔板、铝合金格栅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>南山区工务署</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27200㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>湖南省、保靖县</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、胶合木、 阳极氧化铝板、层叠文化石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>厂房、接待、商业、酒店、办公、展厅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保靖县人民政府</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>规划</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>148000㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨海文化区规划概念设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化馆、图书馆、艺术中心、科技馆、商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>东莞市、滨海湾新区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>东莞滨海湾新区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文保</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公室改造，加装LED屏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乳胶漆、胶合木、石膏板、瓷砖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳前海哈罗外籍人员子女学校改造</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳前海哈罗外籍人员子女学校</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>121㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特色酒吧设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼伦贝尔小酒吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼伦贝尔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛石、原木、阳光板、石板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3430㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文物建筑保护修缮及景观提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、龙岗区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>农业景观，凉亭，休憩，</t>
-  </si>
-  <si>
-    <t>袁小海</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>邱宅</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>文旅</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>装配式居住单元</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
-    <t>台湾教堂</t>
-  </si>
-  <si>
-    <t>2025-11-14</t>
-  </si>
-  <si>
-    <t>南星厂房</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>2025-07-23</t>
-  </si>
-  <si>
-    <t>深圳南园街道立面改造</t>
-  </si>
-  <si>
-    <t>Facade Renovation Project of Nanyuan Subdistrict, Shenzhen</t>
-  </si>
-  <si>
-    <t>城市更新</t>
-  </si>
-  <si>
-    <t>Urban Renewal</t>
-  </si>
-  <si>
-    <t>3500㎡</t>
-  </si>
-  <si>
-    <t>深圳南园路</t>
-  </si>
-  <si>
-    <t>Nanyuan Rd, Shenzhen</t>
-  </si>
-  <si>
-    <t>Real Stone Coating, Exterior Wall Paint, Silicone LED Strip Lights</t>
-  </si>
-  <si>
-    <t>住宅、商业</t>
-  </si>
-  <si>
-    <t>Residential，Commercial</t>
-  </si>
-  <si>
-    <t>深圳市南园街道办</t>
-  </si>
-  <si>
-    <t>Nanyuan Subdistrict Office, Futian District, Shenzhen</t>
-  </si>
-  <si>
-    <t>2025-06-22</t>
-  </si>
-  <si>
-    <t>妈湾3座桥</t>
-  </si>
-  <si>
-    <t>2025-02-12</t>
-  </si>
-  <si>
-    <t>新疆轩润晟非物质文化遗产科技艺术产业园</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>谢老师 观音寺项目</t>
-  </si>
-  <si>
-    <t>2024-10-14</t>
-  </si>
-  <si>
-    <t>妈湾城市艺术装置</t>
-  </si>
-  <si>
-    <t>2024-09-06</t>
-  </si>
-  <si>
-    <t>2024-06-18</t>
-  </si>
-  <si>
-    <t>后海小学初步设计</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>宁夏国药温泉康养小镇</t>
-  </si>
-  <si>
-    <t>Ningxia Sinopharm Hot Spring Wellness Town</t>
-  </si>
-  <si>
-    <t>酒店</t>
-  </si>
-  <si>
-    <t>Hot Spring Resort Hotel</t>
-  </si>
-  <si>
-    <t>150600㎡</t>
-  </si>
-  <si>
-    <t>宁夏固原市泾源县</t>
-  </si>
-  <si>
-    <t>Jingyuan County, Guyuan City, Ningxia Hui Autonomous Region</t>
-  </si>
-  <si>
-    <t>Honeycomb aluminum panels, solid wood,  glass curtain wall</t>
-  </si>
-  <si>
-    <t>温泉别墅、温泉酒店、高端民宿</t>
-  </si>
-  <si>
-    <t>Hot Spring Villas, Hot Spring Hotel, High-end Homestays</t>
-  </si>
-  <si>
-    <t>中国医药集团有限公司</t>
-  </si>
-  <si>
-    <t>China National Pharmaceutical Group Corporation</t>
-  </si>
-  <si>
-    <t>2024-02-22</t>
-  </si>
-  <si>
-    <t>吕洞山景区游客服务中心设计</t>
-  </si>
-  <si>
-    <t>2024-01-03</t>
-  </si>
-  <si>
-    <t>东莞滨海文化区方案设计国际竞赛</t>
-  </si>
-  <si>
-    <t>2023-12-13</t>
-  </si>
-  <si>
-    <t>武夷山茶庄园项目概念规划</t>
-  </si>
-  <si>
-    <t>2023-11-30</t>
-  </si>
-  <si>
-    <t>珠海市（第四批）历史建筑数字化建档</t>
-  </si>
-  <si>
-    <t>2023-11-06</t>
-  </si>
-  <si>
-    <t>深圳前海哈罗外籍人员子女学校改造</t>
-  </si>
-  <si>
-    <t>2023-11-01</t>
-  </si>
-  <si>
-    <t>呼伦贝尔小酒吧</t>
-  </si>
-  <si>
-    <t>2023-10-23</t>
-  </si>
-  <si>
-    <t>河南信阳车云山茶文化民宿</t>
-  </si>
-  <si>
-    <t>Cheyun Mountain Tea Culture Homestay, Xinyang, Henan Province</t>
-  </si>
-  <si>
-    <t>度假民宿</t>
-  </si>
-  <si>
-    <t>Vacation Homestay</t>
-  </si>
-  <si>
-    <t>3900㎡</t>
-  </si>
-  <si>
-    <t>信阳市董家河车云山</t>
-  </si>
-  <si>
-    <t>Cheyun Mountain, Dongjiahe, Xinyang City, Henan Province</t>
-  </si>
-  <si>
-    <t>原木、铝镁锰屋面板、玻璃幕墙</t>
-  </si>
-  <si>
-    <t>Honeycomb aluminum panels、solid wood、glass curtain wall</t>
-  </si>
-  <si>
-    <t>度假民宿、接待、展厅</t>
-  </si>
-  <si>
-    <t>Vacation Homestay，Reception，Showroom</t>
-  </si>
-  <si>
-    <t>河南省住建厅</t>
-  </si>
-  <si>
-    <t>Department of Housing and Urban-Rural Development of Henan Province</t>
-  </si>
-  <si>
-    <t>五里山房</t>
-  </si>
-  <si>
-    <t>2023-08-29</t>
-  </si>
-  <si>
-    <t>台湾新竹县竹东客家文化大合埕</t>
-  </si>
-  <si>
-    <t>Dahecheng of Hakka Culture, Zhudong, Hsinchu County, Taiwan</t>
-  </si>
-  <si>
-    <t>文化建筑</t>
-  </si>
-  <si>
-    <t>Cultural Building</t>
-  </si>
-  <si>
-    <t>11353.78㎡</t>
-  </si>
-  <si>
-    <t>台湾新竹县</t>
-  </si>
-  <si>
-    <t>Hsinchu County, Taiwan, China</t>
-  </si>
-  <si>
-    <t>Fair-facedConcrete, Weathering Steel，Granite，Chinese Fir，Exposed Aggregate</t>
-  </si>
-  <si>
-    <t>办公、商业、展厅、展演、餐饮</t>
-  </si>
-  <si>
-    <t>Office, Commercial, Showroom, Performance Hall, Catering Area</t>
-  </si>
-  <si>
-    <t>新竹县政府</t>
-  </si>
-  <si>
-    <t>Henan Investment Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2023-07-20</t>
-  </si>
-  <si>
-    <t>鹤湖新居微更新</t>
-  </si>
-  <si>
-    <t>2023-07-09</t>
-  </si>
-  <si>
-    <t>海南环岛公路重点驿站酒店</t>
-  </si>
-  <si>
-    <t>Key Resort Inns of Hainan Coastal Ring Road</t>
-  </si>
-  <si>
-    <t>度假驿站酒店</t>
-  </si>
-  <si>
-    <t>Holiday Resort Inn</t>
-  </si>
-  <si>
-    <t>48700㎡</t>
-  </si>
-  <si>
-    <t>海南省东方市板桥镇</t>
-  </si>
-  <si>
-    <t>Banqiao Town, Dongfang City, Hainan Province</t>
-  </si>
-  <si>
-    <t>Fair-Faced Concrete, Aluminum Honeycomb Panel, Glass</t>
-  </si>
-  <si>
-    <t>艺术酒店、艺术博物馆、游客中心、国际交流中心</t>
-  </si>
-  <si>
-    <t>Art Hotel, Art Museum, Visitor Center 、International Exchange Center</t>
-  </si>
-  <si>
-    <t>海南省自然资源和规划厅</t>
-  </si>
-  <si>
-    <t>Hainan Provincial Department of Natural Resources and Planning</t>
-  </si>
-  <si>
-    <t>2023-07-07</t>
-  </si>
-  <si>
-    <t>南方新住宅竞赛</t>
-  </si>
-  <si>
-    <t>2023-06-16</t>
-  </si>
-  <si>
-    <t>坪山河景观桥概念方案设计</t>
-  </si>
-  <si>
-    <t>2023-05-21</t>
-  </si>
-  <si>
-    <t>中原制药厂</t>
-  </si>
-  <si>
-    <t>Zhongyuan Pharmaceutical Factory</t>
-  </si>
-  <si>
-    <t>产业园</t>
-  </si>
-  <si>
-    <t>Industrial Park</t>
-  </si>
-  <si>
-    <t>430000㎡</t>
-  </si>
-  <si>
-    <t>郑州市高新区</t>
-  </si>
-  <si>
-    <t>Zhengzhou High Tech Zone</t>
-  </si>
-  <si>
-    <t>Fair-faced Concrete, Anodized Aluminum Panel, Glass, Weathering Steel</t>
-  </si>
-  <si>
-    <t>办公、商业、展厅、会议、生产车间</t>
-  </si>
-  <si>
-    <t>Office，Commercial，Exhibition Hall，Conference，Production Workshop</t>
-  </si>
-  <si>
-    <t>河南投资集团</t>
-  </si>
-  <si>
-    <t>2023-05-03</t>
-  </si>
-  <si>
-    <t>百校焕新项目</t>
-  </si>
-  <si>
-    <t>2023-04-03</t>
-  </si>
-  <si>
-    <t>利元亨南通华东</t>
-  </si>
-  <si>
-    <t>2022-12-20</t>
-  </si>
-  <si>
-    <t>广东嘉速物流工改工项目</t>
-  </si>
-  <si>
-    <t>2022-11-10</t>
-  </si>
-  <si>
-    <t>大江东唐焱厂房BIPV</t>
-  </si>
-  <si>
-    <t>BIPV Project of Tangyan Factory Building, Dadongjiang</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>书院、景观绿化、凉亭，休憩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夯土、耐候钢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市龙岗区文化广电旅游体育局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>800㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人行景观桥设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、坪山区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐候钢、混凝土、木纹金属板、金属格栅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>景观桥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市坪山区自然资源局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>厂房</t>
-  </si>
-  <si>
-    <t>Factory Building</t>
-  </si>
-  <si>
-    <t>139455㎡</t>
-  </si>
-  <si>
-    <t>浙江省杭州市钱塘区</t>
-  </si>
-  <si>
-    <t>Qiantang District, Hangzhou City, Zhejiang Province, China</t>
-  </si>
-  <si>
-    <t>耐候钢、彩釉玻璃、铝板、碲化镉光伏组件</t>
-  </si>
-  <si>
-    <t>Weathering Steel，Color Glazed Glass，Aluminum Panel，CdTe PV Module</t>
-  </si>
-  <si>
-    <t>厂房、立体车库</t>
-  </si>
-  <si>
-    <t>Factory Building，Stereo Parking Garage</t>
-  </si>
-  <si>
-    <t>焱唐能源科技(杭州)有限责任公司</t>
-  </si>
-  <si>
-    <t>Yantang Energy Technology (Hangzhou) Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2022-05-18</t>
-  </si>
-  <si>
-    <t>大疆顺德智能科技园</t>
-  </si>
-  <si>
-    <t>DJI Shunde Intelligent Science &amp; Technology Park</t>
-  </si>
-  <si>
-    <t>175000㎡</t>
-  </si>
-  <si>
-    <t>佛山市顺德区</t>
-  </si>
-  <si>
-    <t>Shunde District, Foshan City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>Glulam，Weathering Steel，Profiled Metal Sheet</t>
-  </si>
-  <si>
-    <t>深圳市大疆创新科技有限公司</t>
-  </si>
-  <si>
-    <t>SZ DJI Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
-    <t>老君山瑞玺叶星河酒店</t>
-  </si>
-  <si>
-    <t>Laojun Mountain Ruixi Yexinghe Hotel</t>
-  </si>
-  <si>
-    <t>度假酒店</t>
-  </si>
-  <si>
-    <t>Resort Hotel</t>
-  </si>
-  <si>
-    <t>2800㎡</t>
-  </si>
-  <si>
-    <t>洛阳市栾川县老君山追梦谷</t>
-  </si>
-  <si>
-    <t>Laojun Mountain Dream Valley, Luanchuan County, Luoyang City</t>
-  </si>
-  <si>
-    <t>Pure White Micro-Cement、Solid Wood、Dark Grey Stone、Glass Curtain Wall</t>
-  </si>
-  <si>
-    <t>别墅观景客房、商务接待、餐饮、艺术长廊</t>
-  </si>
-  <si>
-    <t>Villa Viewing Guest Rooms、Business Reception Area、Catering、Art Corridor</t>
-  </si>
-  <si>
-    <t>洛阳瑞玺叶星河民宿有限公司</t>
-  </si>
-  <si>
-    <t>Luoyang Ruixi Yexinghe Homestay Co., Ltd.</t>
-  </si>
-  <si>
-    <t>嘉荣物流产业园</t>
-  </si>
-  <si>
-    <t>Jiarong Logistics Industrial Park</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>157290㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>厂房外立面改造</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省、南通市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳极氧化铝板、金属格栅、光伏板、压型金属板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成车间、办公</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏利元亨智能装备有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11500㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>福建省、武夷山</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>厂房、接待、酒店、办公、展厅、观光塔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶文化体验中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶文化主题游客服务中心设计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武夷山华祥苑茶庄园有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>433540㎡</t>
-  </si>
-  <si>
-    <t>东莞市洪梅镇</t>
-  </si>
-  <si>
-    <t>Hongmei Town, Dongguan City</t>
-  </si>
-  <si>
-    <t>Fair-Facedconcrete, Glulam，Anodized Aluminum Panel，Metal Grille，</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、宿舍、商业</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Dormitory，Commercial</t>
-  </si>
-  <si>
-    <t>东莞市嘉耀实业投资有限公司</t>
-  </si>
-  <si>
-    <t>Dongguan Jiayao Industrial Investment Co., Ltd.</t>
-  </si>
-  <si>
-    <t>小天才智能科技中心</t>
-  </si>
-  <si>
-    <t>Imoo Intelligent Technology Center</t>
-  </si>
-  <si>
-    <t>Science and Technology Park</t>
-  </si>
-  <si>
-    <t>195560㎡</t>
-  </si>
-  <si>
-    <t>东莞市滨海湾新区</t>
-  </si>
-  <si>
-    <t>Dongguan Binhaiwan New District</t>
-  </si>
-  <si>
-    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃</t>
-  </si>
-  <si>
-    <t>Glulam，Anodized Aluminum Panel，Metal Grille，Glass</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、公寓</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Apartment</t>
-  </si>
-  <si>
-    <t>广东小天才科技有限公司</t>
-  </si>
-  <si>
-    <t>Guangdong Genius Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>生命之树装置深化设计</t>
-  </si>
-  <si>
-    <t>Detail Design of Tree of Life Installation</t>
-  </si>
-  <si>
-    <t>艺术装置</t>
-  </si>
-  <si>
-    <t>Art Installation</t>
-  </si>
-  <si>
-    <t>300㎡</t>
-  </si>
-  <si>
-    <t>重庆市经开区</t>
-  </si>
-  <si>
-    <t>Chongqing Economic and Technological Development Zone</t>
-  </si>
-  <si>
-    <t>胶合木</t>
-  </si>
-  <si>
-    <t>Glulam</t>
-  </si>
-  <si>
-    <t>广阳湾珊瑚小学</t>
-  </si>
-  <si>
-    <t>Guangyang Bay Coral Primary School</t>
-  </si>
-  <si>
-    <t>2021-12-03</t>
-  </si>
-  <si>
-    <t>庐南学校项目</t>
-  </si>
-  <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>菜鸟物流中心</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>鹏峰</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>小米上海汽车总部</t>
-  </si>
-  <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
-    <t>城市展厅</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>华为团泊洼地办公项目</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>欢聚集团总部产业园</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>海阳路学校</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>佛山企业家大厦</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>鹏峰奥迪4s店</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>境工作室汇报</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>万兴科技产业研究中心</t>
-  </si>
-  <si>
-    <t>Wondershare Industrial Research Center</t>
-  </si>
-  <si>
-    <t>119344㎡</t>
-  </si>
-  <si>
-    <t>湖南长沙市</t>
-  </si>
-  <si>
-    <t>Changsha City, Hunan Province</t>
-  </si>
-  <si>
-    <t>研发办公、商业、公寓</t>
-  </si>
-  <si>
-    <t>R&amp;D &amp; Office，Commercial，Apartment</t>
-  </si>
-  <si>
-    <t>万兴科技集团股份有限公司</t>
-  </si>
-  <si>
-    <t>Wondershare Technology Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2020-09-18</t>
-  </si>
-  <si>
-    <t>李沧项目</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>小天才产业园</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>常州怀德中路项目</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>中联重科智慧产业城</t>
-  </si>
-  <si>
-    <t>2020-04-08</t>
-  </si>
-  <si>
-    <t>佛山绿地彩管大厦</t>
-  </si>
-  <si>
-    <t>Greenland Caiguan Building, Foshan</t>
-  </si>
-  <si>
-    <t>超高层办公楼</t>
-  </si>
-  <si>
-    <t>Super High-rise Office Building</t>
-  </si>
-  <si>
-    <t>261173㎡</t>
-  </si>
-  <si>
-    <t>佛山市禅城区</t>
-  </si>
-  <si>
-    <t>Chancheng District, Foshan</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel，Glass，Perforated Metal Panel</t>
-  </si>
-  <si>
-    <t>办公、酒店、数据中心</t>
-  </si>
-  <si>
-    <t>Office, Hotel，Data Center Complex</t>
-  </si>
-  <si>
-    <t>绿地集团</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
-    <t>广东洲明节能科技有限公司LED生产基地</t>
-  </si>
-  <si>
-    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd. LED Production Base</t>
-  </si>
-  <si>
-    <t>394349㎡</t>
-  </si>
-  <si>
-    <t>惠州市大亚湾区</t>
-  </si>
-  <si>
-    <t>Dayawan District, Huizhou City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、金属格栅、玻璃</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel，Metal Grille，Glass</t>
-  </si>
-  <si>
-    <t>厂房、研发办公、宿舍</t>
-  </si>
-  <si>
-    <t>Factory Building，R&amp;D &amp; Office，Dormitory</t>
-  </si>
-  <si>
-    <t>广东洲明节能科技有限公司</t>
-  </si>
-  <si>
-    <t>Guangdong Unilumin Energy Savings Technology Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>PA018276.01中粮祥云•地铁小镇项目商办地块</t>
-  </si>
-  <si>
-    <t>中粮祥云•地铁小镇项目商办地块</t>
-  </si>
-  <si>
-    <t>2019-11-11</t>
-  </si>
-  <si>
-    <t>虹海研发大厦</t>
-  </si>
-  <si>
-    <t>2019-09-29</t>
-  </si>
-  <si>
-    <t>联润大厦项目</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>万达展览馆</t>
-  </si>
-  <si>
-    <t>2019-02-28</t>
-  </si>
-  <si>
-    <t>郑州富士康蔚来云城商业D地块方案</t>
-  </si>
-  <si>
-    <t>2019-02-18</t>
-  </si>
-  <si>
-    <t>许昌信通金融中心项目</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
-    <t>黄山五里山房酒店群</t>
-  </si>
-  <si>
-    <t>Wuli Shanfang Hotel Cluster, Huangshan</t>
-  </si>
-  <si>
-    <t>21500㎡</t>
-  </si>
-  <si>
-    <t>安徽黄山黟县碧阳镇</t>
-  </si>
-  <si>
-    <t>Biyang Town, Yi County, Huangshan City, Anhui Province</t>
-  </si>
-  <si>
-    <t>艺术涂料、金属穿孔铝板、铝镁锰屋面板、青灰瓦</t>
-  </si>
-  <si>
-    <t>Art Coating、Perforated Aluminum Panel、Aluminum-Magnesium-Manganese Roof Panel、Blue-Grey Clay Tile</t>
-  </si>
-  <si>
-    <t>度假别墅客房、商务接待、茶文化展厅、徽文化研学</t>
-  </si>
-  <si>
-    <t>Holiday Villa Guest Rooms, Business Reception Area, Tea Culture Exhibition Hall 、Huizhou Culture Study Base</t>
-  </si>
-  <si>
-    <t>黟县徽黄旅游发展有限公司</t>
-  </si>
-  <si>
-    <t>Yixian Huihuang Tourism Development Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>恒大水世界</t>
-  </si>
-  <si>
-    <t>2018-09-29</t>
-  </si>
-  <si>
-    <t>公司2015-2018作品集</t>
-  </si>
-  <si>
-    <t>2018-09-10</t>
-  </si>
-  <si>
-    <t>崇州7号地块</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>公司装修</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>郑州曲梁863产业园</t>
-  </si>
-  <si>
-    <t>2018-02-11</t>
-  </si>
-  <si>
-    <t>昆仑世纪花园</t>
-  </si>
-  <si>
-    <t>2018-01-12</t>
-  </si>
-  <si>
-    <t>广西巴马酒店综合体项目</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
-    <t>巴马.高端星级酒店综合体</t>
-  </si>
-  <si>
-    <t>Premium Star-rated Hotel Complex in Bama</t>
-  </si>
-  <si>
-    <t>高端度假酒店综合体</t>
-  </si>
-  <si>
-    <t>Premium Holiday Hotel Complex</t>
-  </si>
-  <si>
-    <t>200865㎡</t>
-  </si>
-  <si>
-    <t>巴马瑶族自治县</t>
-  </si>
-  <si>
-    <t>Bama Yao Autonomous County</t>
-  </si>
-  <si>
-    <t>蜂窝铝板、玻璃幕墙、金属格栅</t>
-  </si>
-  <si>
-    <t>Honeycomb Aluminum Panels, Glass Curtain Wall 、 Metal Grilles</t>
-  </si>
-  <si>
-    <t>五星级酒店、高端公寓、瑶族文化体验中心</t>
-  </si>
-  <si>
-    <t>Five-star Hotel, High-end Apartments, Yao Culture Experience Center</t>
-  </si>
-  <si>
-    <t>广西长江天成投资集团</t>
-  </si>
-  <si>
-    <t>Guangxi Yangtze Tessa Investment Group Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2017-12-05</t>
-  </si>
-  <si>
-    <t>宜宾亿豪酒店</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>甘肃西部中药城</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>福建德化城东中小企业创业园</t>
-  </si>
-  <si>
-    <t>2017-08-24</t>
-  </si>
-  <si>
-    <t>新安区第三工业区康美智慧药房改造项目概念方案</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>康养健康小镇咸宁项目概念性规划设计</t>
-  </si>
-  <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
-    <t>郑州金水</t>
-  </si>
-  <si>
-    <t>2017-05-22</t>
-  </si>
-  <si>
-    <t>广西玉林中药城项目</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>湖南靖州茯苓物流交易中心</t>
-  </si>
-  <si>
-    <t>2017-03-14</t>
-  </si>
-  <si>
-    <t>西宁城西御景华城</t>
-  </si>
-  <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
-    <t>佛山顺德家具厂</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>螺阳镇会所</t>
-  </si>
-  <si>
-    <t>2016-12-19</t>
-  </si>
-  <si>
-    <t>南京K2016-腾旭科技</t>
-  </si>
-  <si>
-    <t>2016-10-26</t>
-  </si>
-  <si>
-    <t>同济工业大厦立面设计</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>广东东明节能科技有限公司LED生产基地项目</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>螺阳镇松星村安置区</t>
-  </si>
-  <si>
-    <t>2016-06-12</t>
-  </si>
-  <si>
-    <t>中国（揭阳）国际珠宝翡翠交易中心项目</t>
-  </si>
-  <si>
-    <t>2016-06-10</t>
-  </si>
-  <si>
-    <t>亲戚房子（谢勇士+高丽+邱四平）</t>
-  </si>
-  <si>
-    <t>2016-05-09</t>
-  </si>
-  <si>
-    <t>中港珠宝旅游商业城</t>
-  </si>
-  <si>
-    <t>2016-05-03</t>
-  </si>
-  <si>
-    <t>富士康企业会所</t>
-  </si>
-  <si>
-    <t>2016-03-30</t>
-  </si>
-  <si>
-    <t>坪山周大生</t>
-  </si>
-  <si>
-    <t>2015-12-21</t>
-  </si>
-  <si>
-    <t>晋江周氏置业项目</t>
-  </si>
-  <si>
-    <t>2015-09-09</t>
-  </si>
-  <si>
-    <t>深圳检验检测认证技术中心建筑设计项目</t>
-  </si>
-  <si>
-    <t>2015-09-01</t>
-  </si>
-  <si>
-    <t>深圳职业技术学院留仙洞校区G栋学生宿舍建设</t>
-  </si>
-  <si>
-    <t>2015-08-13</t>
-  </si>
-  <si>
-    <t>宏发公明售楼处</t>
-  </si>
-  <si>
-    <t>2015-07-14</t>
-  </si>
-  <si>
-    <t>梅林中学扩建学生宿舍楼工程</t>
-  </si>
-  <si>
-    <t>2015-06-01</t>
-  </si>
-  <si>
-    <t>美国云峰商务酒店</t>
-  </si>
-  <si>
-    <t>2015-05-25</t>
-  </si>
-  <si>
-    <t>博林沙井地块项目</t>
-  </si>
-  <si>
-    <t>2015-05-21</t>
-  </si>
-  <si>
-    <t>坪山现代精密办公楼</t>
-  </si>
-  <si>
-    <t>2015-05-08</t>
-  </si>
-  <si>
-    <t>宝投航城工业厂区设计</t>
-  </si>
-  <si>
-    <t>2015-03-12</t>
-  </si>
-  <si>
-    <t>拉斯维加斯雪蛋赌场</t>
-  </si>
-  <si>
-    <t>2015-02-10</t>
-  </si>
-  <si>
-    <t>滇红博物馆</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
-    <t>深圳大鹏较场尾大旅小舍民宿改造</t>
-  </si>
-  <si>
-    <t>Dalv Xiaoshe Homestay Renovation Project, Jiaochangwei, Dapeng New Area, Shenzhen</t>
-  </si>
-  <si>
-    <t>民宿</t>
-  </si>
-  <si>
-    <t>166485㎡</t>
-  </si>
-  <si>
-    <t>2014-09-17</t>
-  </si>
-  <si>
-    <t>博林天瑞花园立面</t>
-  </si>
-  <si>
-    <t>2014-07-30</t>
-  </si>
-  <si>
-    <t>岑溪汇洋新世界</t>
-  </si>
-  <si>
-    <t>2014-07-18</t>
-  </si>
-  <si>
-    <t>龙华简上村（原2011-04-30—部项目）</t>
-  </si>
-  <si>
-    <t>2014-07-16</t>
-  </si>
-  <si>
-    <t>岑溪市思湖广场</t>
-  </si>
-  <si>
-    <t>2014-07-08</t>
-  </si>
-  <si>
-    <t>河北天户峪旅游度假村项目</t>
-  </si>
-  <si>
-    <t>2014-05-20</t>
-  </si>
-  <si>
-    <t>蛇口工业八路南源工业区更新单元改造项目</t>
-  </si>
-  <si>
-    <t>2014-04-02</t>
-  </si>
-  <si>
-    <t>中泰艺术名庭改造</t>
-  </si>
-  <si>
-    <t>2014-03-26</t>
-  </si>
-  <si>
-    <t>深圳湾“超级城市”国际竞赛</t>
-  </si>
-  <si>
-    <t>2013-12-29</t>
-  </si>
-  <si>
-    <t>博林海德城</t>
-  </si>
-  <si>
-    <t>2013-12-24</t>
-  </si>
-  <si>
-    <t>广东喜之郎集团总部大厦</t>
-  </si>
-  <si>
-    <t>2013-11-25</t>
-  </si>
-  <si>
-    <t>南京明发</t>
-  </si>
-  <si>
-    <t>2013-10-10</t>
-  </si>
-  <si>
-    <t>宝安机场城市更新项目</t>
-  </si>
-  <si>
-    <t>2013-09-18</t>
-  </si>
-  <si>
-    <t>城市复兴</t>
-  </si>
-  <si>
-    <t>2013-09-13</t>
-  </si>
-  <si>
-    <t>宝安机场口岸综合楼项目</t>
-  </si>
-  <si>
-    <t>2013-07-02</t>
-  </si>
-  <si>
-    <t>华润深圳湾综合发展项目北区住宅竞赛</t>
-  </si>
-  <si>
-    <t>2013-06-28</t>
-  </si>
-  <si>
-    <t>老挝茶文化体验中心</t>
-  </si>
-  <si>
-    <t>2013-02-13</t>
-  </si>
-  <si>
-    <t>武汉大学艺术楼</t>
-  </si>
-  <si>
-    <t>Fine Arts Building, Wuhan University</t>
-  </si>
-  <si>
-    <t>文教</t>
-  </si>
-  <si>
-    <t>Culture &amp; Education</t>
-  </si>
-  <si>
-    <t>5371㎡</t>
-  </si>
-  <si>
-    <t>湖北武汉市</t>
-  </si>
-  <si>
-    <t>Wuhan City, Hubei Province</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、玻璃</t>
-  </si>
-  <si>
-    <t>Anodized Aluminum Panel， Glass</t>
-  </si>
-  <si>
-    <t>教室，图书室，音乐厅、会议</t>
-  </si>
-  <si>
-    <t>Classroom, Library, Concert Hall ， Conference Space</t>
-  </si>
-  <si>
-    <t>武汉大学</t>
-  </si>
-  <si>
-    <t>Wuhan University</t>
-  </si>
-  <si>
-    <t>2013-01-01</t>
-  </si>
-  <si>
-    <t>老挝万象茶文化中心</t>
-  </si>
-  <si>
-    <t>Vientiane Tea Culture Center, Laos</t>
-  </si>
-  <si>
-    <t>3200㎡</t>
-  </si>
-  <si>
-    <t>老挝万象市</t>
-  </si>
-  <si>
-    <t>Vientiane Municipality, Laos</t>
-  </si>
-  <si>
-    <t>清水混凝土、胶合木、金属格栅、</t>
-  </si>
-  <si>
-    <t>Fair-Facedconcrete, Glulam， Metal Grille</t>
-  </si>
-  <si>
-    <t>办公、展厅、会所、宿舍</t>
-  </si>
-  <si>
-    <t>Office，Showroom，Club House，Dormitory</t>
-  </si>
-  <si>
-    <t>2012-12-25</t>
-  </si>
-  <si>
-    <t>华润惠州小径湾滨海度假村2期</t>
-  </si>
-  <si>
-    <t>China Resources Park Lane Harbour Coastal Resort Phase 2, Huizhou</t>
-  </si>
-  <si>
-    <t>居住</t>
-  </si>
-  <si>
-    <t>2012-10-18</t>
-  </si>
-  <si>
-    <t>贵阳玉蝶</t>
-  </si>
-  <si>
-    <t>2012-07-14</t>
-  </si>
-  <si>
-    <t>南京文化中心</t>
-  </si>
-  <si>
-    <t>2012-04-10</t>
-  </si>
-  <si>
-    <t>Foshan Entrepreneur Building</t>
-  </si>
-  <si>
-    <t>157553㎡</t>
-  </si>
-  <si>
-    <t>广东佛山市</t>
-  </si>
-  <si>
-    <t>Foshan City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>办公、酒店、会议，商业</t>
-  </si>
-  <si>
-    <t>Office, Hotel, Conference ， Commercial</t>
-  </si>
-  <si>
-    <t>佛山企业家联合体</t>
-  </si>
-  <si>
-    <t>Foshan Entrepreneurs Federation</t>
-  </si>
-  <si>
-    <t>2011-11-06</t>
-  </si>
-  <si>
-    <t>上海杨浦智创天地-w</t>
-  </si>
-  <si>
-    <t>2011-09-05</t>
-  </si>
-  <si>
-    <t>淄博文化中心</t>
-  </si>
-  <si>
-    <t>2011-07-08</t>
-  </si>
-  <si>
-    <t>港珠澳大桥珠海口岸规划国际竞赛</t>
-  </si>
-  <si>
-    <t>International Planning Competition, Zhuhai Port of HZMB</t>
-  </si>
-  <si>
-    <t>交通枢纽</t>
-  </si>
-  <si>
-    <t>Transport Hub（</t>
-  </si>
-  <si>
-    <t>586152m2</t>
-  </si>
-  <si>
-    <t>广东珠海市</t>
-  </si>
-  <si>
-    <t>Zhuhai City, Guangdong Province</t>
-  </si>
-  <si>
-    <t>海关口岸，办公，商业</t>
-  </si>
-  <si>
-    <t>Customs Port, Office ， Commercial Facilities</t>
-  </si>
-  <si>
-    <t>珠海市港珠澳大桥建设协调办公室</t>
-  </si>
-  <si>
-    <t>Zhuhai HZMB Construction Coordination Office</t>
-  </si>
-  <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
-    <t>世界自然基金会汉中游客信息中心</t>
-  </si>
-  <si>
-    <t>WWF Hanzhong Visitor Information Centre</t>
-  </si>
-  <si>
-    <t>Cultural &amp; Tourism</t>
-  </si>
-  <si>
-    <t>332㎡</t>
-  </si>
-  <si>
-    <t>陕西汉中市</t>
-  </si>
-  <si>
-    <t>Hanzhong City, Shaanxi Province</t>
-  </si>
-  <si>
-    <t>胶合木、冷弯薄壁型钢</t>
-  </si>
-  <si>
-    <t>Glulam，Cold-Formed Thin-Wall Steel</t>
-  </si>
-  <si>
-    <t>展厅、接待、办公</t>
-  </si>
-  <si>
-    <t>Showroom, Reception ， Office</t>
-  </si>
-  <si>
-    <t>WWF世界自然基金会</t>
-  </si>
-  <si>
-    <t>WWF – World Wide Fund for Nature</t>
-  </si>
-  <si>
-    <t>2010-12-04</t>
-  </si>
-  <si>
-    <t>淄博大剧院</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
-    <t>四川里坪村小学校</t>
-  </si>
-  <si>
-    <t>Liping Village Primary School, Sichuan</t>
-  </si>
-  <si>
-    <t>学校</t>
-  </si>
-  <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>201㎡</t>
-  </si>
-  <si>
-    <t>四川青川县</t>
-  </si>
-  <si>
-    <t>Qingchuan, Sichuan</t>
-  </si>
-  <si>
-    <t>生土、原木</t>
-  </si>
-  <si>
-    <t>Raw Earth，Log</t>
-  </si>
-  <si>
-    <t>2022-05-28</t>
-  </si>
-  <si>
-    <t>新丰项目阶段性成果整理</t>
-  </si>
-  <si>
-    <t>2022-01-06</t>
-  </si>
-  <si>
-    <t>新丰美食街</t>
-  </si>
-  <si>
-    <t>新丰菜市场改造</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>规划局环保局办公楼</t>
-  </si>
-  <si>
-    <t>2020-09-06</t>
-  </si>
-  <si>
-    <t>垃圾站+厕所</t>
-  </si>
-  <si>
-    <t>2020-06-27</t>
-  </si>
-  <si>
-    <t>黄局自宅</t>
-  </si>
-  <si>
-    <t>2020-06-09</t>
-  </si>
-  <si>
-    <t>黄寨景观</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>遥田图书馆</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>方志馆档案馆</t>
-  </si>
-  <si>
-    <t>2019-10-12</t>
-  </si>
-  <si>
-    <t>新丰文化中心</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>新丰廉租房项目</t>
-  </si>
-  <si>
-    <t>2019-02-19</t>
-  </si>
-  <si>
-    <t>新丰黄磜镇幸福公社</t>
-  </si>
-  <si>
-    <t>2018-11-16</t>
-  </si>
-  <si>
-    <t>新丰规划局涵洞改造</t>
-  </si>
-  <si>
-    <t>2018-10-10</t>
-  </si>
-  <si>
-    <t>新丰气象站</t>
-  </si>
-  <si>
-    <t>2018-07-31</t>
-  </si>
-  <si>
-    <t>新丰城市厕所项目</t>
-  </si>
-  <si>
-    <t>2018-07-09</t>
-  </si>
-  <si>
-    <t>新丰村委会改造</t>
-  </si>
-  <si>
-    <t>2017-04-17</t>
-  </si>
-  <si>
-    <t>新丰老一中改造</t>
-  </si>
-  <si>
-    <t>外墙漆、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>农村自建房别墅景观设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>农村自建房别墅设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>外墙漆、玻璃、铝板</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>居住</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>376㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱建新</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>惠州24时辰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4200㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>驿站</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、耐候钢、花岗石、杉木、洗石子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>耐候钢、彩釉玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李松蓢项目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>316574㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高品质生活居住区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳市、光明区、公明街道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>香槟金铝板、真石漆、莱姆石，玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳市公明李松蓢股份合作公司     深圳市特发鸿顺实业有限公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>居住、商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>100平米</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>惠州市“百千万工程”指挥办</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>滨海驿站设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>装配式居住</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胶合木、耐候钢、压型金属板</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>居住</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>潘先生</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>文旅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胶合木、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教会</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>办公</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1800㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>办公楼立面升级改造</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清远市、高新区雄兴工业区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东省、陆丰陂洋莲花寨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>湖北省，洪湖市</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>惠州市、惠东县、稔平半岛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>穿孔铝板、铝板、木纹瓷砖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清远市南星化工有限公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产业园</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非物质文化遗产科技艺术产业园</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>30100㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆维吾尔自治区、乌鲁木齐市</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蜂窝铝板、原木、玻璃幕墙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、蜂窝铝板、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯白微水泥、原木、深灰石材、玻璃幕墙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、胶合木、 阳极氧化铝板、金属格栅、</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 阳极氧化铝板、纯白微水泥、木纹瓷砖、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>艺术馆、商业、酒店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆轩润景文化传媒有限公司</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>城中村住宅外墙立面更新</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3000㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>寺院接待、宿舍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>寺院活动接待及住宿设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>台湾省、台南市、新化区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>学校</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>73456㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生态的“新公园式学校”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深圳市、龙华区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、阳极氧化铝板、玻璃、耐候钢</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>真石漆，外墙漆、硅胶灯带</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清水混凝土、耐候钢、穿孔铝板、外墙漆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙华区工务署</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>观城9年一贯制学校</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教学及辅助用房、办公用房、生活用房</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6500㎡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高端高尔夫练习场设计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>西港云壤高尔夫练习场</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>柬埔寨、西港云壤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胶合木、耐候钢、玻璃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>打位区、售楼处、办公</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2009,7 +2253,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2029,6 +2273,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2090,7 +2340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2130,6 +2380,15 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2462,9 +2721,9 @@
     <col min="9" max="9" width="12.9140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="30" style="2" customWidth="1"/>
     <col min="11" max="11" width="36" style="2" customWidth="1"/>
-    <col min="12" max="12" width="37.83203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="42.75" style="2" customWidth="1"/>
     <col min="13" max="13" width="40" style="2" customWidth="1"/>
-    <col min="14" max="14" width="31.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="41.08203125" style="2" customWidth="1"/>
     <col min="15" max="15" width="32" style="2" customWidth="1"/>
     <col min="16" max="16" width="30" style="2" customWidth="1"/>
     <col min="17" max="17" width="34" style="2" customWidth="1"/>
@@ -2539,39 +2798,39 @@
         <v>46370</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12" t="s">
-        <v>20</v>
+        <v>658</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:17" ht="34" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="9">
@@ -2581,151 +2840,151 @@
         <v>517.96</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="Q3" s="3"/>
     </row>
     <row r="4" spans="1:17" ht="34" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="10">
         <v>46152</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="11" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17" ht="34" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
         <v>2026</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="11" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="Q5" s="3"/>
     </row>
     <row r="6" spans="1:17" ht="34" customHeight="1">
       <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="10">
         <v>46252</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>571</v>
+        <v>627</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" ht="34" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="9">
@@ -2737,11 +2996,11 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -2749,75 +3008,75 @@
     </row>
     <row r="8" spans="1:17" ht="34" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="10">
         <v>46090</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" ht="34" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="9">
         <v>45889</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -2825,483 +3084,589 @@
     </row>
     <row r="10" spans="1:17" ht="34" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="F10" s="10">
         <v>46147</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="M10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="34" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>619</v>
+      </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="9">
+        <v>45876</v>
+      </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>625</v>
+      </c>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>621</v>
+      </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3" t="s">
+        <v>622</v>
+      </c>
       <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
+      <c r="N11" s="3" t="s">
+        <v>623</v>
+      </c>
       <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="P11" s="14" t="s">
+        <v>624</v>
+      </c>
       <c r="Q11" s="3"/>
     </row>
     <row r="12" spans="1:17" ht="34" customHeight="1">
       <c r="A12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5">
         <v>2026</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17" ht="34" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3">
         <v>2026</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" ht="34" customHeight="1">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
     </row>
     <row r="15" spans="1:17" ht="34" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="10">
         <v>45559</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>602</v>
+      </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="F16" s="9">
+        <v>45873</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>628</v>
+      </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>620</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>629</v>
+      </c>
       <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3" t="s">
+        <v>611</v>
+      </c>
       <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3" t="s">
+        <v>630</v>
+      </c>
       <c r="Q16" s="3"/>
     </row>
     <row r="17" spans="1:17" ht="34" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="F17" s="5">
         <v>2024</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="L17" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="L17" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="M17" s="5" t="s">
+      <c r="N17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="O17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="P17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="P17" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="F18" s="9">
+        <v>45608</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>680</v>
+      </c>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>632</v>
+      </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>633</v>
+      </c>
       <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>634</v>
+      </c>
       <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3" t="s">
+        <v>635</v>
+      </c>
       <c r="Q18" s="3"/>
     </row>
     <row r="19" spans="1:17" ht="34" customHeight="1">
       <c r="A19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="D19" s="5" t="s">
+        <v>636</v>
+      </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="F19" s="10">
+        <v>45310</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>638</v>
+      </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="J19" s="5" t="s">
+        <v>640</v>
+      </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
+      <c r="N19" s="5" t="s">
+        <v>639</v>
+      </c>
       <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="P19" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="Q19" s="5"/>
     </row>
     <row r="20" spans="1:17" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="9">
+        <v>45296</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="1:17" ht="34" customHeight="1">
+      <c r="A21" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:17" ht="34" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="B21" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
     </row>
     <row r="22" spans="1:17" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>646</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>602</v>
+      </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="F22" s="9">
+        <v>45366</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>644</v>
+      </c>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>620</v>
+      </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="3" t="s">
+        <v>645</v>
+      </c>
       <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>577</v>
+      </c>
       <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3" t="s">
+        <v>647</v>
+      </c>
       <c r="Q22" s="3"/>
     </row>
     <row r="23" spans="1:17" ht="34" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="D23" s="5" t="s">
+        <v>614</v>
+      </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="F23" s="10">
+        <v>45403</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>649</v>
+      </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="J23" s="5" t="s">
+        <v>651</v>
+      </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="5" t="s">
+        <v>652</v>
+      </c>
       <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
+      <c r="N23" s="5" t="s">
+        <v>653</v>
+      </c>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
     </row>
     <row r="24" spans="1:17" ht="34" customHeight="1">
       <c r="A24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="F24" s="5">
         <v>2024</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="N24" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="O24" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="P24" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="N24" s="5" t="s">
+      <c r="Q24" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="34" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -3321,278 +3686,334 @@
     </row>
     <row r="26" spans="1:17" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="F26" s="3">
         <v>2025</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>654</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="M26" s="3" t="s">
+      <c r="P26" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="Q26" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="34" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="D27" s="5" t="s">
+        <v>642</v>
+      </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="F27" s="10">
+        <v>45478</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>656</v>
+      </c>
       <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="J27" s="5" t="s">
+        <v>657</v>
+      </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="5" t="s">
+        <v>660</v>
+      </c>
       <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
+      <c r="N27" s="5" t="s">
+        <v>659</v>
+      </c>
       <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="P27" s="5" t="s">
+        <v>661</v>
+      </c>
       <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="1:17" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="F28" s="3">
         <v>2023</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="O28" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="M28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="O28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A29" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="B29" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="Q28" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="34" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
     </row>
     <row r="30" spans="1:17" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>619</v>
+      </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="F30" s="9">
+        <v>45349</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>663</v>
+      </c>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>664</v>
+      </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="3" t="s">
+        <v>665</v>
+      </c>
       <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+      <c r="N30" s="3" t="s">
+        <v>666</v>
+      </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3" t="s">
+        <v>667</v>
+      </c>
       <c r="Q30" s="3"/>
     </row>
     <row r="31" spans="1:17" ht="34" customHeight="1">
       <c r="A31" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="F31" s="5">
         <v>2023</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="N31" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="O31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="L31" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="M31" s="5" t="s">
+      <c r="P31" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="N31" s="5" t="s">
+      <c r="Q31" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A32" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="B32" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="P31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="34" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
     </row>
     <row r="33" spans="1:17" ht="34" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="D33" s="5" t="s">
+        <v>668</v>
+      </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="F33" s="10">
+        <v>45061</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>670</v>
+      </c>
       <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="J33" s="5" t="s">
+        <v>671</v>
+      </c>
       <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="5" t="s">
+        <v>673</v>
+      </c>
       <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
+      <c r="N33" s="5" t="s">
+        <v>674</v>
+      </c>
       <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
+      <c r="P33" s="5" t="s">
+        <v>675</v>
+      </c>
       <c r="Q33" s="5"/>
     </row>
     <row r="34" spans="1:17" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3" t="s">
+        <v>586</v>
+      </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="F34" s="9">
+        <v>44943</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>682</v>
+      </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -3606,304 +4027,304 @@
     </row>
     <row r="35" spans="1:17" ht="34" customHeight="1">
       <c r="A35" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="F35" s="5">
         <v>2025</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="M35" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="N35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="O35" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="P35" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N35" s="5" t="s">
+      <c r="Q35" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F36" s="3">
         <v>2022</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="P36" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="Q36" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="34" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="F37" s="3">
         <v>2022</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="M37" s="3" t="s">
+      <c r="P37" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="Q37" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="34" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F38" s="5">
         <v>2022</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="N38" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="O38" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="L38" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="M38" s="5" t="s">
+      <c r="P38" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="N38" s="5" t="s">
+      <c r="Q38" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="P38" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="34" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F39" s="3">
         <v>2022</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="N39" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="O39" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="P39" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="N39" s="3" t="s">
+      <c r="Q39" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="34" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="F40" s="5">
         <v>2022</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="M40" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="N40" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="P40" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="Q40" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="N40" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="P40" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="34" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3923,10 +4344,10 @@
     </row>
     <row r="42" spans="1:17" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -3946,10 +4367,10 @@
     </row>
     <row r="43" spans="1:17" ht="34" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -3969,10 +4390,10 @@
     </row>
     <row r="44" spans="1:17" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -3992,10 +4413,10 @@
     </row>
     <row r="45" spans="1:17" ht="34" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -4015,10 +4436,10 @@
     </row>
     <row r="46" spans="1:17" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -4038,10 +4459,10 @@
     </row>
     <row r="47" spans="1:17" ht="34" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -4061,10 +4482,10 @@
     </row>
     <row r="48" spans="1:17" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -4084,10 +4505,10 @@
     </row>
     <row r="49" spans="1:17" ht="34" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -4107,10 +4528,10 @@
     </row>
     <row r="50" spans="1:17" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -4130,10 +4551,10 @@
     </row>
     <row r="51" spans="1:17" ht="34" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -4153,59 +4574,59 @@
     </row>
     <row r="52" spans="1:17" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F52" s="3">
         <v>2021</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N52" s="3" t="s">
+      <c r="Q52" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="34" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -4225,10 +4646,10 @@
     </row>
     <row r="54" spans="1:17" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -4248,10 +4669,10 @@
     </row>
     <row r="55" spans="1:17" ht="34" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -4271,10 +4692,10 @@
     </row>
     <row r="56" spans="1:17" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -4294,108 +4715,108 @@
     </row>
     <row r="57" spans="1:17" ht="34" customHeight="1">
       <c r="A57" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="F57" s="5">
         <v>2022</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="M57" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="K57" s="5" t="s">
+      <c r="N57" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="L57" s="5" t="s">
+      <c r="O57" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="M57" s="5" t="s">
+      <c r="P57" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="N57" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="O57" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="P57" s="5" t="s">
-        <v>269</v>
-      </c>
       <c r="Q57" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F58" s="3">
         <v>2020</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="N58" s="3" t="s">
+      <c r="Q58" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="34" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -4415,10 +4836,10 @@
     </row>
     <row r="60" spans="1:17" ht="34" customHeight="1">
       <c r="A60" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -4438,10 +4859,10 @@
     </row>
     <row r="61" spans="1:17" ht="34" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -4461,10 +4882,10 @@
     </row>
     <row r="62" spans="1:17" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -4484,10 +4905,10 @@
     </row>
     <row r="63" spans="1:17" ht="34" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -4507,10 +4928,10 @@
     </row>
     <row r="64" spans="1:17" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -4530,10 +4951,10 @@
     </row>
     <row r="65" spans="1:17" ht="34" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -4553,59 +4974,59 @@
     </row>
     <row r="66" spans="1:17" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F66" s="3">
         <v>2019</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="N66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="34" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -4625,10 +5046,10 @@
     </row>
     <row r="68" spans="1:17" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -4648,10 +5069,10 @@
     </row>
     <row r="69" spans="1:17" ht="34" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -4671,10 +5092,10 @@
     </row>
     <row r="70" spans="1:17" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -4694,10 +5115,10 @@
     </row>
     <row r="71" spans="1:17" ht="34" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -4717,10 +5138,10 @@
     </row>
     <row r="72" spans="1:17" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -4740,10 +5161,10 @@
     </row>
     <row r="73" spans="1:17" ht="34" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -4763,59 +5184,59 @@
     </row>
     <row r="74" spans="1:17" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="F74" s="3">
         <v>2018</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="M74" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="N74" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L74" s="3" t="s">
+      <c r="O74" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="M74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="N74" s="3" t="s">
+      <c r="Q74" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q74" s="3" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="34" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -4835,10 +5256,10 @@
     </row>
     <row r="76" spans="1:17" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -4858,10 +5279,10 @@
     </row>
     <row r="77" spans="1:17" ht="34" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -4881,10 +5302,10 @@
     </row>
     <row r="78" spans="1:17" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
@@ -4904,10 +5325,10 @@
     </row>
     <row r="79" spans="1:17" ht="34" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -4927,10 +5348,10 @@
     </row>
     <row r="80" spans="1:17" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -4950,10 +5371,10 @@
     </row>
     <row r="81" spans="1:17" ht="34" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -4973,10 +5394,10 @@
     </row>
     <row r="82" spans="1:17" ht="34" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -4996,10 +5417,10 @@
     </row>
     <row r="83" spans="1:17" ht="34" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -5019,10 +5440,10 @@
     </row>
     <row r="84" spans="1:17" ht="34" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -5042,10 +5463,10 @@
     </row>
     <row r="85" spans="1:17" ht="34" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -5065,10 +5486,10 @@
     </row>
     <row r="86" spans="1:17" ht="34" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -5088,10 +5509,10 @@
     </row>
     <row r="87" spans="1:17" ht="34" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -5111,10 +5532,10 @@
     </row>
     <row r="88" spans="1:17" ht="34" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -5134,10 +5555,10 @@
     </row>
     <row r="89" spans="1:17" ht="34" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -5157,10 +5578,10 @@
     </row>
     <row r="90" spans="1:17" ht="34" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -5180,10 +5601,10 @@
     </row>
     <row r="91" spans="1:17" ht="34" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -5203,10 +5624,10 @@
     </row>
     <row r="92" spans="1:17" ht="34" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -5226,10 +5647,10 @@
     </row>
     <row r="93" spans="1:17" ht="34" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -5249,10 +5670,10 @@
     </row>
     <row r="94" spans="1:17" ht="34" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
@@ -5272,10 +5693,10 @@
     </row>
     <row r="95" spans="1:17" ht="34" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -5295,10 +5716,10 @@
     </row>
     <row r="96" spans="1:17" ht="34" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
@@ -5318,10 +5739,10 @@
     </row>
     <row r="97" spans="1:17" ht="34" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -5341,10 +5762,10 @@
     </row>
     <row r="98" spans="1:17" ht="34" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -5364,10 +5785,10 @@
     </row>
     <row r="99" spans="1:17" ht="34" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -5387,10 +5808,10 @@
     </row>
     <row r="100" spans="1:17" ht="34" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -5410,10 +5831,10 @@
     </row>
     <row r="101" spans="1:17" ht="34" customHeight="1">
       <c r="A101" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -5433,10 +5854,10 @@
     </row>
     <row r="102" spans="1:17" ht="34" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -5456,10 +5877,10 @@
     </row>
     <row r="103" spans="1:17" ht="34" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -5479,10 +5900,10 @@
     </row>
     <row r="104" spans="1:17" ht="34" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -5502,10 +5923,10 @@
     </row>
     <row r="105" spans="1:17" ht="34" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -5525,59 +5946,59 @@
     </row>
     <row r="106" spans="1:17" ht="34" customHeight="1">
       <c r="A106" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="E106" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F106" s="3">
         <v>2015</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M106" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="N106" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="M106" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N106" s="3" t="s">
+      <c r="P106" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q106" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="P106" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q106" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="34" customHeight="1">
       <c r="A107" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
@@ -5597,10 +6018,10 @@
     </row>
     <row r="108" spans="1:17" ht="34" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -5620,10 +6041,10 @@
     </row>
     <row r="109" spans="1:17" ht="34" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -5643,10 +6064,10 @@
     </row>
     <row r="110" spans="1:17" ht="34" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -5666,10 +6087,10 @@
     </row>
     <row r="111" spans="1:17" ht="34" customHeight="1">
       <c r="A111" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -5689,10 +6110,10 @@
     </row>
     <row r="112" spans="1:17" ht="34" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -5712,10 +6133,10 @@
     </row>
     <row r="113" spans="1:17" ht="34" customHeight="1">
       <c r="A113" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -5735,10 +6156,10 @@
     </row>
     <row r="114" spans="1:17" ht="34" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
@@ -5758,10 +6179,10 @@
     </row>
     <row r="115" spans="1:17" ht="34" customHeight="1">
       <c r="A115" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -5781,10 +6202,10 @@
     </row>
     <row r="116" spans="1:17" ht="34" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -5804,10 +6225,10 @@
     </row>
     <row r="117" spans="1:17" ht="34" customHeight="1">
       <c r="A117" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -5827,10 +6248,10 @@
     </row>
     <row r="118" spans="1:17" ht="34" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -5850,10 +6271,10 @@
     </row>
     <row r="119" spans="1:17" ht="34" customHeight="1">
       <c r="A119" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
@@ -5873,10 +6294,10 @@
     </row>
     <row r="120" spans="1:17" ht="34" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -5896,10 +6317,10 @@
     </row>
     <row r="121" spans="1:17" ht="34" customHeight="1">
       <c r="A121" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
@@ -5919,10 +6340,10 @@
     </row>
     <row r="122" spans="1:17" ht="34" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
@@ -5942,153 +6363,153 @@
     </row>
     <row r="123" spans="1:17" ht="34" customHeight="1">
       <c r="A123" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="D123" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="E123" s="5" t="s">
         <v>435</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>438</v>
       </c>
       <c r="F123" s="6">
         <v>2013</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="K123" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="L123" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="M123" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="K123" s="5" t="s">
+      <c r="N123" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="L123" s="5" t="s">
+      <c r="O123" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="M123" s="5" t="s">
+      <c r="P123" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="N123" s="5" t="s">
+      <c r="Q123" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="O123" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="P123" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q123" s="5" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="34" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F124" s="4">
         <v>2013</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="M124" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="N124" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="O124" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="M124" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="O124" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
     </row>
     <row r="125" spans="1:17" ht="34" customHeight="1">
       <c r="A125" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>461</v>
-      </c>
       <c r="E125" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F125" s="6">
         <v>2012</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="L125" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="M125" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="K125" s="5" t="s">
+      <c r="N125" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="L125" s="5" t="s">
+      <c r="O125" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="M125" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="N125" s="5" t="s">
+      <c r="P125" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q125" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="O125" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="P125" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q125" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="34" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
@@ -6108,10 +6529,10 @@
     </row>
     <row r="127" spans="1:17" ht="34" customHeight="1">
       <c r="A127" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
@@ -6131,59 +6552,59 @@
     </row>
     <row r="128" spans="1:17" ht="34" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F128" s="4">
         <v>2013</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="O128" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="P128" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="L128" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N128" s="3" t="s">
+      <c r="Q128" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="O128" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="P128" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q128" s="3" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="34" customHeight="1">
       <c r="A129" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
@@ -6203,10 +6624,10 @@
     </row>
     <row r="130" spans="1:17" ht="34" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
@@ -6226,108 +6647,108 @@
     </row>
     <row r="131" spans="1:17" ht="34" customHeight="1">
       <c r="A131" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="E131" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>483</v>
       </c>
       <c r="F131" s="6">
         <v>2011</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="L131" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="N131" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="O131" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="K131" s="5" t="s">
+      <c r="P131" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="L131" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="M131" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="N131" s="5" t="s">
+      <c r="Q131" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="O131" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="P131" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q131" s="5" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="34" customHeight="1">
       <c r="A132" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="F132" s="4">
         <v>2011</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="M132" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="N132" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="L132" s="3" t="s">
+      <c r="O132" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="M132" s="3" t="s">
+      <c r="P132" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="N132" s="3" t="s">
+      <c r="Q132" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="O132" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="P132" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q132" s="3" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="34" customHeight="1">
       <c r="A133" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
@@ -6347,55 +6768,55 @@
     </row>
     <row r="134" spans="1:17" ht="34" customHeight="1">
       <c r="A134" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="F134" s="4">
         <v>2009</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="M134" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="K134" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="M134" s="3" t="s">
-        <v>515</v>
-      </c>
       <c r="N134" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="P134" s="3"/>
       <c r="Q134" s="3"/>
     </row>
     <row r="135" spans="1:17" ht="34" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -6415,10 +6836,10 @@
     </row>
     <row r="136" spans="1:17" ht="34" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
@@ -6438,10 +6859,10 @@
     </row>
     <row r="137" spans="1:17" ht="34" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -6461,10 +6882,10 @@
     </row>
     <row r="138" spans="1:17" ht="34" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
@@ -6484,10 +6905,10 @@
     </row>
     <row r="139" spans="1:17" ht="34" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -6507,10 +6928,10 @@
     </row>
     <row r="140" spans="1:17" ht="34" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
@@ -6530,10 +6951,10 @@
     </row>
     <row r="141" spans="1:17" ht="34" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -6553,10 +6974,10 @@
     </row>
     <row r="142" spans="1:17" ht="34" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
@@ -6576,10 +6997,10 @@
     </row>
     <row r="143" spans="1:17" ht="34" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -6599,10 +7020,10 @@
     </row>
     <row r="144" spans="1:17" ht="34" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
@@ -6622,10 +7043,10 @@
     </row>
     <row r="145" spans="1:17" ht="34" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -6645,10 +7066,10 @@
     </row>
     <row r="146" spans="1:17" ht="34" customHeight="1">
       <c r="A146" s="8" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
@@ -6668,10 +7089,10 @@
     </row>
     <row r="147" spans="1:17" ht="34" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -6691,10 +7112,10 @@
     </row>
     <row r="148" spans="1:17" ht="34" customHeight="1">
       <c r="A148" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
@@ -6714,10 +7135,10 @@
     </row>
     <row r="149" spans="1:17" ht="34" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -6737,10 +7158,10 @@
     </row>
     <row r="150" spans="1:17" ht="34" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
@@ -6760,10 +7181,10 @@
     </row>
     <row r="151" spans="1:17" ht="34" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>

--- a/src/content/info/案例指标信息.xlsx
+++ b/src/content/info/案例指标信息.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\L\d\03-开合\OpenLink\src\content\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D005BE71-B4F2-4B39-99A4-509988444DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB617DA-E3F3-4B8B-8636-B38CDD939E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,11 +19,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">案例指标信息!$A$1:$Q$151</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="700">
   <si>
     <t>时间（date）</t>
   </si>
@@ -457,9 +458,6 @@
     <t>2022-12-20</t>
   </si>
   <si>
-    <t>广东嘉速物流工改工项目</t>
-  </si>
-  <si>
     <t>2022-11-10</t>
   </si>
   <si>
@@ -682,9 +680,6 @@
     <t>2021-10-19</t>
   </si>
   <si>
-    <t>鹏峰</t>
-  </si>
-  <si>
     <t>2021-10-15</t>
   </si>
   <si>
@@ -809,9 +804,6 @@
   </si>
   <si>
     <t>Chancheng District, Foshan</t>
-  </si>
-  <si>
-    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
   </si>
   <si>
     <t>Anodized Aluminum Panel，Glass，Perforated Metal Panel</t>
@@ -2208,7 +2200,87 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>433540㎡</t>
+    <t>101009㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、阳极氧化铝板、玻璃、金属格栅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教学及辅助用房、幼儿园、办公用房、生活用房</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏峰地下停车场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>59139㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川省、天府新区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶合木、 阳极氧化铝板、金属格栅、玻璃、清水混凝土</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川天府新区教育和卫生健康局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市、宝安区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清水混凝土、金属格栅、阳极氧化铝板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停车场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹏峰集团</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳极氧化铝板、玻璃，金属穿孔板</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公，商业、公寓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>87790㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公、社区服务站、文化活动中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3139㎡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>老挝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>办公、展厅、会所</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2798,22 +2870,22 @@
         <v>46370</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12" t="s">
@@ -2830,7 +2902,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="9">
@@ -2840,23 +2912,23 @@
         <v>517.96</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="Q3" s="3"/>
     </row>
@@ -2865,7 +2937,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5" t="s">
@@ -2876,26 +2948,26 @@
         <v>46152</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="11" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="Q4" s="5"/>
     </row>
@@ -2904,37 +2976,37 @@
         <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
         <v>2026</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="11" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="Q5" s="3"/>
     </row>
@@ -2947,31 +3019,31 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="10">
         <v>46252</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="Q6" s="5"/>
     </row>
@@ -2984,7 +3056,7 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="9">
@@ -2996,11 +3068,11 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -3015,33 +3087,33 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="10">
         <v>46090</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q8" s="5"/>
     </row>
@@ -3050,33 +3122,33 @@
         <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="9">
         <v>45889</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -3105,7 +3177,7 @@
         <v>38</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
@@ -3115,7 +3187,7 @@
         <v>40</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>41</v>
@@ -3142,7 +3214,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="9">
@@ -3150,23 +3222,23 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="Q11" s="3"/>
     </row>
@@ -3179,33 +3251,33 @@
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5">
         <v>2026</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="Q12" s="5"/>
     </row>
@@ -3218,31 +3290,31 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3">
         <v>2026</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -3276,37 +3348,37 @@
         <v>54</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="10">
         <v>45559</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q15" s="5"/>
     </row>
@@ -3319,33 +3391,33 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="9">
         <v>45873</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="Q16" s="3"/>
     </row>
@@ -3380,7 +3452,7 @@
         <v>64</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>65</v>
@@ -3407,33 +3479,33 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="9">
         <v>45608</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="Q18" s="3"/>
     </row>
@@ -3446,31 +3518,31 @@
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="10">
         <v>45310</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="O19" s="5"/>
       <c r="P19" s="5" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="Q19" s="5"/>
     </row>
@@ -3483,33 +3555,33 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="9">
         <v>45296</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>679</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="Q20" s="3"/>
     </row>
@@ -3541,37 +3613,37 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="9">
         <v>45366</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="Q22" s="3"/>
     </row>
@@ -3580,33 +3652,33 @@
         <v>79</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="10">
         <v>45403</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -3695,7 +3767,7 @@
         <v>97</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>99</v>
@@ -3707,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
@@ -3717,7 +3789,7 @@
         <v>102</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>103</v>
@@ -3744,33 +3816,33 @@
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="10">
         <v>45478</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="O27" s="5"/>
       <c r="P27" s="5" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="Q27" s="5"/>
     </row>
@@ -3805,7 +3877,7 @@
         <v>117</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>118</v>
@@ -3855,33 +3927,33 @@
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="9">
         <v>45349</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="Q30" s="3"/>
     </row>
@@ -3916,7 +3988,7 @@
         <v>134</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>135</v>
@@ -3966,33 +4038,33 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="10">
         <v>45061</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="5" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="Q33" s="5"/>
     </row>
@@ -4000,20 +4072,12 @@
       <c r="A34" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="3" t="s">
-        <v>586</v>
-      </c>
+      <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="9">
-        <v>44943</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>682</v>
-      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -4027,62 +4091,62 @@
     </row>
     <row r="35" spans="1:17" ht="34" customHeight="1">
       <c r="A35" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="F35" s="5">
         <v>2025</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="L35" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="M35" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="M35" s="5" t="s">
+      <c r="N35" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="N35" s="5" t="s">
+      <c r="O35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="P35" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="P35" s="5" t="s">
+      <c r="Q35" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>130</v>
@@ -4090,97 +4154,97 @@
       <c r="E36" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="3">
-        <v>2022</v>
+      <c r="F36" s="9">
+        <v>45006</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="M36" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="M36" s="3" t="s">
+      <c r="N36" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="P36" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N36" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="P36" s="3" t="s">
+      <c r="Q36" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="34" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F37" s="3">
         <v>2022</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="M37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="M37" s="3" t="s">
+      <c r="N37" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="O37" s="3" t="s">
+      <c r="P37" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="P37" s="3" t="s">
+      <c r="Q37" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="34" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>130</v>
@@ -4188,166 +4252,180 @@
       <c r="E38" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F38" s="5">
-        <v>2022</v>
+      <c r="F38" s="10">
+        <v>44943</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="L38" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="M38" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="L38" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="M38" s="5" t="s">
+      <c r="N38" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="N38" s="5" t="s">
+      <c r="O38" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="P38" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="P38" s="5" t="s">
+      <c r="Q38" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="34" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>130</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39" s="9">
+        <v>45012</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F39" s="3">
-        <v>2022</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="L39" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N39" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="N39" s="3" t="s">
+      <c r="O39" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="O39" s="3" t="s">
+      <c r="P39" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="P39" s="3" t="s">
+      <c r="Q39" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="34" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="F40" s="5">
         <v>2022</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="L40" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="M40" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="M40" s="5" t="s">
+      <c r="N40" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="P40" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="N40" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="P40" s="5" t="s">
+      <c r="Q40" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="34" customHeight="1">
       <c r="A41" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>599</v>
+      </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="10">
+        <v>44689</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>679</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
+      <c r="J41" s="5" t="s">
+        <v>680</v>
+      </c>
       <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="5" t="s">
+        <v>681</v>
+      </c>
       <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
+      <c r="N41" s="5" t="s">
+        <v>682</v>
+      </c>
       <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
+      <c r="P41" s="5" t="s">
+        <v>680</v>
+      </c>
       <c r="Q41" s="5"/>
     </row>
     <row r="42" spans="1:17" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -4367,151 +4445,179 @@
     </row>
     <row r="43" spans="1:17" ht="34" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>219</v>
+        <v>683</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+      <c r="D43" s="5" t="s">
+        <v>616</v>
+      </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="F43" s="10">
+        <v>44488</v>
+      </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="J43" s="5" t="s">
+        <v>688</v>
+      </c>
       <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="5" t="s">
+        <v>689</v>
+      </c>
       <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
+      <c r="N43" s="5" t="s">
+        <v>690</v>
+      </c>
       <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
+      <c r="P43" s="5" t="s">
+        <v>691</v>
+      </c>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:17" ht="34" customHeight="1">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+    </row>
+    <row r="45" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A45" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="1:17" ht="34" customHeight="1">
-      <c r="A45" s="5" t="s">
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+    </row>
+    <row r="46" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A46" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-    </row>
-    <row r="46" spans="1:17" ht="34" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+    </row>
+    <row r="47" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A47" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="1:17" ht="34" customHeight="1">
-      <c r="A47" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
     </row>
     <row r="48" spans="1:17" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>599</v>
+      </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="F48" s="9">
+        <v>44370</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>684</v>
+      </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>685</v>
+      </c>
       <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
+      <c r="L48" s="3" t="s">
+        <v>686</v>
+      </c>
       <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
+      <c r="N48" s="3" t="s">
+        <v>608</v>
+      </c>
       <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
+      <c r="P48" s="3" t="s">
+        <v>687</v>
+      </c>
       <c r="Q48" s="3"/>
     </row>
     <row r="49" spans="1:17" ht="34" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
+      <c r="D49" s="5" t="s">
+        <v>574</v>
+      </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -4526,61 +4632,61 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
     </row>
-    <row r="50" spans="1:17" ht="34" customHeight="1">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15"/>
+    </row>
+    <row r="51" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A51" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="1:17" ht="34" customHeight="1">
-      <c r="A51" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
     </row>
     <row r="52" spans="1:17" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>130</v>
@@ -4588,45 +4694,45 @@
       <c r="E52" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="3">
-        <v>2021</v>
+      <c r="F52" s="9">
+        <v>44792</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N52" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="O52" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="N52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="Q52" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="34" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -4644,35 +4750,35 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
     </row>
-    <row r="54" spans="1:17" ht="34" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
+    <row r="54" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+      <c r="Q54" s="15"/>
     </row>
     <row r="55" spans="1:17" ht="34" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -4692,10 +4798,10 @@
     </row>
     <row r="56" spans="1:17" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -4715,154 +4821,164 @@
     </row>
     <row r="57" spans="1:17" ht="34" customHeight="1">
       <c r="A57" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="F57" s="5">
         <v>2022</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="M57" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="K57" s="5" t="s">
+      <c r="N57" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="L57" s="5" t="s">
+      <c r="O57" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="M57" s="5" t="s">
+      <c r="P57" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="N57" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="O57" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="P57" s="5" t="s">
-        <v>266</v>
-      </c>
       <c r="Q57" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>130</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F58" s="3">
         <v>2020</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="N58" s="3" t="s">
+      <c r="Q58" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="34" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>692</v>
+      </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+      <c r="F59" s="9">
+        <v>43784</v>
+      </c>
+      <c r="G59" s="3">
+        <v>138726</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
+      <c r="L59" s="3" t="s">
+        <v>693</v>
+      </c>
       <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
+      <c r="N59" s="3" t="s">
+        <v>694</v>
+      </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
     </row>
-    <row r="60" spans="1:17" ht="34" customHeight="1">
-      <c r="A60" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
+    <row r="60" spans="1:17" s="16" customFormat="1" ht="34" customHeight="1">
+      <c r="A60" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
     </row>
     <row r="61" spans="1:17" ht="34" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -4882,33 +4998,43 @@
     </row>
     <row r="62" spans="1:17" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="F62" s="9">
+        <v>43737</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>695</v>
+      </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
+      <c r="L62" s="3" t="s">
+        <v>693</v>
+      </c>
       <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
+      <c r="N62" s="3" t="s">
+        <v>696</v>
+      </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
     <row r="63" spans="1:17" ht="34" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -4928,10 +5054,10 @@
     </row>
     <row r="64" spans="1:17" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -4951,10 +5077,10 @@
     </row>
     <row r="65" spans="1:17" ht="34" customHeight="1">
       <c r="A65" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -4974,59 +5100,59 @@
     </row>
     <row r="66" spans="1:17" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F66" s="3">
         <v>2019</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="N66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="34" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -5046,10 +5172,10 @@
     </row>
     <row r="68" spans="1:17" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -5069,10 +5195,10 @@
     </row>
     <row r="69" spans="1:17" ht="34" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -5092,10 +5218,10 @@
     </row>
     <row r="70" spans="1:17" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -5115,10 +5241,10 @@
     </row>
     <row r="71" spans="1:17" ht="34" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -5138,10 +5264,10 @@
     </row>
     <row r="72" spans="1:17" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -5161,10 +5287,10 @@
     </row>
     <row r="73" spans="1:17" ht="34" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -5184,59 +5310,59 @@
     </row>
     <row r="74" spans="1:17" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="F74" s="3">
         <v>2018</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="M74" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="N74" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="L74" s="3" t="s">
+      <c r="O74" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="M74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="N74" s="3" t="s">
+      <c r="Q74" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q74" s="3" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="34" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -5256,10 +5382,10 @@
     </row>
     <row r="76" spans="1:17" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -5279,10 +5405,10 @@
     </row>
     <row r="77" spans="1:17" ht="34" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -5302,10 +5428,10 @@
     </row>
     <row r="78" spans="1:17" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
@@ -5325,10 +5451,10 @@
     </row>
     <row r="79" spans="1:17" ht="34" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -5348,10 +5474,10 @@
     </row>
     <row r="80" spans="1:17" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -5371,10 +5497,10 @@
     </row>
     <row r="81" spans="1:17" ht="34" customHeight="1">
       <c r="A81" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -5394,10 +5520,10 @@
     </row>
     <row r="82" spans="1:17" ht="34" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -5417,10 +5543,10 @@
     </row>
     <row r="83" spans="1:17" ht="34" customHeight="1">
       <c r="A83" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -5440,10 +5566,10 @@
     </row>
     <row r="84" spans="1:17" ht="34" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -5463,10 +5589,10 @@
     </row>
     <row r="85" spans="1:17" ht="34" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -5486,10 +5612,10 @@
     </row>
     <row r="86" spans="1:17" ht="34" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -5509,10 +5635,10 @@
     </row>
     <row r="87" spans="1:17" ht="34" customHeight="1">
       <c r="A87" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -5532,10 +5658,10 @@
     </row>
     <row r="88" spans="1:17" ht="34" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -5555,10 +5681,10 @@
     </row>
     <row r="89" spans="1:17" ht="34" customHeight="1">
       <c r="A89" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -5578,10 +5704,10 @@
     </row>
     <row r="90" spans="1:17" ht="34" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -5601,10 +5727,10 @@
     </row>
     <row r="91" spans="1:17" ht="34" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -5624,10 +5750,10 @@
     </row>
     <row r="92" spans="1:17" ht="34" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -5647,10 +5773,10 @@
     </row>
     <row r="93" spans="1:17" ht="34" customHeight="1">
       <c r="A93" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -5670,10 +5796,10 @@
     </row>
     <row r="94" spans="1:17" ht="34" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
@@ -5693,10 +5819,10 @@
     </row>
     <row r="95" spans="1:17" ht="34" customHeight="1">
       <c r="A95" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -5716,10 +5842,10 @@
     </row>
     <row r="96" spans="1:17" ht="34" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
@@ -5739,10 +5865,10 @@
     </row>
     <row r="97" spans="1:17" ht="34" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -5762,10 +5888,10 @@
     </row>
     <row r="98" spans="1:17" ht="34" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -5785,10 +5911,10 @@
     </row>
     <row r="99" spans="1:17" ht="34" customHeight="1">
       <c r="A99" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -5808,10 +5934,10 @@
     </row>
     <row r="100" spans="1:17" ht="34" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -5831,10 +5957,10 @@
     </row>
     <row r="101" spans="1:17" ht="34" customHeight="1">
       <c r="A101" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -5854,10 +5980,10 @@
     </row>
     <row r="102" spans="1:17" ht="34" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -5877,10 +6003,10 @@
     </row>
     <row r="103" spans="1:17" ht="34" customHeight="1">
       <c r="A103" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -5900,10 +6026,10 @@
     </row>
     <row r="104" spans="1:17" ht="34" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -5923,10 +6049,10 @@
     </row>
     <row r="105" spans="1:17" ht="34" customHeight="1">
       <c r="A105" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -5946,59 +6072,59 @@
     </row>
     <row r="106" spans="1:17" ht="34" customHeight="1">
       <c r="A106" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="E106" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F106" s="3">
         <v>2015</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K106" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K106" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="L106" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="M106" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="M106" s="3" t="s">
+      <c r="N106" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="N106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="O106" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="P106" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="34" customHeight="1">
       <c r="A107" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
@@ -6018,10 +6144,10 @@
     </row>
     <row r="108" spans="1:17" ht="34" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -6041,10 +6167,10 @@
     </row>
     <row r="109" spans="1:17" ht="34" customHeight="1">
       <c r="A109" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -6064,10 +6190,10 @@
     </row>
     <row r="110" spans="1:17" ht="34" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -6087,10 +6213,10 @@
     </row>
     <row r="111" spans="1:17" ht="34" customHeight="1">
       <c r="A111" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -6110,10 +6236,10 @@
     </row>
     <row r="112" spans="1:17" ht="34" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -6133,10 +6259,10 @@
     </row>
     <row r="113" spans="1:17" ht="34" customHeight="1">
       <c r="A113" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -6156,10 +6282,10 @@
     </row>
     <row r="114" spans="1:17" ht="34" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
@@ -6179,10 +6305,10 @@
     </row>
     <row r="115" spans="1:17" ht="34" customHeight="1">
       <c r="A115" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -6202,10 +6328,10 @@
     </row>
     <row r="116" spans="1:17" ht="34" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -6225,10 +6351,10 @@
     </row>
     <row r="117" spans="1:17" ht="34" customHeight="1">
       <c r="A117" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -6248,10 +6374,10 @@
     </row>
     <row r="118" spans="1:17" ht="34" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -6271,10 +6397,10 @@
     </row>
     <row r="119" spans="1:17" ht="34" customHeight="1">
       <c r="A119" s="5" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
@@ -6294,10 +6420,10 @@
     </row>
     <row r="120" spans="1:17" ht="34" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -6317,10 +6443,10 @@
     </row>
     <row r="121" spans="1:17" ht="34" customHeight="1">
       <c r="A121" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
@@ -6340,85 +6466,97 @@
     </row>
     <row r="122" spans="1:17" ht="34" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
+      <c r="D122" s="3" t="s">
+        <v>571</v>
+      </c>
       <c r="E122" s="3"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="3"/>
+      <c r="F122" s="9">
+        <v>42010</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>697</v>
+      </c>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
-      <c r="J122" s="3"/>
+      <c r="J122" s="3" t="s">
+        <v>698</v>
+      </c>
       <c r="K122" s="3"/>
-      <c r="L122" s="3"/>
+      <c r="L122" s="3" t="s">
+        <v>669</v>
+      </c>
       <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
+      <c r="N122" s="3" t="s">
+        <v>699</v>
+      </c>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
       <c r="Q122" s="3"/>
     </row>
     <row r="123" spans="1:17" ht="34" customHeight="1">
       <c r="A123" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D123" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="E123" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="F123" s="6">
         <v>2013</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="K123" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="L123" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="M123" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="K123" s="5" t="s">
+      <c r="N123" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="L123" s="5" t="s">
+      <c r="O123" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="M123" s="5" t="s">
+      <c r="P123" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="N123" s="5" t="s">
+      <c r="Q123" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="O123" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="P123" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q123" s="5" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="34" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>98</v>
@@ -6430,86 +6568,86 @@
         <v>2013</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="M124" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="K124" s="3" t="s">
+      <c r="N124" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="O124" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="M124" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="O124" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
     </row>
     <row r="125" spans="1:17" ht="34" customHeight="1">
       <c r="A125" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>458</v>
-      </c>
       <c r="E125" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F125" s="6">
         <v>2012</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K125" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="K125" s="5" t="s">
+      <c r="L125" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="L125" s="5" t="s">
+      <c r="M125" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="M125" s="5" t="s">
+      <c r="N125" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="N125" s="5" t="s">
+      <c r="O125" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="O125" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="P125" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q125" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="34" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
@@ -6529,10 +6667,10 @@
     </row>
     <row r="127" spans="1:17" ht="34" customHeight="1">
       <c r="A127" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
@@ -6552,59 +6690,59 @@
     </row>
     <row r="128" spans="1:17" ht="34" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F128" s="4">
         <v>2013</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="O128" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="P128" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="L128" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="N128" s="3" t="s">
+      <c r="Q128" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="O128" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="P128" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="Q128" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="34" customHeight="1">
       <c r="A129" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
@@ -6624,10 +6762,10 @@
     </row>
     <row r="130" spans="1:17" ht="34" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
@@ -6647,108 +6785,108 @@
     </row>
     <row r="131" spans="1:17" ht="34" customHeight="1">
       <c r="A131" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="E131" s="5" t="s">
         <v>477</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="F131" s="6">
         <v>2011</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="L131" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="N131" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="O131" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="K131" s="5" t="s">
+      <c r="P131" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="L131" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="M131" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="N131" s="5" t="s">
+      <c r="Q131" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="O131" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="P131" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q131" s="5" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="34" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F132" s="4">
         <v>2011</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="M132" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="K132" s="3" t="s">
+      <c r="N132" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="L132" s="3" t="s">
+      <c r="O132" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="M132" s="3" t="s">
+      <c r="P132" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="N132" s="3" t="s">
+      <c r="Q132" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="O132" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="P132" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q132" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="133" spans="1:17" ht="34" customHeight="1">
       <c r="A133" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
@@ -6768,55 +6906,55 @@
     </row>
     <row r="134" spans="1:17" ht="34" customHeight="1">
       <c r="A134" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="F134" s="4">
         <v>2009</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="M134" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="K134" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="M134" s="3" t="s">
-        <v>512</v>
-      </c>
       <c r="N134" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="P134" s="3"/>
       <c r="Q134" s="3"/>
     </row>
     <row r="135" spans="1:17" ht="34" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -6836,10 +6974,10 @@
     </row>
     <row r="136" spans="1:17" ht="34" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
@@ -6859,10 +6997,10 @@
     </row>
     <row r="137" spans="1:17" ht="34" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -6882,10 +7020,10 @@
     </row>
     <row r="138" spans="1:17" ht="34" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
@@ -6905,10 +7043,10 @@
     </row>
     <row r="139" spans="1:17" ht="34" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -6928,10 +7066,10 @@
     </row>
     <row r="140" spans="1:17" ht="34" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
@@ -6951,10 +7089,10 @@
     </row>
     <row r="141" spans="1:17" ht="34" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -6974,10 +7112,10 @@
     </row>
     <row r="142" spans="1:17" ht="34" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
@@ -6997,10 +7135,10 @@
     </row>
     <row r="143" spans="1:17" ht="34" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -7020,10 +7158,10 @@
     </row>
     <row r="144" spans="1:17" ht="34" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
@@ -7043,10 +7181,10 @@
     </row>
     <row r="145" spans="1:17" ht="34" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -7066,10 +7204,10 @@
     </row>
     <row r="146" spans="1:17" ht="34" customHeight="1">
       <c r="A146" s="8" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
@@ -7089,10 +7227,10 @@
     </row>
     <row r="147" spans="1:17" ht="34" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -7112,10 +7250,10 @@
     </row>
     <row r="148" spans="1:17" ht="34" customHeight="1">
       <c r="A148" s="8" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
@@ -7135,10 +7273,10 @@
     </row>
     <row r="149" spans="1:17" ht="34" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -7158,10 +7296,10 @@
     </row>
     <row r="150" spans="1:17" ht="34" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
@@ -7181,10 +7319,10 @@
     </row>
     <row r="151" spans="1:17" ht="34" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
